--- a/data/pest_disease_control.xlsx
+++ b/data/pest_disease_control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="989" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="214">
   <si>
     <t>Date</t>
   </si>
@@ -493,6 +493,9 @@
     <t>2025-07-01</t>
   </si>
   <si>
+    <t>2025-07-15</t>
+  </si>
+  <si>
     <t>DG03000</t>
   </si>
   <si>
@@ -613,6 +616,9 @@
     <t>DG19000</t>
   </si>
   <si>
+    <t>DG27004</t>
+  </si>
+  <si>
     <t>R570</t>
   </si>
   <si>
@@ -631,10 +637,10 @@
     <t>97F1692</t>
   </si>
   <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>26.4</t>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>0</t>
@@ -1007,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L244"/>
+  <dimension ref="A1:L245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1053,10 +1059,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D2">
         <v>0.32</v>
@@ -1074,7 +1080,7 @@
         <v>6</v>
       </c>
       <c r="L2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1082,13 +1088,13 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H3">
         <v>6.327</v>
       </c>
       <c r="I3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J3">
         <v>12.347</v>
@@ -1097,7 +1103,7 @@
         <v>4</v>
       </c>
       <c r="L3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1105,10 +1111,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D4">
         <v>0.43</v>
@@ -1126,7 +1132,7 @@
         <v>9</v>
       </c>
       <c r="L4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1134,10 +1140,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D5">
         <v>1.07</v>
@@ -1155,7 +1161,7 @@
         <v>11</v>
       </c>
       <c r="L5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1163,10 +1169,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D6">
         <v>1.05</v>
@@ -1184,7 +1190,7 @@
         <v>10</v>
       </c>
       <c r="L6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1192,10 +1198,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D7">
         <v>1.32</v>
@@ -1213,7 +1219,7 @@
         <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1221,10 +1227,10 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C8" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D8">
         <v>0.06</v>
@@ -1242,7 +1248,7 @@
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1250,10 +1256,10 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D9">
         <v>0.16</v>
@@ -1271,7 +1277,7 @@
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1279,10 +1285,10 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D10">
         <v>0.28</v>
@@ -1300,7 +1306,7 @@
         <v>6</v>
       </c>
       <c r="L10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1308,10 +1314,10 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D11">
         <v>0.6</v>
@@ -1329,7 +1335,7 @@
         <v>7</v>
       </c>
       <c r="L11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1337,10 +1343,10 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D12">
         <v>0.16</v>
@@ -1358,7 +1364,7 @@
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1366,10 +1372,10 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D13">
         <v>0.5</v>
@@ -1387,7 +1393,7 @@
         <v>7</v>
       </c>
       <c r="L13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1395,10 +1401,10 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D14">
         <v>0.2</v>
@@ -1416,7 +1422,7 @@
         <v>7</v>
       </c>
       <c r="L14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1424,10 +1430,10 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C15" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D15">
         <v>0.15</v>
@@ -1445,7 +1451,7 @@
         <v>7</v>
       </c>
       <c r="L15" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1453,10 +1459,10 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C16" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D16">
         <v>0.6</v>
@@ -1474,7 +1480,7 @@
         <v>8</v>
       </c>
       <c r="L16" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1482,10 +1488,10 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C17" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D17">
         <v>0.47</v>
@@ -1503,7 +1509,7 @@
         <v>7</v>
       </c>
       <c r="L17" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1511,10 +1517,10 @@
         <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C18" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D18">
         <v>0.32</v>
@@ -1532,7 +1538,7 @@
         <v>7</v>
       </c>
       <c r="L18" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1540,10 +1546,10 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D19">
         <v>0.47</v>
@@ -1561,7 +1567,7 @@
         <v>8</v>
       </c>
       <c r="L19" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1569,10 +1575,10 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C20" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D20">
         <v>0.2</v>
@@ -1590,7 +1596,7 @@
         <v>8</v>
       </c>
       <c r="L20" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1598,10 +1604,10 @@
         <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C21" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D21">
         <v>0.33</v>
@@ -1619,7 +1625,7 @@
         <v>11</v>
       </c>
       <c r="L21" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1627,10 +1633,10 @@
         <v>32</v>
       </c>
       <c r="B22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C22" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D22">
         <v>0.43</v>
@@ -1648,7 +1654,7 @@
         <v>11</v>
       </c>
       <c r="L22" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1656,10 +1662,10 @@
         <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C23" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D23">
         <v>0.67</v>
@@ -1677,7 +1683,7 @@
         <v>11</v>
       </c>
       <c r="L23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1685,10 +1691,10 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C24" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D24">
         <v>0.76</v>
@@ -1706,7 +1712,7 @@
         <v>10</v>
       </c>
       <c r="L24" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1714,10 +1720,10 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C25" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D25">
         <v>0.52</v>
@@ -1735,7 +1741,7 @@
         <v>11</v>
       </c>
       <c r="L25" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -1743,10 +1749,10 @@
         <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C26" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D26">
         <v>0.29</v>
@@ -1764,7 +1770,7 @@
         <v>11</v>
       </c>
       <c r="L26" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -1772,10 +1778,10 @@
         <v>37</v>
       </c>
       <c r="B27" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C27" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D27">
         <v>0.28</v>
@@ -1793,7 +1799,7 @@
         <v>11</v>
       </c>
       <c r="L27" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -1801,10 +1807,10 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D28">
         <v>0.11</v>
@@ -1822,7 +1828,7 @@
         <v>11</v>
       </c>
       <c r="L28" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -1830,10 +1836,10 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D29">
         <v>0.4</v>
@@ -1851,7 +1857,7 @@
         <v>23</v>
       </c>
       <c r="L29" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -1859,10 +1865,10 @@
         <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C30" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D30">
         <v>0.29</v>
@@ -1880,7 +1886,7 @@
         <v>23</v>
       </c>
       <c r="L30" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -1888,10 +1894,10 @@
         <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C31" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D31">
         <v>0.64</v>
@@ -1909,7 +1915,7 @@
         <v>23</v>
       </c>
       <c r="L31" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -1917,10 +1923,10 @@
         <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C32" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D32">
         <v>0.68</v>
@@ -1938,7 +1944,7 @@
         <v>23</v>
       </c>
       <c r="L32" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -1946,10 +1952,10 @@
         <v>43</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D33">
         <v>0.49</v>
@@ -1967,7 +1973,7 @@
         <v>23</v>
       </c>
       <c r="L33" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -1975,10 +1981,10 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D34">
         <v>0.49</v>
@@ -1996,7 +2002,7 @@
         <v>23</v>
       </c>
       <c r="L34" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2004,10 +2010,10 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C35" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D35">
         <v>0.45</v>
@@ -2025,7 +2031,7 @@
         <v>23</v>
       </c>
       <c r="L35" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2033,10 +2039,10 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C36" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D36">
         <v>0.55</v>
@@ -2054,7 +2060,7 @@
         <v>23</v>
       </c>
       <c r="L36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2062,10 +2068,10 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C37" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D37">
         <v>0.43</v>
@@ -2083,7 +2089,7 @@
         <v>23</v>
       </c>
       <c r="L37" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2091,10 +2097,10 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C38" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D38">
         <v>0.08</v>
@@ -2112,7 +2118,7 @@
         <v>18</v>
       </c>
       <c r="L38" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2120,10 +2126,10 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C39" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D39">
         <v>0.52</v>
@@ -2141,7 +2147,7 @@
         <v>18</v>
       </c>
       <c r="L39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2149,10 +2155,10 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C40" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D40">
         <v>0.83</v>
@@ -2170,7 +2176,7 @@
         <v>19</v>
       </c>
       <c r="L40" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2178,10 +2184,10 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C41" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D41">
         <v>0.83</v>
@@ -2199,7 +2205,7 @@
         <v>18</v>
       </c>
       <c r="L41" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2207,10 +2213,10 @@
         <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C42" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D42">
         <v>0.8100000000000001</v>
@@ -2228,7 +2234,7 @@
         <v>18</v>
       </c>
       <c r="L42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2236,10 +2242,10 @@
         <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C43" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D43">
         <v>0.38</v>
@@ -2257,7 +2263,7 @@
         <v>18</v>
       </c>
       <c r="L43" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2265,10 +2271,10 @@
         <v>53</v>
       </c>
       <c r="B44" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C44" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D44">
         <v>0.28</v>
@@ -2286,7 +2292,7 @@
         <v>19</v>
       </c>
       <c r="L44" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2294,10 +2300,10 @@
         <v>54</v>
       </c>
       <c r="B45" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C45" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D45">
         <v>0.26</v>
@@ -2315,7 +2321,7 @@
         <v>17</v>
       </c>
       <c r="L45" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2323,10 +2329,10 @@
         <v>55</v>
       </c>
       <c r="B46" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C46" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D46">
         <v>0.49</v>
@@ -2344,7 +2350,7 @@
         <v>18</v>
       </c>
       <c r="L46" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2352,10 +2358,10 @@
         <v>56</v>
       </c>
       <c r="B47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C47" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D47">
         <v>0.89</v>
@@ -2373,7 +2379,7 @@
         <v>18</v>
       </c>
       <c r="L47" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2381,10 +2387,10 @@
         <v>57</v>
       </c>
       <c r="B48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C48" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D48">
         <v>1.03</v>
@@ -2402,7 +2408,7 @@
         <v>19</v>
       </c>
       <c r="L48" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2410,10 +2416,10 @@
         <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C49" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D49">
         <v>0.4</v>
@@ -2431,7 +2437,7 @@
         <v>18</v>
       </c>
       <c r="L49" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2439,10 +2445,10 @@
         <v>59</v>
       </c>
       <c r="B50" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C50" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D50">
         <v>0.29</v>
@@ -2460,7 +2466,7 @@
         <v>19</v>
       </c>
       <c r="L50" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2468,10 +2474,10 @@
         <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C51" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D51">
         <v>0.2</v>
@@ -2489,7 +2495,7 @@
         <v>19</v>
       </c>
       <c r="L51" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2497,10 +2503,10 @@
         <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C52" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D52">
         <v>0.08</v>
@@ -2518,7 +2524,7 @@
         <v>18</v>
       </c>
       <c r="L52" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2526,10 +2532,10 @@
         <v>62</v>
       </c>
       <c r="B53" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C53" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D53">
         <v>0.16</v>
@@ -2547,7 +2553,7 @@
         <v>3</v>
       </c>
       <c r="L53" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2555,10 +2561,10 @@
         <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C54" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D54">
         <v>0.08</v>
@@ -2576,7 +2582,7 @@
         <v>4</v>
       </c>
       <c r="L54" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -2584,10 +2590,10 @@
         <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C55" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D55">
         <v>0.16</v>
@@ -2605,7 +2611,7 @@
         <v>4</v>
       </c>
       <c r="L55" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -2613,10 +2619,10 @@
         <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C56" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D56">
         <v>0.25</v>
@@ -2634,7 +2640,7 @@
         <v>4</v>
       </c>
       <c r="L56" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -2642,10 +2648,10 @@
         <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C57" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D57">
         <v>0.17</v>
@@ -2663,7 +2669,7 @@
         <v>4</v>
       </c>
       <c r="L57" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -2671,10 +2677,10 @@
         <v>67</v>
       </c>
       <c r="B58" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C58" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D58">
         <v>0.2</v>
@@ -2692,7 +2698,7 @@
         <v>4</v>
       </c>
       <c r="L58" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -2700,10 +2706,10 @@
         <v>68</v>
       </c>
       <c r="B59" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C59" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D59">
         <v>0.1</v>
@@ -2721,7 +2727,7 @@
         <v>4</v>
       </c>
       <c r="L59" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -2729,10 +2735,10 @@
         <v>62</v>
       </c>
       <c r="B60" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C60" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D60">
         <v>1.28</v>
@@ -2750,7 +2756,7 @@
         <v>11</v>
       </c>
       <c r="L60" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -2758,10 +2764,10 @@
         <v>63</v>
       </c>
       <c r="B61" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C61" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D61">
         <v>0.77</v>
@@ -2779,7 +2785,7 @@
         <v>11</v>
       </c>
       <c r="L61" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -2787,10 +2793,10 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C62" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D62">
         <v>1.22</v>
@@ -2808,7 +2814,7 @@
         <v>12</v>
       </c>
       <c r="L62" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -2816,10 +2822,10 @@
         <v>65</v>
       </c>
       <c r="B63" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C63" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D63">
         <v>0.91</v>
@@ -2837,7 +2843,7 @@
         <v>11</v>
       </c>
       <c r="L63" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -2845,10 +2851,10 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C64" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D64">
         <v>0.9399999999999999</v>
@@ -2866,7 +2872,7 @@
         <v>12</v>
       </c>
       <c r="L64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -2874,10 +2880,10 @@
         <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C65" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D65">
         <v>0.71</v>
@@ -2895,7 +2901,7 @@
         <v>12</v>
       </c>
       <c r="L65" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -2903,10 +2909,10 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C66" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D66">
         <v>0.45</v>
@@ -2924,7 +2930,7 @@
         <v>12</v>
       </c>
       <c r="L66" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -2932,10 +2938,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C67" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D67">
         <v>0.17</v>
@@ -2953,7 +2959,7 @@
         <v>13</v>
       </c>
       <c r="L67" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -2961,10 +2967,10 @@
         <v>73</v>
       </c>
       <c r="B68" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C68" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D68">
         <v>0.12</v>
@@ -2982,7 +2988,7 @@
         <v>9</v>
       </c>
       <c r="L68" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -2990,10 +2996,10 @@
         <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C69" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D69">
         <v>0.05</v>
@@ -3011,7 +3017,7 @@
         <v>7</v>
       </c>
       <c r="L69" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3019,10 +3025,10 @@
         <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C70" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D70">
         <v>0.18</v>
@@ -3040,7 +3046,7 @@
         <v>7</v>
       </c>
       <c r="L70" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3048,10 +3054,10 @@
         <v>76</v>
       </c>
       <c r="B71" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C71" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D71">
         <v>0.07000000000000001</v>
@@ -3069,7 +3075,7 @@
         <v>7</v>
       </c>
       <c r="L71" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3077,10 +3083,10 @@
         <v>77</v>
       </c>
       <c r="B72" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D72">
         <v>0.21</v>
@@ -3098,7 +3104,7 @@
         <v>8</v>
       </c>
       <c r="L72" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3106,10 +3112,10 @@
         <v>38</v>
       </c>
       <c r="B73" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C73" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D73">
         <v>0.21</v>
@@ -3127,7 +3133,7 @@
         <v>8</v>
       </c>
       <c r="L73" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3135,10 +3141,10 @@
         <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C74" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D74">
         <v>0.14</v>
@@ -3156,7 +3162,7 @@
         <v>5</v>
       </c>
       <c r="L74" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3164,10 +3170,10 @@
         <v>79</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C75" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D75">
         <v>0.57</v>
@@ -3185,7 +3191,7 @@
         <v>13</v>
       </c>
       <c r="L75" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3193,10 +3199,10 @@
         <v>58</v>
       </c>
       <c r="B76" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C76" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D76">
         <v>1.02</v>
@@ -3214,7 +3220,7 @@
         <v>13</v>
       </c>
       <c r="L76" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3222,10 +3228,10 @@
         <v>80</v>
       </c>
       <c r="B77" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C77" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D77">
         <v>1.31</v>
@@ -3243,7 +3249,7 @@
         <v>14</v>
       </c>
       <c r="L77" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3251,10 +3257,10 @@
         <v>81</v>
       </c>
       <c r="B78" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C78" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D78">
         <v>0.95</v>
@@ -3272,7 +3278,7 @@
         <v>14</v>
       </c>
       <c r="L78" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3280,10 +3286,10 @@
         <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C79" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D79">
         <v>0.9399999999999999</v>
@@ -3301,7 +3307,7 @@
         <v>14</v>
       </c>
       <c r="L79" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3309,10 +3315,10 @@
         <v>83</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C80" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D80">
         <v>0.26</v>
@@ -3330,7 +3336,7 @@
         <v>14</v>
       </c>
       <c r="L80" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3338,10 +3344,10 @@
         <v>46</v>
       </c>
       <c r="B81" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C81" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D81">
         <v>0.19</v>
@@ -3359,7 +3365,7 @@
         <v>14</v>
       </c>
       <c r="L81" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3367,10 +3373,10 @@
         <v>84</v>
       </c>
       <c r="B82" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C82" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D82">
         <v>0.26</v>
@@ -3388,7 +3394,7 @@
         <v>14</v>
       </c>
       <c r="L82" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3396,10 +3402,10 @@
         <v>85</v>
       </c>
       <c r="B83" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C83" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D83">
         <v>0.95</v>
@@ -3417,7 +3423,7 @@
         <v>16</v>
       </c>
       <c r="L83" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -3425,10 +3431,10 @@
         <v>86</v>
       </c>
       <c r="B84" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C84" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D84">
         <v>1.36</v>
@@ -3446,7 +3452,7 @@
         <v>17</v>
       </c>
       <c r="L84" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -3454,10 +3460,10 @@
         <v>87</v>
       </c>
       <c r="B85" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C85" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D85">
         <v>1.73</v>
@@ -3475,7 +3481,7 @@
         <v>17</v>
       </c>
       <c r="L85" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -3483,10 +3489,10 @@
         <v>88</v>
       </c>
       <c r="B86" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C86" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D86">
         <v>1.73</v>
@@ -3504,7 +3510,7 @@
         <v>17</v>
       </c>
       <c r="L86" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -3512,10 +3518,10 @@
         <v>89</v>
       </c>
       <c r="B87" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C87" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D87">
         <v>1.47</v>
@@ -3533,7 +3539,7 @@
         <v>17</v>
       </c>
       <c r="L87" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -3541,10 +3547,10 @@
         <v>90</v>
       </c>
       <c r="B88" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C88" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D88">
         <v>0.6899999999999999</v>
@@ -3562,7 +3568,7 @@
         <v>13</v>
       </c>
       <c r="L88" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -3570,10 +3576,10 @@
         <v>91</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C89" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D89">
         <v>0.89</v>
@@ -3591,7 +3597,7 @@
         <v>13</v>
       </c>
       <c r="L89" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -3599,10 +3605,10 @@
         <v>92</v>
       </c>
       <c r="B90" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C90" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D90">
         <v>1.66</v>
@@ -3620,7 +3626,7 @@
         <v>13</v>
       </c>
       <c r="L90" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -3628,10 +3634,10 @@
         <v>93</v>
       </c>
       <c r="B91" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C91" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D91">
         <v>2.38</v>
@@ -3649,7 +3655,7 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -3657,10 +3663,10 @@
         <v>66</v>
       </c>
       <c r="B92" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C92" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D92">
         <v>1.62</v>
@@ -3678,7 +3684,7 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -3686,10 +3692,10 @@
         <v>72</v>
       </c>
       <c r="B93" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C93" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D93">
         <v>0.64</v>
@@ -3707,7 +3713,7 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -3715,10 +3721,10 @@
         <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C94" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D94">
         <v>0.14</v>
@@ -3736,7 +3742,7 @@
         <v>9</v>
       </c>
       <c r="L94" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -3744,10 +3750,10 @@
         <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C95" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D95">
         <v>0.14</v>
@@ -3765,7 +3771,7 @@
         <v>9</v>
       </c>
       <c r="L95" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -3773,10 +3779,10 @@
         <v>96</v>
       </c>
       <c r="B96" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C96" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D96">
         <v>0.29</v>
@@ -3794,7 +3800,7 @@
         <v>9</v>
       </c>
       <c r="L96" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -3802,10 +3808,10 @@
         <v>36</v>
       </c>
       <c r="B97" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C97" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D97">
         <v>0.15</v>
@@ -3823,7 +3829,7 @@
         <v>9</v>
       </c>
       <c r="L97" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -3831,10 +3837,10 @@
         <v>37</v>
       </c>
       <c r="B98" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C98" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D98">
         <v>0.31</v>
@@ -3852,7 +3858,7 @@
         <v>9</v>
       </c>
       <c r="L98" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -3860,10 +3866,10 @@
         <v>38</v>
       </c>
       <c r="B99" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C99" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D99">
         <v>0.23</v>
@@ -3881,7 +3887,7 @@
         <v>8</v>
       </c>
       <c r="L99" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -3889,10 +3895,10 @@
         <v>97</v>
       </c>
       <c r="B100" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C100" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D100">
         <v>0.18</v>
@@ -3910,7 +3916,7 @@
         <v>13</v>
       </c>
       <c r="L100" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -3918,10 +3924,10 @@
         <v>98</v>
       </c>
       <c r="B101" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C101" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D101">
         <v>0.27</v>
@@ -3939,7 +3945,7 @@
         <v>13</v>
       </c>
       <c r="L101" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -3947,10 +3953,10 @@
         <v>99</v>
       </c>
       <c r="B102" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C102" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D102">
         <v>0.17</v>
@@ -3968,7 +3974,7 @@
         <v>13</v>
       </c>
       <c r="L102" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -3976,10 +3982,10 @@
         <v>100</v>
       </c>
       <c r="B103" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C103" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D103">
         <v>0.28</v>
@@ -3997,7 +4003,7 @@
         <v>14</v>
       </c>
       <c r="L103" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4005,10 +4011,10 @@
         <v>46</v>
       </c>
       <c r="B104" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C104" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D104">
         <v>0.17</v>
@@ -4026,7 +4032,7 @@
         <v>13</v>
       </c>
       <c r="L104" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4034,10 +4040,10 @@
         <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C105" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D105">
         <v>0.38</v>
@@ -4055,7 +4061,7 @@
         <v>17</v>
       </c>
       <c r="L105" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -4063,10 +4069,10 @@
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C106" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D106">
         <v>0.15</v>
@@ -4084,7 +4090,7 @@
         <v>16</v>
       </c>
       <c r="L106" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -4092,10 +4098,10 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C107" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D107">
         <v>0.24</v>
@@ -4113,7 +4119,7 @@
         <v>16</v>
       </c>
       <c r="L107" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -4121,10 +4127,10 @@
         <v>60</v>
       </c>
       <c r="B108" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C108" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D108">
         <v>2.19</v>
@@ -4142,7 +4148,7 @@
         <v>17</v>
       </c>
       <c r="L108" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -4150,10 +4156,10 @@
         <v>104</v>
       </c>
       <c r="B109" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C109" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D109">
         <v>0.12</v>
@@ -4171,7 +4177,7 @@
         <v>17</v>
       </c>
       <c r="L109" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -4179,10 +4185,10 @@
         <v>87</v>
       </c>
       <c r="B110" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C110" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D110">
         <v>0.75</v>
@@ -4200,7 +4206,7 @@
         <v>19</v>
       </c>
       <c r="L110" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -4208,10 +4214,10 @@
         <v>105</v>
       </c>
       <c r="B111" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C111" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D111">
         <v>0.75</v>
@@ -4229,7 +4235,7 @@
         <v>21</v>
       </c>
       <c r="L111" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -4237,10 +4243,10 @@
         <v>106</v>
       </c>
       <c r="B112" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C112" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D112">
         <v>0.14</v>
@@ -4258,7 +4264,7 @@
         <v>23</v>
       </c>
       <c r="L112" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -4266,10 +4272,10 @@
         <v>107</v>
       </c>
       <c r="B113" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C113" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D113">
         <v>0.14</v>
@@ -4287,7 +4293,7 @@
         <v>21</v>
       </c>
       <c r="L113" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -4295,10 +4301,10 @@
         <v>108</v>
       </c>
       <c r="B114" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C114" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D114">
         <v>0.14</v>
@@ -4316,7 +4322,7 @@
         <v>19</v>
       </c>
       <c r="L114" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -4324,10 +4330,10 @@
         <v>109</v>
       </c>
       <c r="B115" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C115" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D115">
         <v>0.07000000000000001</v>
@@ -4345,7 +4351,7 @@
         <v>17</v>
       </c>
       <c r="L115" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -4353,10 +4359,10 @@
         <v>110</v>
       </c>
       <c r="B116" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C116" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D116">
         <v>0.63</v>
@@ -4374,7 +4380,7 @@
         <v>17</v>
       </c>
       <c r="L116" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -4382,10 +4388,10 @@
         <v>76</v>
       </c>
       <c r="B117" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C117" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D117">
         <v>1.15</v>
@@ -4403,7 +4409,7 @@
         <v>17</v>
       </c>
       <c r="L117" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -4411,10 +4417,10 @@
         <v>108</v>
       </c>
       <c r="B118" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C118" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D118">
         <v>0.32</v>
@@ -4432,7 +4438,7 @@
         <v>17</v>
       </c>
       <c r="L118" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -4440,10 +4446,10 @@
         <v>111</v>
       </c>
       <c r="B119" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C119" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D119">
         <v>0.41</v>
@@ -4461,7 +4467,7 @@
         <v>17</v>
       </c>
       <c r="L119" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -4469,10 +4475,10 @@
         <v>112</v>
       </c>
       <c r="B120" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C120" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D120">
         <v>0.13</v>
@@ -4490,7 +4496,7 @@
         <v>17</v>
       </c>
       <c r="L120" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -4498,10 +4504,10 @@
         <v>35</v>
       </c>
       <c r="B121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C121" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D121">
         <v>0.13</v>
@@ -4519,7 +4525,7 @@
         <v>17</v>
       </c>
       <c r="L121" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -4527,10 +4533,10 @@
         <v>113</v>
       </c>
       <c r="B122" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C122" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D122">
         <v>0.27</v>
@@ -4548,7 +4554,7 @@
         <v>17</v>
       </c>
       <c r="L122" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -4556,10 +4562,10 @@
         <v>114</v>
       </c>
       <c r="B123" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C123" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D123">
         <v>0.22</v>
@@ -4577,7 +4583,7 @@
         <v>17</v>
       </c>
       <c r="L123" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -4585,10 +4591,10 @@
         <v>59</v>
       </c>
       <c r="B124" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C124" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D124">
         <v>0.11</v>
@@ -4606,7 +4612,7 @@
         <v>16</v>
       </c>
       <c r="L124" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -4614,10 +4620,10 @@
         <v>107</v>
       </c>
       <c r="B125" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C125" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D125">
         <v>0.23</v>
@@ -4635,7 +4641,7 @@
         <v>16</v>
       </c>
       <c r="L125" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -4643,10 +4649,10 @@
         <v>115</v>
       </c>
       <c r="B126" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C126" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D126">
         <v>0.38</v>
@@ -4664,7 +4670,7 @@
         <v>15</v>
       </c>
       <c r="L126" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -4672,10 +4678,10 @@
         <v>116</v>
       </c>
       <c r="B127" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C127" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D127">
         <v>0.23</v>
@@ -4693,7 +4699,7 @@
         <v>17</v>
       </c>
       <c r="L127" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -4701,10 +4707,10 @@
         <v>112</v>
       </c>
       <c r="B128" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C128" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D128">
         <v>0.07000000000000001</v>
@@ -4722,7 +4728,7 @@
         <v>7</v>
       </c>
       <c r="L128" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -4730,10 +4736,10 @@
         <v>75</v>
       </c>
       <c r="B129" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C129" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D129">
         <v>0.29</v>
@@ -4751,7 +4757,7 @@
         <v>7</v>
       </c>
       <c r="L129" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="130" spans="1:12">
@@ -4759,10 +4765,10 @@
         <v>113</v>
       </c>
       <c r="B130" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C130" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D130">
         <v>0.14</v>
@@ -4780,7 +4786,7 @@
         <v>7</v>
       </c>
       <c r="L130" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -4788,10 +4794,10 @@
         <v>114</v>
       </c>
       <c r="B131" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C131" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D131">
         <v>0.23</v>
@@ -4809,7 +4815,7 @@
         <v>7</v>
       </c>
       <c r="L131" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="132" spans="1:12">
@@ -4817,10 +4823,10 @@
         <v>117</v>
       </c>
       <c r="B132" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C132" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D132">
         <v>0.15</v>
@@ -4838,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="L132" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="133" spans="1:12">
@@ -4846,10 +4852,10 @@
         <v>77</v>
       </c>
       <c r="B133" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C133" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D133">
         <v>0.07000000000000001</v>
@@ -4867,7 +4873,7 @@
         <v>7</v>
       </c>
       <c r="L133" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="134" spans="1:12">
@@ -4875,10 +4881,10 @@
         <v>89</v>
       </c>
       <c r="B134" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C134" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D134">
         <v>0.13</v>
@@ -4896,7 +4902,7 @@
         <v>7</v>
       </c>
       <c r="L134" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="135" spans="1:12">
@@ -4904,10 +4910,10 @@
         <v>38</v>
       </c>
       <c r="B135" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C135" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D135">
         <v>0.2</v>
@@ -4925,7 +4931,7 @@
         <v>7</v>
       </c>
       <c r="L135" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="136" spans="1:12">
@@ -4933,10 +4939,10 @@
         <v>118</v>
       </c>
       <c r="B136" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C136" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D136">
         <v>0.17</v>
@@ -4954,7 +4960,7 @@
         <v>21</v>
       </c>
       <c r="L136" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="137" spans="1:12">
@@ -4962,10 +4968,10 @@
         <v>102</v>
       </c>
       <c r="B137" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C137" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D137">
         <v>0.13</v>
@@ -4983,7 +4989,7 @@
         <v>21</v>
       </c>
       <c r="L137" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="138" spans="1:12">
@@ -4991,10 +4997,10 @@
         <v>117</v>
       </c>
       <c r="B138" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C138" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D138">
         <v>0.42</v>
@@ -5012,7 +5018,7 @@
         <v>21</v>
       </c>
       <c r="L138" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="139" spans="1:12">
@@ -5020,10 +5026,10 @@
         <v>119</v>
       </c>
       <c r="B139" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C139" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D139">
         <v>0.76</v>
@@ -5041,7 +5047,7 @@
         <v>21</v>
       </c>
       <c r="L139" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="140" spans="1:12">
@@ -5049,10 +5055,10 @@
         <v>104</v>
       </c>
       <c r="B140" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C140" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D140">
         <v>0.57</v>
@@ -5070,7 +5076,7 @@
         <v>21</v>
       </c>
       <c r="L140" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="141" spans="1:12">
@@ -5078,10 +5084,10 @@
         <v>120</v>
       </c>
       <c r="B141" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C141" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D141">
         <v>0.38</v>
@@ -5099,7 +5105,7 @@
         <v>21</v>
       </c>
       <c r="L141" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="142" spans="1:12">
@@ -5107,10 +5113,10 @@
         <v>121</v>
       </c>
       <c r="B142" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C142" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D142">
         <v>0.07000000000000001</v>
@@ -5128,7 +5134,7 @@
         <v>23</v>
       </c>
       <c r="L142" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:12">
@@ -5136,10 +5142,10 @@
         <v>122</v>
       </c>
       <c r="B143" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C143" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D143">
         <v>0.11</v>
@@ -5157,7 +5163,7 @@
         <v>23</v>
       </c>
       <c r="L143" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="144" spans="1:12">
@@ -5165,10 +5171,10 @@
         <v>123</v>
       </c>
       <c r="B144" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C144" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D144">
         <v>0.14</v>
@@ -5186,7 +5192,7 @@
         <v>23</v>
       </c>
       <c r="L144" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="145" spans="1:12">
@@ -5194,10 +5200,10 @@
         <v>67</v>
       </c>
       <c r="B145" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C145" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D145">
         <v>2.26</v>
@@ -5215,7 +5221,7 @@
         <v>23</v>
       </c>
       <c r="L145" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="146" spans="1:12">
@@ -5223,10 +5229,10 @@
         <v>124</v>
       </c>
       <c r="B146" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C146" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D146">
         <v>0.22</v>
@@ -5244,7 +5250,7 @@
         <v>23</v>
       </c>
       <c r="L146" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="147" spans="1:12">
@@ -5252,10 +5258,10 @@
         <v>125</v>
       </c>
       <c r="B147" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C147" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D147">
         <v>0.13</v>
@@ -5273,7 +5279,7 @@
         <v>23</v>
       </c>
       <c r="L147" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="148" spans="1:12">
@@ -5281,10 +5287,10 @@
         <v>126</v>
       </c>
       <c r="B148" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C148" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D148">
         <v>0.09</v>
@@ -5302,7 +5308,7 @@
         <v>23</v>
       </c>
       <c r="L148" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="149" spans="1:12">
@@ -5310,10 +5316,10 @@
         <v>127</v>
       </c>
       <c r="B149" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C149" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D149">
         <v>0.09</v>
@@ -5331,7 +5337,7 @@
         <v>23</v>
       </c>
       <c r="L149" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="150" spans="1:12">
@@ -5339,10 +5345,10 @@
         <v>122</v>
       </c>
       <c r="B150" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C150" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D150">
         <v>0.06</v>
@@ -5360,7 +5366,7 @@
         <v>27</v>
       </c>
       <c r="L150" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="151" spans="1:12">
@@ -5368,10 +5374,10 @@
         <v>128</v>
       </c>
       <c r="B151" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C151" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D151">
         <v>0.11</v>
@@ -5389,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="L151" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="152" spans="1:12">
@@ -5397,10 +5403,10 @@
         <v>129</v>
       </c>
       <c r="B152" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C152" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D152">
         <v>0.08</v>
@@ -5418,7 +5424,7 @@
         <v>27</v>
       </c>
       <c r="L152" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="153" spans="1:12">
@@ -5426,10 +5432,10 @@
         <v>130</v>
       </c>
       <c r="B153" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C153" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D153">
         <v>0.11</v>
@@ -5447,7 +5453,7 @@
         <v>27</v>
       </c>
       <c r="L153" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="154" spans="1:12">
@@ -5455,10 +5461,10 @@
         <v>131</v>
       </c>
       <c r="B154" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C154" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D154">
         <v>0.08</v>
@@ -5476,7 +5482,7 @@
         <v>26</v>
       </c>
       <c r="L154" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="155" spans="1:12">
@@ -5484,10 +5490,10 @@
         <v>132</v>
       </c>
       <c r="B155" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C155" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D155">
         <v>0.5600000000000001</v>
@@ -5505,7 +5511,7 @@
         <v>27</v>
       </c>
       <c r="L155" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="156" spans="1:12">
@@ -5513,10 +5519,10 @@
         <v>133</v>
       </c>
       <c r="B156" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C156" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D156">
         <v>1.04</v>
@@ -5534,7 +5540,7 @@
         <v>27</v>
       </c>
       <c r="L156" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="157" spans="1:12">
@@ -5542,10 +5548,10 @@
         <v>134</v>
       </c>
       <c r="B157" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C157" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D157">
         <v>1.14</v>
@@ -5563,7 +5569,7 @@
         <v>27</v>
       </c>
       <c r="L157" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="158" spans="1:12">
@@ -5571,10 +5577,10 @@
         <v>106</v>
       </c>
       <c r="B158" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C158" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D158">
         <v>0.14</v>
@@ -5592,7 +5598,7 @@
         <v>7</v>
       </c>
       <c r="L158" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="159" spans="1:12">
@@ -5600,10 +5606,10 @@
         <v>132</v>
       </c>
       <c r="B159" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C159" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D159">
         <v>0.21</v>
@@ -5621,7 +5627,7 @@
         <v>7</v>
       </c>
       <c r="L159" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="160" spans="1:12">
@@ -5629,10 +5635,10 @@
         <v>135</v>
       </c>
       <c r="B160" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C160" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D160">
         <v>0.25</v>
@@ -5650,7 +5656,7 @@
         <v>7</v>
       </c>
       <c r="L160" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="161" spans="1:12">
@@ -5658,10 +5664,10 @@
         <v>136</v>
       </c>
       <c r="B161" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C161" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D161">
         <v>0.42</v>
@@ -5679,7 +5685,7 @@
         <v>7</v>
       </c>
       <c r="L161" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="162" spans="1:12">
@@ -5687,10 +5693,10 @@
         <v>99</v>
       </c>
       <c r="B162" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C162" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D162">
         <v>0.09</v>
@@ -5708,7 +5714,7 @@
         <v>17</v>
       </c>
       <c r="L162" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="163" spans="1:12">
@@ -5716,10 +5722,10 @@
         <v>137</v>
       </c>
       <c r="B163" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C163" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D163">
         <v>0.38</v>
@@ -5737,7 +5743,7 @@
         <v>18</v>
       </c>
       <c r="L163" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="164" spans="1:12">
@@ -5745,10 +5751,10 @@
         <v>138</v>
       </c>
       <c r="B164" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C164" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D164">
         <v>0.64</v>
@@ -5766,7 +5772,7 @@
         <v>17</v>
       </c>
       <c r="L164" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="165" spans="1:12">
@@ -5774,10 +5780,10 @@
         <v>124</v>
       </c>
       <c r="B165" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C165" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D165">
         <v>0.71</v>
@@ -5795,7 +5801,7 @@
         <v>19</v>
       </c>
       <c r="L165" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="166" spans="1:12">
@@ -5803,10 +5809,10 @@
         <v>70</v>
       </c>
       <c r="B166" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C166" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D166">
         <v>0.06</v>
@@ -5824,7 +5830,7 @@
         <v>21</v>
       </c>
       <c r="L166" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="167" spans="1:12">
@@ -5832,10 +5838,10 @@
         <v>128</v>
       </c>
       <c r="B167" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C167" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D167">
         <v>0.09</v>
@@ -5853,7 +5859,7 @@
         <v>21</v>
       </c>
       <c r="L167" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="168" spans="1:12">
@@ -5861,10 +5867,10 @@
         <v>71</v>
       </c>
       <c r="B168" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C168" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D168">
         <v>0.15</v>
@@ -5882,7 +5888,7 @@
         <v>13</v>
       </c>
       <c r="L168" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="169" spans="1:12">
@@ -5890,10 +5896,10 @@
         <v>139</v>
       </c>
       <c r="B169" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C169" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D169">
         <v>0.12</v>
@@ -5911,7 +5917,7 @@
         <v>13</v>
       </c>
       <c r="L169" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="170" spans="1:12">
@@ -5919,10 +5925,10 @@
         <v>140</v>
       </c>
       <c r="B170" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C170" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D170">
         <v>0.15</v>
@@ -5940,7 +5946,7 @@
         <v>13</v>
       </c>
       <c r="L170" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="171" spans="1:12">
@@ -5948,10 +5954,10 @@
         <v>130</v>
       </c>
       <c r="B171" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C171" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D171">
         <v>0.12</v>
@@ -5969,7 +5975,7 @@
         <v>14</v>
       </c>
       <c r="L171" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="172" spans="1:12">
@@ -5977,10 +5983,10 @@
         <v>84</v>
       </c>
       <c r="B172" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C172" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D172">
         <v>0.18</v>
@@ -5998,7 +6004,7 @@
         <v>15</v>
       </c>
       <c r="L172" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="173" spans="1:12">
@@ -6006,10 +6012,10 @@
         <v>137</v>
       </c>
       <c r="B173" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C173" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D173">
         <v>0.09</v>
@@ -6027,7 +6033,7 @@
         <v>19</v>
       </c>
       <c r="L173" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="174" spans="1:12">
@@ -6035,10 +6041,10 @@
         <v>139</v>
       </c>
       <c r="B174" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C174" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D174">
         <v>0.5</v>
@@ -6056,7 +6062,7 @@
         <v>17</v>
       </c>
       <c r="L174" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="175" spans="1:12">
@@ -6064,10 +6070,10 @@
         <v>141</v>
       </c>
       <c r="B175" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C175" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D175">
         <v>0.23</v>
@@ -6085,7 +6091,7 @@
         <v>17</v>
       </c>
       <c r="L175" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="176" spans="1:12">
@@ -6093,10 +6099,10 @@
         <v>142</v>
       </c>
       <c r="B176" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C176" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D176">
         <v>0.35</v>
@@ -6114,7 +6120,7 @@
         <v>17</v>
       </c>
       <c r="L176" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="177" spans="1:12">
@@ -6122,10 +6128,10 @@
         <v>143</v>
       </c>
       <c r="B177" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C177" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D177">
         <v>0.1</v>
@@ -6143,7 +6149,7 @@
         <v>17</v>
       </c>
       <c r="L177" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -6151,10 +6157,10 @@
         <v>139</v>
       </c>
       <c r="B178" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C178" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D178">
         <v>0.52</v>
@@ -6172,7 +6178,7 @@
         <v>17</v>
       </c>
       <c r="L178" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="179" spans="1:12">
@@ -6180,10 +6186,10 @@
         <v>141</v>
       </c>
       <c r="B179" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C179" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D179">
         <v>0.3</v>
@@ -6201,7 +6207,7 @@
         <v>17</v>
       </c>
       <c r="L179" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="180" spans="1:12">
@@ -6209,10 +6215,10 @@
         <v>142</v>
       </c>
       <c r="B180" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C180" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D180">
         <v>1.43</v>
@@ -6230,7 +6236,7 @@
         <v>17</v>
       </c>
       <c r="L180" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="181" spans="1:12">
@@ -6238,10 +6244,10 @@
         <v>143</v>
       </c>
       <c r="B181" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C181" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D181">
         <v>0.22</v>
@@ -6259,7 +6265,7 @@
         <v>21</v>
       </c>
       <c r="L181" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="182" spans="1:12">
@@ -6267,10 +6273,10 @@
         <v>144</v>
       </c>
       <c r="B182" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C182" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D182">
         <v>0.29</v>
@@ -6288,7 +6294,7 @@
         <v>21</v>
       </c>
       <c r="L182" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="183" spans="1:12">
@@ -6296,10 +6302,10 @@
         <v>46</v>
       </c>
       <c r="B183" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C183" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D183">
         <v>0.27</v>
@@ -6317,7 +6323,7 @@
         <v>21</v>
       </c>
       <c r="L183" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="184" spans="1:12">
@@ -6325,10 +6331,10 @@
         <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C184" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D184">
         <v>0.21</v>
@@ -6346,7 +6352,7 @@
         <v>21</v>
       </c>
       <c r="L184" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -6354,10 +6360,10 @@
         <v>123</v>
       </c>
       <c r="B185" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C185" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D185">
         <v>0.09</v>
@@ -6375,7 +6381,7 @@
         <v>4</v>
       </c>
       <c r="L185" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="186" spans="1:12">
@@ -6383,10 +6389,10 @@
         <v>100</v>
       </c>
       <c r="B186" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C186" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D186">
         <v>0.23</v>
@@ -6404,7 +6410,7 @@
         <v>4</v>
       </c>
       <c r="L186" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="187" spans="1:12">
@@ -6412,10 +6418,10 @@
         <v>130</v>
       </c>
       <c r="B187" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C187" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D187">
         <v>0.45</v>
@@ -6433,7 +6439,7 @@
         <v>4</v>
       </c>
       <c r="L187" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="188" spans="1:12">
@@ -6441,10 +6447,10 @@
         <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C188" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D188">
         <v>0.23</v>
@@ -6462,7 +6468,7 @@
         <v>5</v>
       </c>
       <c r="L188" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -6470,10 +6476,10 @@
         <v>133</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C189" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D189">
         <v>0.07000000000000001</v>
@@ -6491,7 +6497,7 @@
         <v>26</v>
       </c>
       <c r="L189" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -6499,10 +6505,10 @@
         <v>108</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C190" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D190">
         <v>0.19</v>
@@ -6520,7 +6526,7 @@
         <v>27</v>
       </c>
       <c r="L190" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -6528,10 +6534,10 @@
         <v>78</v>
       </c>
       <c r="B191" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C191" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D191">
         <v>0.21</v>
@@ -6549,7 +6555,7 @@
         <v>27</v>
       </c>
       <c r="L191" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -6557,10 +6563,10 @@
         <v>145</v>
       </c>
       <c r="B192" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C192" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D192">
         <v>0.15</v>
@@ -6578,7 +6584,7 @@
         <v>27</v>
       </c>
       <c r="L192" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -6586,10 +6592,10 @@
         <v>135</v>
       </c>
       <c r="B193" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C193" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D193">
         <v>0.03</v>
@@ -6607,7 +6613,7 @@
         <v>23</v>
       </c>
       <c r="L193" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -6615,10 +6621,10 @@
         <v>38</v>
       </c>
       <c r="B194" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C194" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D194">
         <v>0.07000000000000001</v>
@@ -6636,7 +6642,7 @@
         <v>23</v>
       </c>
       <c r="L194" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -6644,10 +6650,10 @@
         <v>61</v>
       </c>
       <c r="B195" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C195" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D195">
         <v>0.1</v>
@@ -6665,7 +6671,7 @@
         <v>23</v>
       </c>
       <c r="L195" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -6673,10 +6679,10 @@
         <v>146</v>
       </c>
       <c r="B196" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C196" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D196">
         <v>0.21</v>
@@ -6694,7 +6700,7 @@
         <v>23</v>
       </c>
       <c r="L196" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -6702,10 +6708,10 @@
         <v>147</v>
       </c>
       <c r="B197" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C197" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D197">
         <v>0.21</v>
@@ -6723,7 +6729,7 @@
         <v>23</v>
       </c>
       <c r="L197" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="198" spans="1:12">
@@ -6731,10 +6737,10 @@
         <v>148</v>
       </c>
       <c r="B198" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C198" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D198">
         <v>0.14</v>
@@ -6752,7 +6758,7 @@
         <v>23</v>
       </c>
       <c r="L198" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="199" spans="1:12">
@@ -6760,10 +6766,10 @@
         <v>140</v>
       </c>
       <c r="B199" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C199" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D199">
         <v>0.17</v>
@@ -6781,7 +6787,7 @@
         <v>13</v>
       </c>
       <c r="L199" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -6789,10 +6795,10 @@
         <v>130</v>
       </c>
       <c r="B200" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C200" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D200">
         <v>0.33</v>
@@ -6810,7 +6816,7 @@
         <v>13</v>
       </c>
       <c r="L200" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -6818,10 +6824,10 @@
         <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C201" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D201">
         <v>0.5</v>
@@ -6839,7 +6845,7 @@
         <v>13</v>
       </c>
       <c r="L201" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -6847,10 +6853,10 @@
         <v>134</v>
       </c>
       <c r="B202" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C202" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D202">
         <v>0.33</v>
@@ -6868,7 +6874,7 @@
         <v>13</v>
       </c>
       <c r="L202" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="203" spans="1:12">
@@ -6876,10 +6882,10 @@
         <v>38</v>
       </c>
       <c r="B203" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C203" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D203">
         <v>0.39</v>
@@ -6897,7 +6903,7 @@
         <v>17</v>
       </c>
       <c r="L203" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="204" spans="1:12">
@@ -6905,10 +6911,10 @@
         <v>61</v>
       </c>
       <c r="B204" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C204" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D204">
         <v>0.67</v>
@@ -6926,7 +6932,7 @@
         <v>19</v>
       </c>
       <c r="L204" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -6934,10 +6940,10 @@
         <v>120</v>
       </c>
       <c r="B205" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C205" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D205">
         <v>0.5600000000000001</v>
@@ -6955,7 +6961,7 @@
         <v>19</v>
       </c>
       <c r="L205" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="206" spans="1:12">
@@ -6963,10 +6969,10 @@
         <v>148</v>
       </c>
       <c r="B206" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C206" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D206">
         <v>0.39</v>
@@ -6984,7 +6990,7 @@
         <v>19</v>
       </c>
       <c r="L206" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="207" spans="1:12">
@@ -6992,10 +6998,10 @@
         <v>149</v>
       </c>
       <c r="B207" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C207" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D207">
         <v>0.28</v>
@@ -7013,7 +7019,7 @@
         <v>19</v>
       </c>
       <c r="L207" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -7021,10 +7027,10 @@
         <v>150</v>
       </c>
       <c r="B208" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C208" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D208">
         <v>0.28</v>
@@ -7042,7 +7048,7 @@
         <v>19</v>
       </c>
       <c r="L208" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -7050,10 +7056,10 @@
         <v>130</v>
       </c>
       <c r="B209" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C209" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D209">
         <v>0.09</v>
@@ -7071,7 +7077,7 @@
         <v>19</v>
       </c>
       <c r="L209" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -7079,10 +7085,10 @@
         <v>68</v>
       </c>
       <c r="B210" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C210" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D210">
         <v>0.18</v>
@@ -7100,7 +7106,7 @@
         <v>19</v>
       </c>
       <c r="L210" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -7108,10 +7114,10 @@
         <v>125</v>
       </c>
       <c r="B211" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C211" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D211">
         <v>0.27</v>
@@ -7129,7 +7135,7 @@
         <v>19</v>
       </c>
       <c r="L211" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -7137,10 +7143,10 @@
         <v>151</v>
       </c>
       <c r="B212" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C212" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D212">
         <v>0.18</v>
@@ -7158,7 +7164,7 @@
         <v>19</v>
       </c>
       <c r="L212" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -7166,10 +7172,10 @@
         <v>130</v>
       </c>
       <c r="B213" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C213" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D213">
         <v>0.15</v>
@@ -7187,7 +7193,7 @@
         <v>17</v>
       </c>
       <c r="L213" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -7195,10 +7201,10 @@
         <v>68</v>
       </c>
       <c r="B214" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C214" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D214">
         <v>0.25</v>
@@ -7216,7 +7222,7 @@
         <v>17</v>
       </c>
       <c r="L214" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -7224,10 +7230,10 @@
         <v>152</v>
       </c>
       <c r="B215" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C215" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D215">
         <v>0.45</v>
@@ -7245,7 +7251,7 @@
         <v>17</v>
       </c>
       <c r="L215" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -7253,10 +7259,10 @@
         <v>126</v>
       </c>
       <c r="B216" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C216" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D216">
         <v>0.35</v>
@@ -7274,7 +7280,7 @@
         <v>17</v>
       </c>
       <c r="L216" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="217" spans="1:12">
@@ -7282,10 +7288,10 @@
         <v>130</v>
       </c>
       <c r="B217" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C217" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D217">
         <v>0.15</v>
@@ -7303,7 +7309,7 @@
         <v>17</v>
       </c>
       <c r="L217" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -7311,10 +7317,10 @@
         <v>68</v>
       </c>
       <c r="B218" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C218" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D218">
         <v>0.25</v>
@@ -7332,7 +7338,7 @@
         <v>17</v>
       </c>
       <c r="L218" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="219" spans="1:12">
@@ -7340,10 +7346,10 @@
         <v>152</v>
       </c>
       <c r="B219" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C219" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D219">
         <v>0.45</v>
@@ -7361,7 +7367,7 @@
         <v>17</v>
       </c>
       <c r="L219" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="220" spans="1:12">
@@ -7369,10 +7375,10 @@
         <v>126</v>
       </c>
       <c r="B220" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C220" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D220">
         <v>0.35</v>
@@ -7390,7 +7396,7 @@
         <v>17</v>
       </c>
       <c r="L220" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="221" spans="1:12">
@@ -7398,10 +7404,10 @@
         <v>130</v>
       </c>
       <c r="B221" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C221" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D221">
         <v>0.15</v>
@@ -7419,7 +7425,7 @@
         <v>11</v>
       </c>
       <c r="L221" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="222" spans="1:12">
@@ -7427,10 +7433,10 @@
         <v>68</v>
       </c>
       <c r="B222" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C222" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D222">
         <v>0.24</v>
@@ -7448,7 +7454,7 @@
         <v>11</v>
       </c>
       <c r="L222" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="223" spans="1:12">
@@ -7456,10 +7462,10 @@
         <v>153</v>
       </c>
       <c r="B223" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C223" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D223">
         <v>0.33</v>
@@ -7477,7 +7483,7 @@
         <v>11</v>
       </c>
       <c r="L223" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="224" spans="1:12">
@@ -7485,10 +7491,10 @@
         <v>151</v>
       </c>
       <c r="B224" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C224" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D224">
         <v>0.24</v>
@@ -7506,7 +7512,7 @@
         <v>11</v>
       </c>
       <c r="L224" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="225" spans="1:12">
@@ -7514,10 +7520,10 @@
         <v>61</v>
       </c>
       <c r="B225" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C225" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D225">
         <v>0.14</v>
@@ -7535,7 +7541,7 @@
         <v>19</v>
       </c>
       <c r="L225" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="226" spans="1:12">
@@ -7543,10 +7549,10 @@
         <v>111</v>
       </c>
       <c r="B226" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C226" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D226">
         <v>0.23</v>
@@ -7564,7 +7570,7 @@
         <v>19</v>
       </c>
       <c r="L226" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="227" spans="1:12">
@@ -7572,10 +7578,10 @@
         <v>116</v>
       </c>
       <c r="B227" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C227" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D227">
         <v>0.36</v>
@@ -7593,7 +7599,7 @@
         <v>19</v>
       </c>
       <c r="L227" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="228" spans="1:12">
@@ -7601,10 +7607,10 @@
         <v>149</v>
       </c>
       <c r="B228" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C228" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D228">
         <v>0.27</v>
@@ -7622,7 +7628,7 @@
         <v>19</v>
       </c>
       <c r="L228" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="229" spans="1:12">
@@ -7630,10 +7636,10 @@
         <v>61</v>
       </c>
       <c r="B229" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C229" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D229">
         <v>0.12</v>
@@ -7651,7 +7657,7 @@
         <v>7</v>
       </c>
       <c r="L229" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="230" spans="1:12">
@@ -7659,10 +7665,10 @@
         <v>154</v>
       </c>
       <c r="B230" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C230" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D230">
         <v>0.22</v>
@@ -7680,7 +7686,7 @@
         <v>7</v>
       </c>
       <c r="L230" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="231" spans="1:12">
@@ -7688,10 +7694,10 @@
         <v>152</v>
       </c>
       <c r="B231" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C231" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D231">
         <v>0.3</v>
@@ -7709,7 +7715,7 @@
         <v>7</v>
       </c>
       <c r="L231" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="232" spans="1:12">
@@ -7717,10 +7723,10 @@
         <v>149</v>
       </c>
       <c r="B232" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C232" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D232">
         <v>0.12</v>
@@ -7738,7 +7744,7 @@
         <v>7</v>
       </c>
       <c r="L232" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="233" spans="1:12">
@@ -7746,10 +7752,10 @@
         <v>61</v>
       </c>
       <c r="B233" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C233" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D233">
         <v>0.24</v>
@@ -7767,7 +7773,7 @@
         <v>19</v>
       </c>
       <c r="L233" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="234" spans="1:12">
@@ -7775,10 +7781,10 @@
         <v>154</v>
       </c>
       <c r="B234" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C234" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D234">
         <v>0.29</v>
@@ -7796,7 +7802,7 @@
         <v>19</v>
       </c>
       <c r="L234" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="235" spans="1:12">
@@ -7804,10 +7810,10 @@
         <v>145</v>
       </c>
       <c r="B235" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C235" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D235">
         <v>0.17</v>
@@ -7825,7 +7831,7 @@
         <v>19</v>
       </c>
       <c r="L235" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="236" spans="1:12">
@@ -7833,10 +7839,10 @@
         <v>149</v>
       </c>
       <c r="B236" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C236" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D236">
         <v>0.14</v>
@@ -7854,7 +7860,7 @@
         <v>19</v>
       </c>
       <c r="L236" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="237" spans="1:12">
@@ -7862,10 +7868,10 @@
         <v>61</v>
       </c>
       <c r="B237" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C237" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D237">
         <v>0.11</v>
@@ -7883,7 +7889,7 @@
         <v>19</v>
       </c>
       <c r="L237" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="238" spans="1:12">
@@ -7891,10 +7897,10 @@
         <v>120</v>
       </c>
       <c r="B238" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C238" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D238">
         <v>0.58</v>
@@ -7912,7 +7918,7 @@
         <v>19</v>
       </c>
       <c r="L238" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="239" spans="1:12">
@@ -7920,10 +7926,10 @@
         <v>148</v>
       </c>
       <c r="B239" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C239" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D239">
         <v>0.47</v>
@@ -7941,7 +7947,7 @@
         <v>19</v>
       </c>
       <c r="L239" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="240" spans="1:12">
@@ -7949,10 +7955,10 @@
         <v>155</v>
       </c>
       <c r="B240" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C240" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D240">
         <v>0.32</v>
@@ -7970,7 +7976,7 @@
         <v>19</v>
       </c>
       <c r="L240" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="241" spans="1:12">
@@ -7978,10 +7984,10 @@
         <v>156</v>
       </c>
       <c r="B241" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C241" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D241">
         <v>3.29</v>
@@ -7999,7 +8005,7 @@
         <v>3</v>
       </c>
       <c r="L241" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="242" spans="1:12">
@@ -8007,10 +8013,10 @@
         <v>156</v>
       </c>
       <c r="B242" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C242" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D242">
         <v>0.2</v>
@@ -8028,7 +8034,7 @@
         <v>3</v>
       </c>
       <c r="L242" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="243" spans="1:12">
@@ -8036,10 +8042,10 @@
         <v>157</v>
       </c>
       <c r="B243" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C243" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D243">
         <v>0.76</v>
@@ -8057,7 +8063,7 @@
         <v>23</v>
       </c>
       <c r="L243" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="244" spans="1:12">
@@ -8065,28 +8071,57 @@
         <v>158</v>
       </c>
       <c r="B244" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C244" t="s">
-        <v>202</v>
-      </c>
-      <c r="D244" t="s">
-        <v>205</v>
-      </c>
-      <c r="E244" t="s">
-        <v>206</v>
-      </c>
-      <c r="F244" t="s">
+        <v>204</v>
+      </c>
+      <c r="D244">
+        <v>0.32</v>
+      </c>
+      <c r="E244">
+        <v>26.4</v>
+      </c>
+      <c r="F244">
+        <v>0</v>
+      </c>
+      <c r="G244">
+        <v>0</v>
+      </c>
+      <c r="K244">
+        <v>12</v>
+      </c>
+      <c r="L244" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12">
+      <c r="A245" t="s">
+        <v>159</v>
+      </c>
+      <c r="B245" t="s">
+        <v>200</v>
+      </c>
+      <c r="C245" t="s">
+        <v>203</v>
+      </c>
+      <c r="D245" t="s">
         <v>207</v>
       </c>
-      <c r="G244" t="s">
-        <v>207</v>
-      </c>
-      <c r="K244" t="s">
+      <c r="E245" t="s">
+        <v>208</v>
+      </c>
+      <c r="F245" t="s">
         <v>209</v>
       </c>
-      <c r="L244" t="s">
+      <c r="G245" t="s">
+        <v>209</v>
+      </c>
+      <c r="K245" t="s">
         <v>211</v>
+      </c>
+      <c r="L245" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/data/pest_disease_control.xlsx
+++ b/data/pest_disease_control.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="249">
   <si>
     <t>Date</t>
   </si>
@@ -57,432 +52,432 @@
     <t>Season</t>
   </si>
   <si>
+    <t>2023-10-10</t>
+  </si>
+  <si>
+    <t>2023-10-12</t>
+  </si>
+  <si>
+    <t>2023-10-18</t>
+  </si>
+  <si>
+    <t>2023-10-25</t>
+  </si>
+  <si>
+    <t>2023-10-4</t>
+  </si>
+  <si>
+    <t>2023-11-1</t>
+  </si>
+  <si>
+    <t>2023-11-21</t>
+  </si>
+  <si>
+    <t>2023-11-28</t>
+  </si>
+  <si>
+    <t>2023-12-1</t>
+  </si>
+  <si>
+    <t>2023-12-12</t>
+  </si>
+  <si>
+    <t>2023-12-19</t>
+  </si>
+  <si>
+    <t>2023-12-27</t>
+  </si>
+  <si>
+    <t>2023-8-15</t>
+  </si>
+  <si>
+    <t>2023-8-3</t>
+  </si>
+  <si>
+    <t>2023-9-12</t>
+  </si>
+  <si>
+    <t>2024-10-1</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>2024-10-11</t>
+  </si>
+  <si>
+    <t>2024-10-14</t>
+  </si>
+  <si>
+    <t>2024-10-16</t>
+  </si>
+  <si>
+    <t>2024-10-17</t>
+  </si>
+  <si>
+    <t>2024-10-18</t>
+  </si>
+  <si>
+    <t>2024-10-19</t>
+  </si>
+  <si>
+    <t>2024-10-2</t>
+  </si>
+  <si>
+    <t>2024-10-21</t>
+  </si>
+  <si>
+    <t>2024-10-22</t>
+  </si>
+  <si>
+    <t>2024-10-23</t>
+  </si>
+  <si>
+    <t>2024-10-24</t>
+  </si>
+  <si>
+    <t>2024-10-28</t>
+  </si>
+  <si>
+    <t>2024-10-29</t>
+  </si>
+  <si>
+    <t>2024-10-30</t>
+  </si>
+  <si>
+    <t>2024-10-31</t>
+  </si>
+  <si>
+    <t>2024-10-7</t>
+  </si>
+  <si>
+    <t>2024-10-8</t>
+  </si>
+  <si>
+    <t>2024-10-9</t>
+  </si>
+  <si>
+    <t>2024-11-1</t>
+  </si>
+  <si>
+    <t>2024-11-11</t>
+  </si>
+  <si>
+    <t>2024-11-113</t>
+  </si>
+  <si>
+    <t>2024-11-12</t>
+  </si>
+  <si>
+    <t>2024-11-13</t>
+  </si>
+  <si>
+    <t>2024-11-14</t>
+  </si>
+  <si>
+    <t>2024-11-15</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>2024-11-19</t>
+  </si>
+  <si>
+    <t>2024-11-20</t>
+  </si>
+  <si>
+    <t>2024-11-21</t>
+  </si>
+  <si>
+    <t>2024-11-22</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>2024-11-26</t>
+  </si>
+  <si>
+    <t>2024-11-27</t>
+  </si>
+  <si>
+    <t>2024-11-28</t>
+  </si>
+  <si>
+    <t>2024-11-4</t>
+  </si>
+  <si>
+    <t>2024-11-5</t>
+  </si>
+  <si>
+    <t>2024-11-6</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>2024-12-11</t>
+  </si>
+  <si>
+    <t>2024-12-16</t>
+  </si>
+  <si>
+    <t>2024-12-17</t>
+  </si>
+  <si>
+    <t>2024-12-2</t>
+  </si>
+  <si>
+    <t>2024-12-23</t>
+  </si>
+  <si>
+    <t>2024-12-24</t>
+  </si>
+  <si>
+    <t>2024-12-3</t>
+  </si>
+  <si>
+    <t>2024-12-30</t>
+  </si>
+  <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
+    <t>2024-12-9</t>
+  </si>
+  <si>
+    <t>2024-1-8</t>
+  </si>
+  <si>
+    <t>2024-2-6</t>
+  </si>
+  <si>
+    <t>2024-6-10</t>
+  </si>
+  <si>
+    <t>2024-6-11</t>
+  </si>
+  <si>
+    <t>2024-6-18</t>
+  </si>
+  <si>
+    <t>2024-6-19</t>
+  </si>
+  <si>
+    <t>2024-6-24</t>
+  </si>
+  <si>
+    <t>2024-6-25</t>
+  </si>
+  <si>
+    <t>2024-6-26</t>
+  </si>
+  <si>
+    <t>2024-6-3</t>
+  </si>
+  <si>
+    <t>2024-7-11</t>
+  </si>
+  <si>
+    <t>2024-7-15</t>
+  </si>
+  <si>
+    <t>2024-7-16</t>
+  </si>
+  <si>
+    <t>2024-7-17</t>
+  </si>
+  <si>
+    <t>2024-7-2</t>
+  </si>
+  <si>
+    <t>2024-7-22</t>
+  </si>
+  <si>
+    <t>2024-7-23</t>
+  </si>
+  <si>
+    <t>2024-7-24</t>
+  </si>
+  <si>
+    <t>2024-7-25</t>
+  </si>
+  <si>
+    <t>2024-7-30</t>
+  </si>
+  <si>
+    <t>2024-7-31</t>
+  </si>
+  <si>
+    <t>2024-7-9</t>
+  </si>
+  <si>
+    <t>2024-8-12</t>
+  </si>
+  <si>
+    <t>2024-8-13</t>
+  </si>
+  <si>
+    <t>2024-8-14</t>
+  </si>
+  <si>
+    <t>2024-8-19</t>
+  </si>
+  <si>
+    <t>2024-8-20</t>
+  </si>
+  <si>
+    <t>2024-8-21</t>
+  </si>
+  <si>
+    <t>2024-8-22</t>
+  </si>
+  <si>
+    <t>2024-8-23</t>
+  </si>
+  <si>
+    <t>2024-8-24</t>
+  </si>
+  <si>
+    <t>2024-8-26</t>
+  </si>
+  <si>
+    <t>2024-8-27</t>
+  </si>
+  <si>
+    <t>2024-8-28</t>
+  </si>
+  <si>
+    <t>2024-8-5</t>
+  </si>
+  <si>
+    <t>2024-8-6</t>
+  </si>
+  <si>
+    <t>2024-8-7</t>
+  </si>
+  <si>
+    <t>2024-9-10</t>
+  </si>
+  <si>
+    <t>2024-9-11</t>
+  </si>
+  <si>
+    <t>2024-9-12</t>
+  </si>
+  <si>
+    <t>2024-9-13</t>
+  </si>
+  <si>
+    <t>2024-9-14</t>
+  </si>
+  <si>
+    <t>2024-9-16</t>
+  </si>
+  <si>
+    <t>2024-9-17</t>
+  </si>
+  <si>
+    <t>2024-9-18</t>
+  </si>
+  <si>
+    <t>2024-9-19</t>
+  </si>
+  <si>
+    <t>2024-9-2</t>
+  </si>
+  <si>
+    <t>2024-9-20</t>
+  </si>
+  <si>
+    <t>2024-9-23</t>
+  </si>
+  <si>
+    <t>2024-9-25</t>
+  </si>
+  <si>
+    <t>2024-9-26</t>
+  </si>
+  <si>
+    <t>2024-9-29</t>
+  </si>
+  <si>
+    <t>2024-9-3</t>
+  </si>
+  <si>
+    <t>2024-9-30</t>
+  </si>
+  <si>
+    <t>2024-9-9</t>
+  </si>
+  <si>
+    <t>2025-1-13</t>
+  </si>
+  <si>
+    <t>2025-1-14</t>
+  </si>
+  <si>
+    <t>2025-1-2</t>
+  </si>
+  <si>
+    <t>2025-1-20</t>
+  </si>
+  <si>
+    <t>2025-1-21</t>
+  </si>
+  <si>
+    <t>2025-1-22</t>
+  </si>
+  <si>
+    <t>2025-1-27</t>
+  </si>
+  <si>
+    <t>2025-1-28</t>
+  </si>
+  <si>
+    <t>2025-1-29</t>
+  </si>
+  <si>
+    <t>2025-1-3</t>
+  </si>
+  <si>
+    <t>2025-1-6</t>
+  </si>
+  <si>
     <t>2025-1-7</t>
   </si>
   <si>
-    <t>2023-8-3</t>
-  </si>
-  <si>
-    <t>2023-8-15</t>
-  </si>
-  <si>
-    <t>2023-9-12</t>
-  </si>
-  <si>
-    <t>2023-10-10</t>
-  </si>
-  <si>
-    <t>2023-10-18</t>
-  </si>
-  <si>
-    <t>2023-11-1</t>
-  </si>
-  <si>
-    <t>2023-11-28</t>
-  </si>
-  <si>
-    <t>2023-12-27</t>
-  </si>
-  <si>
-    <t>2023-12-1</t>
-  </si>
-  <si>
-    <t>2023-12-12</t>
-  </si>
-  <si>
-    <t>2024-1-8</t>
-  </si>
-  <si>
-    <t>2024-2-6</t>
-  </si>
-  <si>
-    <t>2023-10-4</t>
-  </si>
-  <si>
-    <t>2023-10-12</t>
-  </si>
-  <si>
-    <t>2023-10-25</t>
-  </si>
-  <si>
-    <t>2023-11-21</t>
-  </si>
-  <si>
-    <t>2023-12-19</t>
-  </si>
-  <si>
-    <t>2024-6-3</t>
-  </si>
-  <si>
-    <t>2024-6-18</t>
-  </si>
-  <si>
-    <t>2024-7-16</t>
-  </si>
-  <si>
-    <t>2024-8-12</t>
-  </si>
-  <si>
-    <t>2024-9-10</t>
-  </si>
-  <si>
-    <t>2024-10-8</t>
-  </si>
-  <si>
-    <t>2024-11-4</t>
-  </si>
-  <si>
-    <t>2024-12-3</t>
-  </si>
-  <si>
-    <t>2024-6-11</t>
-  </si>
-  <si>
-    <t>2024-6-24</t>
-  </si>
-  <si>
-    <t>2024-7-23</t>
-  </si>
-  <si>
-    <t>2024-8-21</t>
-  </si>
-  <si>
-    <t>2024-9-20</t>
-  </si>
-  <si>
-    <t>2024-10-14</t>
-  </si>
-  <si>
-    <t>2024-11-14</t>
-  </si>
-  <si>
-    <t>2024-12-11</t>
-  </si>
-  <si>
-    <t>2024-6-10</t>
-  </si>
-  <si>
-    <t>2024-6-25</t>
-  </si>
-  <si>
-    <t>2024-7-22</t>
-  </si>
-  <si>
-    <t>2024-8-19</t>
-  </si>
-  <si>
-    <t>2024-9-17</t>
-  </si>
-  <si>
-    <t>2024-10-16</t>
-  </si>
-  <si>
-    <t>2024-11-13</t>
-  </si>
-  <si>
-    <t>2024-6-19</t>
-  </si>
-  <si>
-    <t>2024-7-2</t>
-  </si>
-  <si>
-    <t>2024-9-29</t>
-  </si>
-  <si>
-    <t>2024-8-26</t>
-  </si>
-  <si>
-    <t>2024-7-24</t>
-  </si>
-  <si>
-    <t>2024-10-21</t>
-  </si>
-  <si>
-    <t>2024-11-22</t>
-  </si>
-  <si>
-    <t>2024-12-16</t>
-  </si>
-  <si>
-    <t>2024-6-26</t>
-  </si>
-  <si>
-    <t>2024-7-9</t>
-  </si>
-  <si>
-    <t>2024-8-7</t>
-  </si>
-  <si>
-    <t>2024-9-3</t>
-  </si>
-  <si>
-    <t>2024-10-28</t>
-  </si>
-  <si>
-    <t>2024-11-25</t>
-  </si>
-  <si>
-    <t>2024-12-23</t>
-  </si>
-  <si>
-    <t>2024-8-6</t>
-  </si>
-  <si>
-    <t>2024-10-2</t>
-  </si>
-  <si>
-    <t>2024-11-1</t>
-  </si>
-  <si>
-    <t>2024-11-28</t>
-  </si>
-  <si>
-    <t>2024-7-17</t>
-  </si>
-  <si>
-    <t>2024-8-14</t>
-  </si>
-  <si>
-    <t>2024-9-9</t>
-  </si>
-  <si>
-    <t>2024-10-10</t>
-  </si>
-  <si>
-    <t>2024-11-6</t>
-  </si>
-  <si>
-    <t>2025-1-2</t>
-  </si>
-  <si>
-    <t>2024-7-11</t>
-  </si>
-  <si>
-    <t>2024-8-20</t>
-  </si>
-  <si>
-    <t>2024-9-16</t>
-  </si>
-  <si>
-    <t>2024-10-19</t>
-  </si>
-  <si>
-    <t>2024-11-15</t>
-  </si>
-  <si>
     <t>2025-1-8</t>
   </si>
   <si>
-    <t>2024-7-15</t>
-  </si>
-  <si>
-    <t>2024-7-30</t>
-  </si>
-  <si>
-    <t>2024-8-28</t>
-  </si>
-  <si>
-    <t>2024-9-23</t>
-  </si>
-  <si>
-    <t>2024-11-20</t>
-  </si>
-  <si>
-    <t>2024-7-25</t>
-  </si>
-  <si>
-    <t>2024-8-5</t>
-  </si>
-  <si>
-    <t>2024-9-2</t>
-  </si>
-  <si>
-    <t>2024-9-30</t>
-  </si>
-  <si>
-    <t>2024-7-31</t>
-  </si>
-  <si>
-    <t>2024-8-13</t>
-  </si>
-  <si>
-    <t>2024-9-12</t>
-  </si>
-  <si>
-    <t>2024-8-22</t>
-  </si>
-  <si>
-    <t>2024-9-18</t>
-  </si>
-  <si>
-    <t>2024-10-18</t>
-  </si>
-  <si>
-    <t>2024-11-11</t>
-  </si>
-  <si>
-    <t>2024-8-23</t>
-  </si>
-  <si>
-    <t>2024-9-26</t>
-  </si>
-  <si>
-    <t>2024-10-24</t>
-  </si>
-  <si>
-    <t>2024-12-17</t>
-  </si>
-  <si>
-    <t>2024-9-13</t>
-  </si>
-  <si>
-    <t>2024-10-9</t>
-  </si>
-  <si>
-    <t>2024-11-5</t>
-  </si>
-  <si>
-    <t>2024-12-2</t>
-  </si>
-  <si>
-    <t>2024-8-24</t>
-  </si>
-  <si>
-    <t>2024-9-14</t>
-  </si>
-  <si>
-    <t>2024-12-30</t>
-  </si>
-  <si>
-    <t>2024-8-27</t>
-  </si>
-  <si>
-    <t>2024-9-25</t>
-  </si>
-  <si>
-    <t>2024-10-7</t>
-  </si>
-  <si>
-    <t>2025-1-13</t>
-  </si>
-  <si>
-    <t>2025-1-28</t>
-  </si>
-  <si>
-    <t>2024-10-22</t>
-  </si>
-  <si>
-    <t>2024-9-11</t>
-  </si>
-  <si>
-    <t>2024-11-21</t>
-  </si>
-  <si>
-    <t>2025-1-14</t>
-  </si>
-  <si>
-    <t>2024-9-19</t>
-  </si>
-  <si>
-    <t>2024-10-1</t>
-  </si>
-  <si>
-    <t>2024-10-31</t>
-  </si>
-  <si>
-    <t>2024-12-24</t>
-  </si>
-  <si>
-    <t>2025-1-21</t>
+    <t>2025-2-12</t>
+  </si>
+  <si>
+    <t>2025-2-13</t>
+  </si>
+  <si>
+    <t>2025-2-17</t>
   </si>
   <si>
     <t>2025-2-18</t>
   </si>
   <si>
+    <t>2025-2-25</t>
+  </si>
+  <si>
+    <t>2025-2-4</t>
+  </si>
+  <si>
     <t>2025-3-20</t>
   </si>
   <si>
-    <t>2024-10-17</t>
-  </si>
-  <si>
-    <t>2024-11-16</t>
-  </si>
-  <si>
-    <t>2024-12-10</t>
-  </si>
-  <si>
-    <t>2024-10-11</t>
-  </si>
-  <si>
-    <t>2024-10-23</t>
-  </si>
-  <si>
-    <t>2024-11-18</t>
-  </si>
-  <si>
-    <t>2025-2-4</t>
-  </si>
-  <si>
-    <t>2024-11-19</t>
-  </si>
-  <si>
-    <t>2025-2-13</t>
-  </si>
-  <si>
-    <t>2024-10-29</t>
-  </si>
-  <si>
-    <t>2024-11-27</t>
-  </si>
-  <si>
-    <t>2024-11-12</t>
-  </si>
-  <si>
-    <t>2024-11-26</t>
-  </si>
-  <si>
-    <t>2024-12-9</t>
-  </si>
-  <si>
-    <t>2025-1-6</t>
-  </si>
-  <si>
-    <t>2024-10-30</t>
-  </si>
-  <si>
-    <t>2024-11-113</t>
-  </si>
-  <si>
-    <t>2025-1-27</t>
-  </si>
-  <si>
-    <t>2025-1-3</t>
-  </si>
-  <si>
-    <t>2025-1-29</t>
-  </si>
-  <si>
-    <t>2025-2-12</t>
-  </si>
-  <si>
-    <t>2025-2-25</t>
-  </si>
-  <si>
     <t>2025-3-24</t>
   </si>
   <si>
-    <t>2025-2-17</t>
-  </si>
-  <si>
-    <t>2025-1-20</t>
-  </si>
-  <si>
-    <t>2025-1-22</t>
-  </si>
-  <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
     <t>2025-3-28</t>
   </si>
   <si>
@@ -495,126 +490,213 @@
     <t>2025-07-01</t>
   </si>
   <si>
+    <t>2025-07-23</t>
+  </si>
+  <si>
+    <t>2025-07-25</t>
+  </si>
+  <si>
     <t>2025-08-12</t>
   </si>
   <si>
+    <t>2025-08-18</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
     <t>2025-08-27</t>
   </si>
   <si>
     <t>2025-09-10</t>
   </si>
   <si>
+    <t>2025-09-18</t>
+  </si>
+  <si>
     <t>2025-09-22</t>
   </si>
   <si>
     <t>2025-10-08</t>
   </si>
   <si>
-    <t>2025-07-23</t>
-  </si>
-  <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
     <t>2025-10-18</t>
   </si>
   <si>
-    <t>2025-07-25</t>
-  </si>
-  <si>
-    <t>2025-08-19</t>
-  </si>
-  <si>
-    <t>2025-09-18</t>
+    <t>2025-07-24</t>
+  </si>
+  <si>
+    <t>2025-10-15</t>
+  </si>
+  <si>
+    <t>2025-07-14</t>
+  </si>
+  <si>
+    <t>2025-08-11</t>
+  </si>
+  <si>
+    <t>2025-09-09</t>
+  </si>
+  <si>
+    <t>2025-10-07</t>
+  </si>
+  <si>
+    <t>2025-07-09</t>
+  </si>
+  <si>
+    <t>2025-07-22</t>
+  </si>
+  <si>
+    <t>2025-08-20</t>
+  </si>
+  <si>
+    <t>2025-09-17</t>
+  </si>
+  <si>
+    <t>2025-07-21</t>
+  </si>
+  <si>
+    <t>2025-08-05</t>
+  </si>
+  <si>
+    <t>2025-09-01</t>
+  </si>
+  <si>
+    <t>2025-09-29</t>
+  </si>
+  <si>
+    <t>2025-07-28</t>
+  </si>
+  <si>
+    <t>2025-08-13</t>
+  </si>
+  <si>
+    <t>2025-10-06</t>
+  </si>
+  <si>
+    <t>2025-08-04</t>
+  </si>
+  <si>
+    <t>2025-09-19</t>
+  </si>
+  <si>
+    <t>2025-08-25</t>
+  </si>
+  <si>
+    <t>2025-08-26</t>
+  </si>
+  <si>
+    <t>2025-09-24</t>
+  </si>
+  <si>
+    <t>2025-09-23</t>
+  </si>
+  <si>
+    <t>2025-09-02</t>
+  </si>
+  <si>
+    <t>2025-09-30</t>
+  </si>
+  <si>
+    <t>2025-09-08</t>
+  </si>
+  <si>
+    <t>2025-08-28</t>
+  </si>
+  <si>
+    <t>2025-09-03</t>
+  </si>
+  <si>
+    <t>2025-10-02</t>
+  </si>
+  <si>
+    <t>DG01000</t>
+  </si>
+  <si>
+    <t>DG04000</t>
+  </si>
+  <si>
+    <t>DG02000</t>
   </si>
   <si>
     <t>DG03000</t>
   </si>
   <si>
-    <t>DG01000</t>
-  </si>
-  <si>
-    <t>DG02000</t>
-  </si>
-  <si>
-    <t>DG04000</t>
+    <t>DG07000</t>
+  </si>
+  <si>
+    <t>DG09000</t>
+  </si>
+  <si>
+    <t>DG37000</t>
+  </si>
+  <si>
+    <t>DG25000</t>
+  </si>
+  <si>
+    <t>DG24000</t>
+  </si>
+  <si>
+    <t>DG11000</t>
+  </si>
+  <si>
+    <t>DG31000</t>
+  </si>
+  <si>
+    <t>DG20000</t>
+  </si>
+  <si>
+    <t>DG06000</t>
+  </si>
+  <si>
+    <t>DG10000</t>
+  </si>
+  <si>
+    <t>DG22000</t>
+  </si>
+  <si>
+    <t>DG32000</t>
+  </si>
+  <si>
+    <t>DG34000</t>
+  </si>
+  <si>
+    <t>DG18000</t>
+  </si>
+  <si>
+    <t>DG35000</t>
+  </si>
+  <si>
+    <t>DG13000</t>
+  </si>
+  <si>
+    <t>DG16000</t>
+  </si>
+  <si>
+    <t>DG08000</t>
+  </si>
+  <si>
+    <t>DG12000</t>
+  </si>
+  <si>
+    <t>DG14000</t>
+  </si>
+  <si>
+    <t>DG15000</t>
+  </si>
+  <si>
+    <t>DG38000</t>
   </si>
   <si>
     <t>DG27000</t>
   </si>
   <si>
-    <t>DG11000</t>
-  </si>
-  <si>
-    <t>DG31000</t>
-  </si>
-  <si>
-    <t>DG32000</t>
-  </si>
-  <si>
-    <t>DG16000</t>
-  </si>
-  <si>
-    <t>DG37000</t>
-  </si>
-  <si>
-    <t>DG22000</t>
-  </si>
-  <si>
-    <t>DG08000</t>
-  </si>
-  <si>
     <t>DG29000</t>
   </si>
   <si>
-    <t>DG06000</t>
-  </si>
-  <si>
-    <t>DG13000</t>
-  </si>
-  <si>
     <t>DG33000</t>
   </si>
   <si>
-    <t>DG25000</t>
-  </si>
-  <si>
-    <t>DG34000</t>
-  </si>
-  <si>
-    <t>DG18000</t>
-  </si>
-  <si>
-    <t>DG07000</t>
-  </si>
-  <si>
-    <t>DG09000</t>
-  </si>
-  <si>
-    <t>DG24000</t>
-  </si>
-  <si>
-    <t>DG35000</t>
-  </si>
-  <si>
-    <t>DG10000</t>
-  </si>
-  <si>
-    <t>DG20000</t>
-  </si>
-  <si>
-    <t>DG12000</t>
-  </si>
-  <si>
-    <t>DG14000</t>
-  </si>
-  <si>
-    <t>DG15000</t>
-  </si>
-  <si>
-    <t>DG38000</t>
-  </si>
-  <si>
     <t>DG26000</t>
   </si>
   <si>
@@ -624,15 +706,15 @@
     <t>DG36000</t>
   </si>
   <si>
+    <t>DG05000</t>
+  </si>
+  <si>
+    <t>DG21000</t>
+  </si>
+  <si>
     <t>DG17000</t>
   </si>
   <si>
-    <t>DG05000</t>
-  </si>
-  <si>
-    <t>DG21000</t>
-  </si>
-  <si>
     <t>DG23000</t>
   </si>
   <si>
@@ -645,34 +727,34 @@
     <t>DG19000</t>
   </si>
   <si>
+    <t>MIX</t>
+  </si>
+  <si>
+    <t>N41</t>
+  </si>
+  <si>
+    <t>R579</t>
+  </si>
+  <si>
     <t>R570</t>
   </si>
   <si>
-    <t>MIX</t>
-  </si>
-  <si>
-    <t>R579</t>
-  </si>
-  <si>
-    <t>N41</t>
+    <t>97F1692</t>
   </si>
   <si>
     <t>MN1</t>
   </si>
   <si>
-    <t>97F1692</t>
-  </si>
-  <si>
-    <t>0.6</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>10.87</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>3</t>
+    <t>12</t>
   </si>
   <si>
     <t>2024/25</t>
@@ -684,8 +766,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -748,14 +830,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -802,7 +876,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -834,10 +908,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -869,7 +942,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1045,14 +1117,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L253"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:L301"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1090,15 +1159,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="C2" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D2">
         <v>1.32</v>
@@ -1122,18 +1191,18 @@
         <v>10</v>
       </c>
       <c r="L2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C3" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D3">
         <v>0.47</v>
@@ -1157,18 +1226,18 @@
         <v>7</v>
       </c>
       <c r="L3" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C4" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D4">
         <v>0.06</v>
@@ -1192,18 +1261,18 @@
         <v>6</v>
       </c>
       <c r="L4" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C5" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D5">
         <v>0.32</v>
@@ -1227,18 +1296,18 @@
         <v>7</v>
       </c>
       <c r="L5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D6">
         <v>0.6</v>
@@ -1262,18 +1331,18 @@
         <v>8</v>
       </c>
       <c r="L6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C7" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D7">
         <v>0.16</v>
@@ -1297,18 +1366,18 @@
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C8" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D8">
         <v>0.47</v>
@@ -1332,21 +1401,21 @@
         <v>8</v>
       </c>
       <c r="L8" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C9" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D9">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="E9">
         <v>47.5</v>
@@ -1367,18 +1436,18 @@
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="C10" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D10">
         <v>0.16</v>
@@ -1402,18 +1471,18 @@
         <v>6</v>
       </c>
       <c r="L10" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="C11" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D11">
         <v>0.5</v>
@@ -1437,18 +1506,18 @@
         <v>7</v>
       </c>
       <c r="L11" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C12" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D12">
         <v>0.2</v>
@@ -1472,18 +1541,18 @@
         <v>8</v>
       </c>
       <c r="L12" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C13" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D13">
         <v>0.6</v>
@@ -1507,18 +1576,18 @@
         <v>7</v>
       </c>
       <c r="L13" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="C14" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D14">
         <v>1.07</v>
@@ -1542,18 +1611,18 @@
         <v>11</v>
       </c>
       <c r="L14" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="C15" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D15">
         <v>0.43</v>
@@ -1577,18 +1646,18 @@
         <v>9</v>
       </c>
       <c r="L15" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="C16" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D16">
         <v>1.05</v>
@@ -1612,18 +1681,18 @@
         <v>10</v>
       </c>
       <c r="L16" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C17" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D17">
         <v>0.11</v>
@@ -1647,18 +1716,18 @@
         <v>23</v>
       </c>
       <c r="L17" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="C18" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D18">
         <v>0.06</v>
@@ -1682,21 +1751,21 @@
         <v>27</v>
       </c>
       <c r="L18" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C19" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D19">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E19">
         <v>25</v>
@@ -1717,21 +1786,21 @@
         <v>7</v>
       </c>
       <c r="L19" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C20" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D20">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="E20">
         <v>63.75</v>
@@ -1752,18 +1821,18 @@
         <v>17</v>
       </c>
       <c r="L20" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C21" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D21">
         <v>0.08</v>
@@ -1787,18 +1856,18 @@
         <v>26</v>
       </c>
       <c r="L21" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="C22" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="D22">
         <v>0.45</v>
@@ -1822,18 +1891,18 @@
         <v>23</v>
       </c>
       <c r="L22" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="C23" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D23">
         <v>0.38</v>
@@ -1857,18 +1926,18 @@
         <v>18</v>
       </c>
       <c r="L23" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="C24" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D24">
         <v>0.11</v>
@@ -1892,18 +1961,18 @@
         <v>27</v>
       </c>
       <c r="L24" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C25" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D25">
         <v>0.09</v>
@@ -1927,18 +1996,18 @@
         <v>21</v>
       </c>
       <c r="L25" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="C26" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D26">
         <v>0.17</v>
@@ -1962,18 +2031,18 @@
         <v>13</v>
       </c>
       <c r="L26" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="C27" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D27">
         <v>0.09</v>
@@ -1997,21 +2066,21 @@
         <v>17</v>
       </c>
       <c r="L27" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="C28" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D28">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E28">
         <v>53.75</v>
@@ -2032,21 +2101,21 @@
         <v>14</v>
       </c>
       <c r="L28" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C29" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D29">
-        <v>0.94</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E29">
         <v>65</v>
@@ -2067,18 +2136,18 @@
         <v>12</v>
       </c>
       <c r="L29" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C30" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D30">
         <v>0.06</v>
@@ -2102,21 +2171,21 @@
         <v>21</v>
       </c>
       <c r="L30" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C31" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D31">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="E31">
         <v>46.25</v>
@@ -2137,18 +2206,18 @@
         <v>19</v>
       </c>
       <c r="L31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C32" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D32">
         <v>0.11</v>
@@ -2172,18 +2241,18 @@
         <v>16</v>
       </c>
       <c r="L32" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C33" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D33">
         <v>0.15</v>
@@ -2207,18 +2276,18 @@
         <v>7</v>
       </c>
       <c r="L33" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="C34" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D34">
         <v>0.42</v>
@@ -2242,21 +2311,21 @@
         <v>21</v>
       </c>
       <c r="L34" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>131</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C35" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D35">
-        <v>0.56000000000000005</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E35">
         <v>63.75</v>
@@ -2277,18 +2346,18 @@
         <v>27</v>
       </c>
       <c r="L35" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C36" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D36">
         <v>0.21</v>
@@ -2312,18 +2381,18 @@
         <v>7</v>
       </c>
       <c r="L36" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="C37" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D37">
         <v>0.24</v>
@@ -2347,18 +2416,18 @@
         <v>16</v>
       </c>
       <c r="L37" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>65</v>
-      </c>
-      <c r="B38" t="s">
-        <v>177</v>
-      </c>
       <c r="C38" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D38">
         <v>0.17</v>
@@ -2382,18 +2451,18 @@
         <v>4</v>
       </c>
       <c r="L38" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="C39" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D39">
         <v>1.62</v>
@@ -2417,18 +2486,18 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="C40" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D40">
         <v>0.38</v>
@@ -2452,18 +2521,18 @@
         <v>18</v>
       </c>
       <c r="L40" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="C41" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D41">
         <v>0.09</v>
@@ -2487,18 +2556,18 @@
         <v>19</v>
       </c>
       <c r="L41" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="C42" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D42">
         <v>0.1</v>
@@ -2522,18 +2591,18 @@
         <v>17</v>
       </c>
       <c r="L42" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C43" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D43">
         <v>0.22</v>
@@ -2557,21 +2626,21 @@
         <v>21</v>
       </c>
       <c r="L43" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C44" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D44">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E44">
         <v>65</v>
@@ -2592,18 +2661,18 @@
         <v>23</v>
       </c>
       <c r="L44" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="C45" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D45">
         <v>0.09</v>
@@ -2627,18 +2696,18 @@
         <v>4</v>
       </c>
       <c r="L45" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C46" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D46">
         <v>0.22</v>
@@ -2662,18 +2731,18 @@
         <v>17</v>
       </c>
       <c r="L46" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C47" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D47">
         <v>0.23</v>
@@ -2697,21 +2766,21 @@
         <v>7</v>
       </c>
       <c r="L47" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C48" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D48">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="E48">
         <v>42.5</v>
@@ -2732,18 +2801,18 @@
         <v>11</v>
       </c>
       <c r="L48" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="C49" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D49">
         <v>0.15</v>
@@ -2767,21 +2836,21 @@
         <v>9</v>
       </c>
       <c r="L49" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C50" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D50">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E50">
         <v>90</v>
@@ -2802,21 +2871,21 @@
         <v>23</v>
       </c>
       <c r="L50" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C51" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D51">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E51">
         <v>2.5</v>
@@ -2837,18 +2906,18 @@
         <v>7</v>
       </c>
       <c r="L51" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C52" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D52">
         <v>0.71</v>
@@ -2872,18 +2941,18 @@
         <v>12</v>
       </c>
       <c r="L52" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C53" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D53">
         <v>0.15</v>
@@ -2907,21 +2976,21 @@
         <v>13</v>
       </c>
       <c r="L53" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="C54" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D54">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="E54">
         <v>41.67</v>
@@ -2930,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>2.2200000000000002</v>
+        <v>2.22</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -2942,18 +3011,18 @@
         <v>14</v>
       </c>
       <c r="L54" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="C55" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D55">
         <v>0.23</v>
@@ -2977,21 +3046,21 @@
         <v>4</v>
       </c>
       <c r="L55" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>143</v>
+        <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C56" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D56">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="E56">
         <v>27.65</v>
@@ -3012,18 +3081,18 @@
         <v>21</v>
       </c>
       <c r="L56" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="B57" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C57" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D57">
         <v>0.12</v>
@@ -3047,18 +3116,18 @@
         <v>13</v>
       </c>
       <c r="L57" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="C58" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D58">
         <v>0.5</v>
@@ -3082,18 +3151,18 @@
         <v>17</v>
       </c>
       <c r="L58" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="B59" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="C59" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D59">
         <v>0.52</v>
@@ -3117,21 +3186,21 @@
         <v>17</v>
       </c>
       <c r="L59" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B60" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="C60" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D60">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="E60">
         <v>53.6</v>
@@ -3152,21 +3221,21 @@
         <v>19</v>
       </c>
       <c r="L60" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B61" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="C61" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="D61">
-        <v>0.55000000000000004</v>
+        <v>0.55</v>
       </c>
       <c r="E61">
         <v>20.34</v>
@@ -3187,18 +3256,18 @@
         <v>23</v>
       </c>
       <c r="L61" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="B62" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="C62" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D62">
         <v>0.26</v>
@@ -3222,18 +3291,18 @@
         <v>14</v>
       </c>
       <c r="L62" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="B63" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="C63" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D63">
         <v>0.08</v>
@@ -3257,18 +3326,18 @@
         <v>27</v>
       </c>
       <c r="L63" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="B64" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C64" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D64">
         <v>1.04</v>
@@ -3292,21 +3361,21 @@
         <v>27</v>
       </c>
       <c r="L64" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>132</v>
+        <v>55</v>
       </c>
       <c r="B65" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="C65" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D65">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E65">
         <v>49.63</v>
@@ -3327,18 +3396,18 @@
         <v>26</v>
       </c>
       <c r="L65" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="B66" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C66" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D66">
         <v>0.25</v>
@@ -3362,18 +3431,18 @@
         <v>7</v>
       </c>
       <c r="L66" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="B67" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C67" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D67">
         <v>0.03</v>
@@ -3397,18 +3466,18 @@
         <v>23</v>
       </c>
       <c r="L67" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="B68" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="C68" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D68">
         <v>1.47</v>
@@ -3432,18 +3501,18 @@
         <v>17</v>
       </c>
       <c r="L68" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="B69" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C69" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D69">
         <v>0.13</v>
@@ -3467,18 +3536,18 @@
         <v>7</v>
       </c>
       <c r="L69" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="B70" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="C70" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D70">
         <v>0.76</v>
@@ -3502,18 +3571,18 @@
         <v>21</v>
       </c>
       <c r="L70" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71" t="s">
         <v>59</v>
       </c>
       <c r="B71" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C71" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D71">
         <v>0.2</v>
@@ -3537,18 +3606,18 @@
         <v>19</v>
       </c>
       <c r="L71" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12">
       <c r="A72" t="s">
         <v>59</v>
       </c>
       <c r="B72" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="C72" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D72">
         <v>2.19</v>
@@ -3572,18 +3641,18 @@
         <v>17</v>
       </c>
       <c r="L72" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12">
+      <c r="A73" t="s">
+        <v>60</v>
+      </c>
+      <c r="B73" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>66</v>
-      </c>
-      <c r="B73" t="s">
-        <v>177</v>
-      </c>
       <c r="C73" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D73">
         <v>0.2</v>
@@ -3607,21 +3676,21 @@
         <v>4</v>
       </c>
       <c r="L73" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B74" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C74" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D74">
-        <v>2.2599999999999998</v>
+        <v>2.26</v>
       </c>
       <c r="E74">
         <v>26.09</v>
@@ -3642,18 +3711,18 @@
         <v>23</v>
       </c>
       <c r="L74" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="B75" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C75" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D75">
         <v>0.15</v>
@@ -3677,18 +3746,18 @@
         <v>13</v>
       </c>
       <c r="L75" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="B76" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D76">
         <v>0.17</v>
@@ -3712,18 +3781,18 @@
         <v>13</v>
       </c>
       <c r="L76" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="B77" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="C77" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D77">
         <v>0.64</v>
@@ -3747,18 +3816,18 @@
         <v>17</v>
       </c>
       <c r="L77" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C78" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D78">
         <v>0.45</v>
@@ -3782,18 +3851,18 @@
         <v>12</v>
       </c>
       <c r="L78" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B79" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="C79" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D79">
         <v>0.64</v>
@@ -3805,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="G79">
-        <v>8.64</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -3817,21 +3886,21 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="B80" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C80" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D80">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="E80">
         <v>83.33</v>
@@ -3852,24 +3921,24 @@
         <v>11</v>
       </c>
       <c r="L80" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="B81" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="C81" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D81">
         <v>0.31</v>
       </c>
       <c r="E81">
-        <v>39.229999999999997</v>
+        <v>39.23</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -3887,21 +3956,21 @@
         <v>9</v>
       </c>
       <c r="L81" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="B82" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C82" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D82">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E82">
         <v>39.64</v>
@@ -3922,18 +3991,18 @@
         <v>21</v>
       </c>
       <c r="L82" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="B83" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C83" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D83">
         <v>0.23</v>
@@ -3957,24 +4026,24 @@
         <v>16</v>
       </c>
       <c r="L83" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B84" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C84" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D84">
         <v>0.21</v>
       </c>
       <c r="E84">
-        <v>85.71</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -3992,21 +4061,21 @@
         <v>8</v>
       </c>
       <c r="L84" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B85" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C85" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D85">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E85">
         <v>31.33</v>
@@ -4027,24 +4096,24 @@
         <v>7</v>
       </c>
       <c r="L85" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="B86" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="C86" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D86">
         <v>0.11</v>
       </c>
       <c r="E86">
-        <v>34.549999999999997</v>
+        <v>34.55</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -4062,18 +4131,18 @@
         <v>27</v>
       </c>
       <c r="L86" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="B87" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C87" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D87">
         <v>0.12</v>
@@ -4097,18 +4166,18 @@
         <v>14</v>
       </c>
       <c r="L87" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="B88" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="C88" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D88">
         <v>0.45</v>
@@ -4132,18 +4201,18 @@
         <v>4</v>
       </c>
       <c r="L88" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="B89" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="C89" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D89">
         <v>0.33</v>
@@ -4167,18 +4236,18 @@
         <v>13</v>
       </c>
       <c r="L89" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="B90" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="C90" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D90">
         <v>0.09</v>
@@ -4202,18 +4271,18 @@
         <v>19</v>
       </c>
       <c r="L90" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="B91" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="C91" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D91">
         <v>0.15</v>
@@ -4237,18 +4306,18 @@
         <v>17</v>
       </c>
       <c r="L91" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="C92" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D92">
         <v>0.15</v>
@@ -4272,18 +4341,18 @@
         <v>17</v>
       </c>
       <c r="L92" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="B93" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="C93" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D93">
         <v>0.15</v>
@@ -4307,18 +4376,18 @@
         <v>11</v>
       </c>
       <c r="L93" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="B94" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="C94" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="D94">
         <v>0.43</v>
@@ -4342,18 +4411,18 @@
         <v>23</v>
       </c>
       <c r="L94" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="C95" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D95">
         <v>0.19</v>
@@ -4377,18 +4446,18 @@
         <v>14</v>
       </c>
       <c r="L95" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="B96" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="C96" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D96">
         <v>0.17</v>
@@ -4400,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="G96">
-        <v>4.4400000000000004</v>
+        <v>4.44</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -4412,18 +4481,18 @@
         <v>13</v>
       </c>
       <c r="L96" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="B97" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C97" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D97">
         <v>0.27</v>
@@ -4447,30 +4516,30 @@
         <v>21</v>
       </c>
       <c r="L97" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C98" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D98">
         <v>0.08</v>
       </c>
       <c r="E98">
-        <v>68.400000000000006</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F98">
         <v>0</v>
       </c>
       <c r="G98">
-        <v>8.8000000000000007</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -4482,18 +4551,18 @@
         <v>18</v>
       </c>
       <c r="L98" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B99" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C99" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D99">
         <v>0.1</v>
@@ -4517,18 +4586,18 @@
         <v>23</v>
       </c>
       <c r="L99" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B100" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="C100" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D100">
         <v>0.67</v>
@@ -4552,21 +4621,21 @@
         <v>19</v>
       </c>
       <c r="L100" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B101" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="C101" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D101">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E101">
         <v>5.45</v>
@@ -4587,18 +4656,18 @@
         <v>19</v>
       </c>
       <c r="L101" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B102" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="C102" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D102">
         <v>0.12</v>
@@ -4622,18 +4691,18 @@
         <v>7</v>
       </c>
       <c r="L102" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B103" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="C103" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D103">
         <v>0.24</v>
@@ -4657,24 +4726,24 @@
         <v>19</v>
       </c>
       <c r="L103" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B104" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="C104" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D104">
         <v>0.11</v>
       </c>
       <c r="E104">
-        <v>9.4700000000000006</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="F104">
         <v>3.5</v>
@@ -4692,18 +4761,18 @@
         <v>19</v>
       </c>
       <c r="L104" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
       <c r="A105" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B105" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="C105" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D105">
         <v>0.12</v>
@@ -4727,21 +4796,21 @@
         <v>17</v>
       </c>
       <c r="L105" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B106" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="C106" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D106">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="E106">
         <v>31.9</v>
@@ -4762,21 +4831,21 @@
         <v>21</v>
       </c>
       <c r="L106" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="B107" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C107" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D107">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E107">
         <v>20.71</v>
@@ -4797,18 +4866,18 @@
         <v>19</v>
       </c>
       <c r="L107" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="B108" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C108" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D108">
         <v>0.32</v>
@@ -4832,18 +4901,18 @@
         <v>17</v>
       </c>
       <c r="L108" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="B109" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="C109" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D109">
         <v>0.19</v>
@@ -4867,18 +4936,18 @@
         <v>27</v>
       </c>
       <c r="L109" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="A110" t="s">
+        <v>72</v>
+      </c>
+      <c r="B110" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>67</v>
-      </c>
-      <c r="B110" t="s">
-        <v>177</v>
-      </c>
       <c r="C110" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D110">
         <v>0.1</v>
@@ -4902,18 +4971,18 @@
         <v>4</v>
       </c>
       <c r="L110" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B111" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C111" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D111">
         <v>0.17</v>
@@ -4937,18 +5006,18 @@
         <v>13</v>
       </c>
       <c r="L111" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B112" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="C112" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D112">
         <v>0.18</v>
@@ -4972,18 +5041,18 @@
         <v>19</v>
       </c>
       <c r="L112" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B113" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="C113" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D113">
         <v>0.25</v>
@@ -5007,18 +5076,18 @@
         <v>17</v>
       </c>
       <c r="L113" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B114" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="C114" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D114">
         <v>0.25</v>
@@ -5042,18 +5111,18 @@
         <v>17</v>
       </c>
       <c r="L114" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B115" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="C115" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D115">
         <v>0.24</v>
@@ -5077,18 +5146,18 @@
         <v>11</v>
       </c>
       <c r="L115" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="B116" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C116" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D116">
         <v>0.22</v>
@@ -5100,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="G116">
-        <v>8.6999999999999993</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H116">
         <v>0</v>
@@ -5112,18 +5181,18 @@
         <v>23</v>
       </c>
       <c r="L116" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="B117" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="C117" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D117">
         <v>0.71</v>
@@ -5147,18 +5216,18 @@
         <v>19</v>
       </c>
       <c r="L117" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B118" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C118" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D118">
         <v>0.11</v>
@@ -5182,18 +5251,18 @@
         <v>11</v>
       </c>
       <c r="L118" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B119" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C119" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D119">
         <v>0.21</v>
@@ -5217,18 +5286,18 @@
         <v>8</v>
       </c>
       <c r="L119" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B120" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="C120" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D120">
         <v>0.23</v>
@@ -5252,18 +5321,18 @@
         <v>8</v>
       </c>
       <c r="L120" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B121" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C121" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D121">
         <v>0.2</v>
@@ -5287,21 +5356,21 @@
         <v>7</v>
       </c>
       <c r="L121" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B122" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C122" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D122">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E122">
         <v>52.86</v>
@@ -5322,18 +5391,18 @@
         <v>23</v>
       </c>
       <c r="L122" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="B123" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="C123" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D123">
         <v>0.39</v>
@@ -5357,18 +5426,18 @@
         <v>17</v>
       </c>
       <c r="L123" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="B124" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C124" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D124">
         <v>0.41</v>
@@ -5392,18 +5461,18 @@
         <v>17</v>
       </c>
       <c r="L124" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="B125" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="C125" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D125">
         <v>0.23</v>
@@ -5427,18 +5496,18 @@
         <v>19</v>
       </c>
       <c r="L125" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="B126" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="C126" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D126">
         <v>0.22</v>
@@ -5450,7 +5519,7 @@
         <v>2.5</v>
       </c>
       <c r="G126">
-        <v>1.1100000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="H126">
         <v>0</v>
@@ -5462,21 +5531,21 @@
         <v>7</v>
       </c>
       <c r="L126" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="B127" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="C127" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D127">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="E127">
         <v>29.29</v>
@@ -5497,18 +5566,18 @@
         <v>19</v>
       </c>
       <c r="L127" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="B128" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="C128" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D128">
         <v>0.23</v>
@@ -5532,18 +5601,18 @@
         <v>17</v>
       </c>
       <c r="L128" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12">
       <c r="A129" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="B129" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="C129" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D129">
         <v>0.3</v>
@@ -5567,18 +5636,18 @@
         <v>17</v>
       </c>
       <c r="L129" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12">
       <c r="A130" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="B130" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="C130" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D130">
         <v>0.2</v>
@@ -5602,18 +5671,18 @@
         <v>7</v>
       </c>
       <c r="L130" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12">
       <c r="A131" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="B131" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="C131" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D131">
         <v>0.15</v>
@@ -5637,18 +5706,18 @@
         <v>7</v>
       </c>
       <c r="L131" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12">
       <c r="A132" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="B132" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="C132" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D132">
         <v>0.08</v>
@@ -5672,18 +5741,18 @@
         <v>18</v>
       </c>
       <c r="L132" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12">
       <c r="A133" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="B133" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="C133" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="D133">
         <v>0.4</v>
@@ -5707,18 +5776,18 @@
         <v>23</v>
       </c>
       <c r="L133" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12">
       <c r="A134" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="B134" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C134" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D134">
         <v>0.43</v>
@@ -5742,18 +5811,18 @@
         <v>11</v>
       </c>
       <c r="L134" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12">
       <c r="A135" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="B135" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C135" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D135">
         <v>0.26</v>
@@ -5777,21 +5846,21 @@
         <v>17</v>
       </c>
       <c r="L135" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12">
       <c r="A136" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
       <c r="B136" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="C136" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="D136">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="E136">
         <v>52.5</v>
@@ -5812,18 +5881,18 @@
         <v>23</v>
       </c>
       <c r="L136" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12">
       <c r="A137" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="B137" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="C137" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D137">
         <v>0.52</v>
@@ -5847,18 +5916,18 @@
         <v>18</v>
       </c>
       <c r="L137" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12">
+      <c r="A138" t="s">
+        <v>86</v>
+      </c>
+      <c r="B138" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>61</v>
-      </c>
-      <c r="B138" t="s">
-        <v>177</v>
-      </c>
       <c r="C138" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D138">
         <v>0.16</v>
@@ -5882,18 +5951,18 @@
         <v>3</v>
       </c>
       <c r="L138" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12">
       <c r="A139" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B139" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C139" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D139">
         <v>1.28</v>
@@ -5917,18 +5986,18 @@
         <v>11</v>
       </c>
       <c r="L139" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12">
       <c r="A140" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="B140" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C140" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D140">
         <v>0.33</v>
@@ -5952,21 +6021,21 @@
         <v>11</v>
       </c>
       <c r="L140" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12">
       <c r="A141" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B141" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="C141" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D141">
-        <v>0.56999999999999995</v>
+        <v>0.57</v>
       </c>
       <c r="E141">
         <v>21.25</v>
@@ -5987,18 +6056,18 @@
         <v>13</v>
       </c>
       <c r="L141" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12">
       <c r="A142" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B142" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="C142" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D142">
         <v>0.95</v>
@@ -6022,18 +6091,18 @@
         <v>16</v>
       </c>
       <c r="L142" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12">
       <c r="A143" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="B143" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C143" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D143">
         <v>0.67</v>
@@ -6057,18 +6126,18 @@
         <v>11</v>
       </c>
       <c r="L143" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12">
       <c r="A144" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B144" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C144" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D144">
         <v>0.12</v>
@@ -6092,18 +6161,18 @@
         <v>9</v>
       </c>
       <c r="L144" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12">
       <c r="A145" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="B145" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C145" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D145">
         <v>0.49</v>
@@ -6127,18 +6196,18 @@
         <v>18</v>
       </c>
       <c r="L145" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12">
       <c r="A146" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="B146" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="C146" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D146">
         <v>0.83</v>
@@ -6162,18 +6231,18 @@
         <v>19</v>
       </c>
       <c r="L146" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12">
       <c r="A147" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="B147" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="C147" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="D147">
         <v>0.64</v>
@@ -6197,18 +6266,18 @@
         <v>23</v>
       </c>
       <c r="L147" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12">
       <c r="A148" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="B148" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C148" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D148">
         <v>0.4</v>
@@ -6232,18 +6301,18 @@
         <v>18</v>
       </c>
       <c r="L148" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12">
       <c r="A149" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="B149" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="C149" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D149">
         <v>1.02</v>
@@ -6267,21 +6336,21 @@
         <v>13</v>
       </c>
       <c r="L149" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12">
       <c r="A150" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B150" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="C150" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D150">
-        <v>0.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -6302,18 +6371,18 @@
         <v>13</v>
       </c>
       <c r="L150" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12">
       <c r="A151" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B151" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="C151" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D151">
         <v>1.36</v>
@@ -6337,21 +6406,21 @@
         <v>17</v>
       </c>
       <c r="L151" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12">
       <c r="A152" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B152" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="C152" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D152">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E152">
         <v>3.75</v>
@@ -6372,18 +6441,18 @@
         <v>9</v>
       </c>
       <c r="L152" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12">
+      <c r="A153" t="s">
+        <v>99</v>
+      </c>
+      <c r="B153" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>62</v>
-      </c>
-      <c r="B153" t="s">
-        <v>177</v>
-      </c>
       <c r="C153" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D153">
         <v>0.08</v>
@@ -6407,18 +6476,18 @@
         <v>4</v>
       </c>
       <c r="L153" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12">
       <c r="A154" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="B154" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C154" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D154">
         <v>0.77</v>
@@ -6442,18 +6511,18 @@
         <v>11</v>
       </c>
       <c r="L154" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12">
       <c r="A155" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="B155" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C155" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D155">
         <v>0.76</v>
@@ -6477,21 +6546,21 @@
         <v>10</v>
       </c>
       <c r="L155" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12">
       <c r="A156" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B156" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="C156" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D156">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E156">
         <v>41.25</v>
@@ -6512,18 +6581,18 @@
         <v>9</v>
       </c>
       <c r="L156" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12">
       <c r="A157" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="B157" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C157" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D157">
         <v>0.05</v>
@@ -6547,18 +6616,18 @@
         <v>7</v>
       </c>
       <c r="L157" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12">
       <c r="A158" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="B158" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="C158" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D158">
         <v>0.83</v>
@@ -6582,18 +6651,18 @@
         <v>18</v>
       </c>
       <c r="L158" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12">
       <c r="A159" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="B159" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="C159" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D159">
         <v>1.31</v>
@@ -6617,18 +6686,18 @@
         <v>14</v>
       </c>
       <c r="L159" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12">
       <c r="A160" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="B160" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="C160" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="D160">
         <v>0.68</v>
@@ -6652,18 +6721,18 @@
         <v>23</v>
       </c>
       <c r="L160" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12">
       <c r="A161" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B161" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="C161" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D161">
         <v>0.18</v>
@@ -6687,18 +6756,18 @@
         <v>13</v>
       </c>
       <c r="L161" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12">
       <c r="A162" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B162" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="C162" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D162">
         <v>0.38</v>
@@ -6722,21 +6791,21 @@
         <v>17</v>
       </c>
       <c r="L162" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12">
       <c r="A163" t="s">
         <v>108</v>
       </c>
       <c r="B163" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C163" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D163">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E163">
         <v>8.75</v>
@@ -6757,18 +6826,18 @@
         <v>17</v>
       </c>
       <c r="L163" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12">
       <c r="A164" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="B164" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C164" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D164">
         <v>1.03</v>
@@ -6792,18 +6861,18 @@
         <v>19</v>
       </c>
       <c r="L164" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12">
       <c r="A165" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B165" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C165" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D165">
         <v>0.13</v>
@@ -6827,21 +6896,21 @@
         <v>17</v>
       </c>
       <c r="L165" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12">
       <c r="A166" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B166" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C166" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D166">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E166">
         <v>12.5</v>
@@ -6862,18 +6931,18 @@
         <v>7</v>
       </c>
       <c r="L166" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12">
       <c r="A167" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="B167" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="C167" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D167">
         <v>1.73</v>
@@ -6897,18 +6966,18 @@
         <v>17</v>
       </c>
       <c r="L167" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12">
       <c r="A168" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="B168" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C168" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D168">
         <v>0.75</v>
@@ -6932,18 +7001,18 @@
         <v>19</v>
       </c>
       <c r="L168" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12">
       <c r="A169" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="B169" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="C169" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D169">
         <v>0.89</v>
@@ -6967,18 +7036,18 @@
         <v>13</v>
       </c>
       <c r="L169" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12">
       <c r="A170" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="B170" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C170" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D170">
         <v>1.22</v>
@@ -7002,18 +7071,18 @@
         <v>12</v>
       </c>
       <c r="L170" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12">
+      <c r="A171" t="s">
+        <v>114</v>
+      </c>
+      <c r="B171" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>63</v>
-      </c>
-      <c r="B171" t="s">
-        <v>177</v>
-      </c>
       <c r="C171" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D171">
         <v>0.16</v>
@@ -7037,18 +7106,18 @@
         <v>4</v>
       </c>
       <c r="L171" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12">
       <c r="A172" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="B172" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C172" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D172">
         <v>0.52</v>
@@ -7072,18 +7141,18 @@
         <v>11</v>
       </c>
       <c r="L172" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12">
       <c r="A173" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="B173" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C173" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D173">
         <v>0.13</v>
@@ -7107,18 +7176,18 @@
         <v>17</v>
       </c>
       <c r="L173" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12">
       <c r="A174" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B174" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="C174" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D174">
         <v>0.17</v>
@@ -7142,21 +7211,21 @@
         <v>21</v>
       </c>
       <c r="L174" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12">
       <c r="A175" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="B175" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="C175" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D175">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="E175">
         <v>30</v>
@@ -7177,18 +7246,18 @@
         <v>9</v>
       </c>
       <c r="L175" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12">
       <c r="A176" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="B176" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="C176" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D176">
         <v>0.75</v>
@@ -7212,18 +7281,18 @@
         <v>21</v>
       </c>
       <c r="L176" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12">
       <c r="A177" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B177" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C177" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D177">
         <v>0.63</v>
@@ -7247,18 +7316,18 @@
         <v>17</v>
       </c>
       <c r="L177" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12">
       <c r="A178" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="B178" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="C178" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D178">
         <v>0.95</v>
@@ -7282,21 +7351,21 @@
         <v>14</v>
       </c>
       <c r="L178" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12">
       <c r="A179" t="s">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="B179" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="C179" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D179">
-        <v>0.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E179">
         <v>97.5</v>
@@ -7317,18 +7386,18 @@
         <v>18</v>
       </c>
       <c r="L179" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12">
       <c r="A180" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B180" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="C180" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D180">
         <v>0.27</v>
@@ -7352,21 +7421,21 @@
         <v>13</v>
       </c>
       <c r="L180" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12">
       <c r="A181" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B181" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C181" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D181">
-        <v>7.0000000000000007E-2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E181">
         <v>12.5</v>
@@ -7387,18 +7456,18 @@
         <v>23</v>
       </c>
       <c r="L181" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12">
       <c r="A182" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="B182" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="C182" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D182">
         <v>1.66</v>
@@ -7422,18 +7491,18 @@
         <v>13</v>
       </c>
       <c r="L182" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12">
       <c r="A183" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="B183" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="C183" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="D183">
         <v>0.49</v>
@@ -7457,18 +7526,18 @@
         <v>23</v>
       </c>
       <c r="L183" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12">
       <c r="A184" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="B184" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="C184" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="D184">
         <v>0.49</v>
@@ -7492,18 +7561,18 @@
         <v>23</v>
       </c>
       <c r="L184" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12">
       <c r="A185" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="B185" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="C185" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D185">
         <v>1.73</v>
@@ -7527,18 +7596,18 @@
         <v>17</v>
       </c>
       <c r="L185" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12">
       <c r="A186" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C186" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D186">
         <v>0.27</v>
@@ -7562,21 +7631,21 @@
         <v>17</v>
       </c>
       <c r="L186" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12">
       <c r="A187" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="B187" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C187" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D187">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E187">
         <v>27.5</v>
@@ -7597,18 +7666,18 @@
         <v>7</v>
       </c>
       <c r="L187" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12">
       <c r="A188" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="B188" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="C188" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D188">
         <v>0.15</v>
@@ -7632,18 +7701,18 @@
         <v>16</v>
       </c>
       <c r="L188" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12">
       <c r="A189" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="B189" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="C189" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D189">
         <v>0.13</v>
@@ -7667,18 +7736,18 @@
         <v>21</v>
       </c>
       <c r="L189" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12">
       <c r="A190" t="s">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="B190" t="s">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="C190" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D190">
         <v>0.89</v>
@@ -7702,18 +7771,18 @@
         <v>18</v>
       </c>
       <c r="L190" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12">
+      <c r="A191" t="s">
+        <v>130</v>
+      </c>
+      <c r="B191" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>64</v>
-      </c>
-      <c r="B191" t="s">
-        <v>177</v>
-      </c>
       <c r="C191" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D191">
         <v>0.25</v>
@@ -7737,18 +7806,18 @@
         <v>4</v>
       </c>
       <c r="L191" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12">
       <c r="A192" t="s">
-        <v>64</v>
+        <v>130</v>
       </c>
       <c r="B192" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="C192" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D192">
         <v>0.91</v>
@@ -7772,18 +7841,18 @@
         <v>11</v>
       </c>
       <c r="L192" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12">
       <c r="A193" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="B193" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="C193" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D193">
         <v>2.38</v>
@@ -7807,18 +7876,18 @@
         <v>15</v>
       </c>
       <c r="L193" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12">
       <c r="A194" t="s">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="B194" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C194" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D194">
         <v>0.18</v>
@@ -7842,21 +7911,21 @@
         <v>7</v>
       </c>
       <c r="L194" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12">
       <c r="A195" t="s">
-        <v>74</v>
+        <v>132</v>
       </c>
       <c r="B195" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="C195" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D195">
-        <v>0.28999999999999998</v>
+        <v>0.29</v>
       </c>
       <c r="E195">
         <v>20</v>
@@ -7877,18 +7946,18 @@
         <v>7</v>
       </c>
       <c r="L195" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12">
       <c r="A196" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B196" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C196" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D196">
         <v>0.38</v>
@@ -7912,18 +7981,18 @@
         <v>15</v>
       </c>
       <c r="L196" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12">
       <c r="A197" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B197" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="C197" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D197">
         <v>0.38</v>
@@ -7947,21 +8016,21 @@
         <v>21</v>
       </c>
       <c r="L197" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12">
       <c r="A198" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B198" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="C198" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D198">
-        <v>0.56000000000000005</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E198">
         <v>32.22</v>
@@ -7982,21 +8051,21 @@
         <v>19</v>
       </c>
       <c r="L198" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12">
       <c r="A199" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B199" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="C199" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D199">
-        <v>0.57999999999999996</v>
+        <v>0.58</v>
       </c>
       <c r="E199">
         <v>22.11</v>
@@ -8017,21 +8086,21 @@
         <v>19</v>
       </c>
       <c r="L199" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12">
       <c r="A200" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="B200" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="C200" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D200">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E200">
         <v>3.57</v>
@@ -8052,18 +8121,18 @@
         <v>5</v>
       </c>
       <c r="L200" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12">
       <c r="A201" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="B201" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="C201" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D201">
         <v>0.21</v>
@@ -8087,18 +8156,18 @@
         <v>27</v>
       </c>
       <c r="L201" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12">
       <c r="A202" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B202" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="C202" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D202">
         <v>0.45</v>
@@ -8122,18 +8191,18 @@
         <v>17</v>
       </c>
       <c r="L202" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12">
       <c r="A203" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="C203" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D203">
         <v>0.45</v>
@@ -8157,18 +8226,18 @@
         <v>17</v>
       </c>
       <c r="L203" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12">
       <c r="A204" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B204" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="C204" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D204">
         <v>0.3</v>
@@ -8192,18 +8261,18 @@
         <v>7</v>
       </c>
       <c r="L204" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12">
       <c r="A205" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="B205" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C205" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D205">
         <v>0.13</v>
@@ -8227,24 +8296,24 @@
         <v>23</v>
       </c>
       <c r="L205" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12">
       <c r="A206" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="B206" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="C206" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D206">
         <v>0.27</v>
       </c>
       <c r="E206">
-        <v>88.18</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="F206">
         <v>0</v>
@@ -8262,24 +8331,24 @@
         <v>19</v>
       </c>
       <c r="L206" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12">
       <c r="A207" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="B207" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="C207" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D207">
         <v>0.33</v>
       </c>
       <c r="E207">
-        <v>71.430000000000007</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="F207">
         <v>0</v>
@@ -8297,18 +8366,18 @@
         <v>11</v>
       </c>
       <c r="L207" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12">
       <c r="A208" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B208" t="s">
-        <v>198</v>
+        <v>227</v>
       </c>
       <c r="C208" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D208">
         <v>0.15</v>
@@ -8332,18 +8401,18 @@
         <v>27</v>
       </c>
       <c r="L208" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12">
       <c r="A209" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B209" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="C209" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D209">
         <v>0.17</v>
@@ -8367,18 +8436,18 @@
         <v>19</v>
       </c>
       <c r="L209" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12">
       <c r="A210" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="B210" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="C210" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D210">
         <v>0.23</v>
@@ -8402,18 +8471,18 @@
         <v>17</v>
       </c>
       <c r="L210" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12">
       <c r="A211" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="B211" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="C211" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D211">
         <v>0.36</v>
@@ -8437,24 +8506,24 @@
         <v>19</v>
       </c>
       <c r="L211" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12">
       <c r="A212" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B212" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C212" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D212">
         <v>0.21</v>
       </c>
       <c r="E212">
-        <v>66.430000000000007</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -8472,18 +8541,18 @@
         <v>23</v>
       </c>
       <c r="L212" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12">
       <c r="A213" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B213" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C213" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D213">
         <v>0.21</v>
@@ -8507,18 +8576,18 @@
         <v>23</v>
       </c>
       <c r="L213" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12">
       <c r="A214" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B214" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="C214" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D214">
         <v>0.35</v>
@@ -8542,18 +8611,18 @@
         <v>17</v>
       </c>
       <c r="L214" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12">
       <c r="A215" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B215" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="C215" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D215">
         <v>1.43</v>
@@ -8577,18 +8646,18 @@
         <v>17</v>
       </c>
       <c r="L215" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12">
       <c r="A216" t="s">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="B216" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="C216" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D216">
         <v>0.21</v>
@@ -8612,24 +8681,24 @@
         <v>21</v>
       </c>
       <c r="L216" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12">
       <c r="A217" t="s">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="B217" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="C217" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D217">
         <v>0.23</v>
       </c>
       <c r="E217">
-        <v>40.770000000000003</v>
+        <v>40.77</v>
       </c>
       <c r="F217">
         <v>0</v>
@@ -8647,18 +8716,18 @@
         <v>5</v>
       </c>
       <c r="L217" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12">
       <c r="A218" t="s">
-        <v>12</v>
+        <v>144</v>
       </c>
       <c r="B218" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="C218" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D218">
         <v>0.5</v>
@@ -8682,24 +8751,24 @@
         <v>13</v>
       </c>
       <c r="L218" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12">
       <c r="A219" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="B219" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="C219" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D219">
         <v>0.26</v>
       </c>
       <c r="E219">
-        <v>70.739999999999995</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="F219">
         <v>0</v>
@@ -8717,18 +8786,18 @@
         <v>14</v>
       </c>
       <c r="L219" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12">
       <c r="A220" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="B220" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="C220" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D220">
         <v>0.18</v>
@@ -8752,21 +8821,21 @@
         <v>15</v>
       </c>
       <c r="L220" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12">
       <c r="A221" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B221" t="s">
-        <v>199</v>
+        <v>228</v>
       </c>
       <c r="C221" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D221">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E221">
         <v>60.36</v>
@@ -8787,18 +8856,18 @@
         <v>23</v>
       </c>
       <c r="L221" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12">
       <c r="A222" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B222" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="C222" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D222">
         <v>0.39</v>
@@ -8822,18 +8891,18 @@
         <v>19</v>
       </c>
       <c r="L222" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12">
       <c r="A223" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B223" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="C223" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D223">
         <v>0.47</v>
@@ -8857,18 +8926,18 @@
         <v>19</v>
       </c>
       <c r="L223" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12">
       <c r="A224" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="B224" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="C224" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D224">
         <v>0.42</v>
@@ -8892,18 +8961,18 @@
         <v>7</v>
       </c>
       <c r="L224" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12">
       <c r="A225" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B225" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="C225" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D225">
         <v>0.18</v>
@@ -8927,18 +8996,18 @@
         <v>19</v>
       </c>
       <c r="L225" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12">
       <c r="A226" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B226" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="C226" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D226">
         <v>0.24</v>
@@ -8950,7 +9019,7 @@
         <v>0</v>
       </c>
       <c r="G226">
-        <v>9.0500000000000007</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H226">
         <v>0</v>
@@ -8962,18 +9031,18 @@
         <v>11</v>
       </c>
       <c r="L226" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12">
       <c r="A227" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="B227" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C227" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D227">
         <v>0.09</v>
@@ -8997,18 +9066,18 @@
         <v>23</v>
       </c>
       <c r="L227" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12">
       <c r="A228" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="B228" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="C228" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D228">
         <v>0.35</v>
@@ -9032,18 +9101,18 @@
         <v>17</v>
       </c>
       <c r="L228" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12">
       <c r="A229" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="B229" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="C229" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D229">
         <v>0.35</v>
@@ -9067,21 +9136,21 @@
         <v>17</v>
       </c>
       <c r="L229" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12">
       <c r="A230" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B230" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="C230" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D230">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="E230">
         <v>63.89</v>
@@ -9090,7 +9159,7 @@
         <v>0</v>
       </c>
       <c r="G230">
-        <v>8.89</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H230">
         <v>0</v>
@@ -9102,24 +9171,24 @@
         <v>19</v>
       </c>
       <c r="L230" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12">
       <c r="A231" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B231" t="s">
-        <v>204</v>
+        <v>233</v>
       </c>
       <c r="C231" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D231">
         <v>0.27</v>
       </c>
       <c r="E231">
-        <v>37.270000000000003</v>
+        <v>37.27</v>
       </c>
       <c r="F231">
         <v>0</v>
@@ -9137,18 +9206,18 @@
         <v>19</v>
       </c>
       <c r="L231" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12">
       <c r="A232" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B232" t="s">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="C232" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D232">
         <v>0.12</v>
@@ -9172,21 +9241,21 @@
         <v>7</v>
       </c>
       <c r="L232" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12">
       <c r="A233" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B233" t="s">
-        <v>206</v>
+        <v>235</v>
       </c>
       <c r="C233" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D233">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="E233">
         <v>63.93</v>
@@ -9207,21 +9276,21 @@
         <v>19</v>
       </c>
       <c r="L233" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12">
       <c r="A234" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="B234" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C234" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="D234">
-        <v>1.1399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="E234">
         <v>55</v>
@@ -9242,18 +9311,18 @@
         <v>27</v>
       </c>
       <c r="L234" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12">
       <c r="A235" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="B235" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="C235" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D235">
         <v>0.33</v>
@@ -9277,18 +9346,18 @@
         <v>13</v>
       </c>
       <c r="L235" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12">
       <c r="A236" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="B236" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C236" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D236">
         <v>0.09</v>
@@ -9312,21 +9381,21 @@
         <v>23</v>
       </c>
       <c r="L236" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12">
       <c r="A237" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B237" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="C237" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D237">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="E237">
         <v>40</v>
@@ -9347,18 +9416,18 @@
         <v>19</v>
       </c>
       <c r="L237" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12">
       <c r="A238" t="s">
         <v>154</v>
       </c>
       <c r="B238" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="C238" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D238">
         <v>0.32</v>
@@ -9382,18 +9451,18 @@
         <v>19</v>
       </c>
       <c r="L238" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12">
       <c r="A239" t="s">
         <v>155</v>
       </c>
       <c r="B239" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C239" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D239">
         <v>3.29</v>
@@ -9417,18 +9486,18 @@
         <v>3</v>
       </c>
       <c r="L239" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12">
       <c r="A240" t="s">
         <v>155</v>
       </c>
       <c r="B240" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="C240" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D240">
         <v>0.2</v>
@@ -9452,18 +9521,18 @@
         <v>3</v>
       </c>
       <c r="L240" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12">
       <c r="A241" t="s">
         <v>156</v>
       </c>
       <c r="B241" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="C241" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="D241">
         <v>0.76</v>
@@ -9487,18 +9556,18 @@
         <v>23</v>
       </c>
       <c r="L241" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12">
       <c r="A242" t="s">
         <v>157</v>
       </c>
       <c r="B242" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="C242" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D242">
         <v>0.32</v>
@@ -9522,18 +9591,18 @@
         <v>12</v>
       </c>
       <c r="L242" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12">
       <c r="A243" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B243" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C243" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D243">
         <v>5.43</v>
@@ -9557,18 +9626,18 @@
         <v>5</v>
       </c>
       <c r="L243" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12">
       <c r="A244" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B244" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="C244" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D244">
         <v>0.4</v>
@@ -9592,18 +9661,18 @@
         <v>5</v>
       </c>
       <c r="L244" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12">
       <c r="A245" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B245" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C245" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D245">
         <v>0.11</v>
@@ -9627,18 +9696,18 @@
         <v>18</v>
       </c>
       <c r="L245" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12">
       <c r="A246" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B246" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C246" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D246">
         <v>2.57</v>
@@ -9662,18 +9731,18 @@
         <v>5</v>
       </c>
       <c r="L246" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12">
       <c r="A247" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B247" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="C247" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="D247">
         <v>0.5</v>
@@ -9697,18 +9766,18 @@
         <v>4</v>
       </c>
       <c r="L247" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12">
       <c r="A248" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B248" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C248" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D248">
         <v>0.22</v>
@@ -9732,18 +9801,18 @@
         <v>18</v>
       </c>
       <c r="L248" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12">
       <c r="A249" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B249" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C249" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D249">
         <v>0.17</v>
@@ -9755,7 +9824,7 @@
         <v>0</v>
       </c>
       <c r="G249">
-        <v>2.2200000000000002</v>
+        <v>2.22</v>
       </c>
       <c r="H249">
         <v>0</v>
@@ -9767,30 +9836,30 @@
         <v>18</v>
       </c>
       <c r="L249" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12">
       <c r="A250" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B250" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="C250" t="s">
-        <v>213</v>
-      </c>
-      <c r="D250" t="s">
-        <v>214</v>
-      </c>
-      <c r="E250" t="s">
-        <v>215</v>
-      </c>
-      <c r="F250" t="s">
-        <v>216</v>
-      </c>
-      <c r="G250" t="s">
-        <v>217</v>
+        <v>241</v>
+      </c>
+      <c r="D250">
+        <v>0.6</v>
+      </c>
+      <c r="E250">
+        <v>15</v>
+      </c>
+      <c r="F250">
+        <v>0</v>
+      </c>
+      <c r="G250">
+        <v>3</v>
       </c>
       <c r="H250">
         <v>0</v>
@@ -9798,25 +9867,25 @@
       <c r="J250">
         <v>0</v>
       </c>
-      <c r="K250" t="s">
-        <v>217</v>
+      <c r="K250">
+        <v>3</v>
       </c>
       <c r="L250" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12">
       <c r="A251" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B251" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C251" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D251">
-        <v>0.28000000000000003</v>
+        <v>0.28</v>
       </c>
       <c r="E251">
         <v>41.61</v>
@@ -9837,18 +9906,18 @@
         <v>18</v>
       </c>
       <c r="L251" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12">
       <c r="A252" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B252" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="C252" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="D252">
         <v>0.11</v>
@@ -9872,18 +9941,18 @@
         <v>18</v>
       </c>
       <c r="L252" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12">
       <c r="A253" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B253" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C253" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
       <c r="D253">
         <v>2.86</v>
@@ -9907,13 +9976,1402 @@
         <v>5</v>
       </c>
       <c r="L253" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12">
+      <c r="A254" t="s">
+        <v>169</v>
+      </c>
+      <c r="B254" t="s">
+        <v>207</v>
+      </c>
+      <c r="C254" t="s">
+        <v>242</v>
+      </c>
+      <c r="D254">
+        <v>0.79</v>
+      </c>
+      <c r="E254">
+        <v>19.83</v>
+      </c>
+      <c r="F254">
+        <v>5.5</v>
+      </c>
+      <c r="G254">
+        <v>4.31</v>
+      </c>
+      <c r="K254">
+        <v>29</v>
+      </c>
+      <c r="L254" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12">
+      <c r="A255" t="s">
+        <v>162</v>
+      </c>
+      <c r="B255" t="s">
+        <v>207</v>
+      </c>
+      <c r="C255" t="s">
+        <v>242</v>
+      </c>
+      <c r="D255">
+        <v>0.83</v>
+      </c>
+      <c r="E255">
+        <v>15</v>
+      </c>
+      <c r="F255">
+        <v>0</v>
+      </c>
+      <c r="G255">
+        <v>1.03</v>
+      </c>
+      <c r="K255">
+        <v>29</v>
+      </c>
+      <c r="L255" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12">
+      <c r="A256" t="s">
+        <v>170</v>
+      </c>
+      <c r="B256" t="s">
+        <v>207</v>
+      </c>
+      <c r="C256" t="s">
+        <v>242</v>
+      </c>
+      <c r="D256">
+        <v>0.88</v>
+      </c>
+      <c r="E256">
+        <v>0.52</v>
+      </c>
+      <c r="F256">
+        <v>0</v>
+      </c>
+      <c r="G256">
+        <v>0</v>
+      </c>
+      <c r="K256">
+        <v>27</v>
+      </c>
+      <c r="L256" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12">
+      <c r="A257" t="s">
+        <v>171</v>
+      </c>
+      <c r="B257" t="s">
+        <v>208</v>
+      </c>
+      <c r="C257" t="s">
+        <v>238</v>
+      </c>
+      <c r="D257">
+        <v>0.72</v>
+      </c>
+      <c r="E257">
+        <v>24.8</v>
+      </c>
+      <c r="F257">
+        <v>4.5</v>
+      </c>
+      <c r="G257">
+        <v>4.8</v>
+      </c>
+      <c r="K257">
+        <v>18</v>
+      </c>
+      <c r="L257" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12">
+      <c r="A258" t="s">
+        <v>172</v>
+      </c>
+      <c r="B258" t="s">
+        <v>208</v>
+      </c>
+      <c r="C258" t="s">
+        <v>238</v>
+      </c>
+      <c r="D258">
+        <v>1.6</v>
+      </c>
+      <c r="E258">
+        <v>0</v>
+      </c>
+      <c r="F258">
+        <v>0</v>
+      </c>
+      <c r="G258">
+        <v>1</v>
+      </c>
+      <c r="K258">
+        <v>18</v>
+      </c>
+      <c r="L258" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12">
+      <c r="A259" t="s">
+        <v>173</v>
+      </c>
+      <c r="B259" t="s">
+        <v>208</v>
+      </c>
+      <c r="C259" t="s">
+        <v>238</v>
+      </c>
+      <c r="D259">
+        <v>1.72</v>
+      </c>
+      <c r="E259">
+        <v>13.6</v>
+      </c>
+      <c r="F259">
+        <v>0</v>
+      </c>
+      <c r="G259">
+        <v>2</v>
+      </c>
+      <c r="K259">
+        <v>19</v>
+      </c>
+      <c r="L259" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12">
+      <c r="A260" t="s">
+        <v>174</v>
+      </c>
+      <c r="B260" t="s">
+        <v>208</v>
+      </c>
+      <c r="C260" t="s">
+        <v>238</v>
+      </c>
+      <c r="D260">
+        <v>1.4</v>
+      </c>
+      <c r="E260">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="F260">
+        <v>0</v>
+      </c>
+      <c r="G260">
+        <v>0</v>
+      </c>
+      <c r="K260">
+        <v>18</v>
+      </c>
+      <c r="L260" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12">
+      <c r="A261" t="s">
+        <v>175</v>
+      </c>
+      <c r="B261" t="s">
+        <v>198</v>
+      </c>
+      <c r="C261" t="s">
+        <v>237</v>
+      </c>
+      <c r="D261">
+        <v>0.65</v>
+      </c>
+      <c r="E261">
+        <v>26.47</v>
+      </c>
+      <c r="F261">
+        <v>0</v>
+      </c>
+      <c r="G261">
+        <v>0</v>
+      </c>
+      <c r="K261">
+        <v>13</v>
+      </c>
+      <c r="L261" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12">
+      <c r="A262" t="s">
+        <v>176</v>
+      </c>
+      <c r="B262" t="s">
+        <v>198</v>
+      </c>
+      <c r="C262" t="s">
+        <v>237</v>
+      </c>
+      <c r="D262">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E262">
+        <v>32.94</v>
+      </c>
+      <c r="F262">
+        <v>0</v>
+      </c>
+      <c r="G262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>13</v>
+      </c>
+      <c r="L262" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12">
+      <c r="A263" t="s">
+        <v>177</v>
+      </c>
+      <c r="B263" t="s">
+        <v>198</v>
+      </c>
+      <c r="C263" t="s">
+        <v>237</v>
+      </c>
+      <c r="D263">
+        <v>1.88</v>
+      </c>
+      <c r="E263">
+        <v>35.29</v>
+      </c>
+      <c r="F263">
+        <v>0</v>
+      </c>
+      <c r="G263">
+        <v>1.76</v>
+      </c>
+      <c r="K263">
+        <v>13</v>
+      </c>
+      <c r="L263" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12">
+      <c r="A264" t="s">
+        <v>178</v>
+      </c>
+      <c r="B264" t="s">
+        <v>198</v>
+      </c>
+      <c r="C264" t="s">
+        <v>237</v>
+      </c>
+      <c r="D264">
+        <v>2.18</v>
+      </c>
+      <c r="E264">
+        <v>21.76</v>
+      </c>
+      <c r="F264">
+        <v>0</v>
+      </c>
+      <c r="G264">
+        <v>1.18</v>
+      </c>
+      <c r="K264">
+        <v>12</v>
+      </c>
+      <c r="L264" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12">
+      <c r="A265" t="s">
+        <v>179</v>
+      </c>
+      <c r="B265" t="s">
+        <v>213</v>
+      </c>
+      <c r="C265" t="s">
+        <v>238</v>
+      </c>
+      <c r="D265">
+        <v>0.36</v>
+      </c>
+      <c r="E265">
+        <v>30</v>
+      </c>
+      <c r="F265">
+        <v>4.5</v>
+      </c>
+      <c r="G265">
+        <v>4.8</v>
+      </c>
+      <c r="K265">
+        <v>18</v>
+      </c>
+      <c r="L265" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12">
+      <c r="A266" t="s">
+        <v>180</v>
+      </c>
+      <c r="B266" t="s">
+        <v>213</v>
+      </c>
+      <c r="C266" t="s">
+        <v>238</v>
+      </c>
+      <c r="D266">
+        <v>2.08</v>
+      </c>
+      <c r="E266">
+        <v>18.8</v>
+      </c>
+      <c r="F266">
+        <v>0</v>
+      </c>
+      <c r="G266">
+        <v>6.8</v>
+      </c>
+      <c r="K266">
+        <v>18</v>
+      </c>
+      <c r="L266" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12">
+      <c r="A267" t="s">
+        <v>181</v>
+      </c>
+      <c r="B267" t="s">
+        <v>213</v>
+      </c>
+      <c r="C267" t="s">
+        <v>238</v>
+      </c>
+      <c r="D267">
+        <v>2.24</v>
+      </c>
+      <c r="E267">
+        <v>8.4</v>
+      </c>
+      <c r="F267">
+        <v>0</v>
+      </c>
+      <c r="G267">
+        <v>2</v>
+      </c>
+      <c r="K267">
+        <v>18</v>
+      </c>
+      <c r="L267" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12">
+      <c r="A268" t="s">
+        <v>182</v>
+      </c>
+      <c r="B268" t="s">
+        <v>213</v>
+      </c>
+      <c r="C268" t="s">
+        <v>238</v>
+      </c>
+      <c r="D268">
+        <v>2</v>
+      </c>
+      <c r="E268">
+        <v>7.2</v>
+      </c>
+      <c r="F268">
+        <v>0</v>
+      </c>
+      <c r="G268">
+        <v>1.2</v>
+      </c>
+      <c r="K268">
+        <v>18</v>
+      </c>
+      <c r="L268" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12">
+      <c r="A269" t="s">
+        <v>183</v>
+      </c>
+      <c r="B269" t="s">
+        <v>204</v>
+      </c>
+      <c r="C269" t="s">
+        <v>239</v>
+      </c>
+      <c r="D269">
+        <v>0.14</v>
+      </c>
+      <c r="E269">
+        <v>15.71</v>
+      </c>
+      <c r="F269">
+        <v>0</v>
+      </c>
+      <c r="G269">
+        <v>0.71</v>
+      </c>
+      <c r="K269">
+        <v>7</v>
+      </c>
+      <c r="L269" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12">
+      <c r="A270" t="s">
+        <v>184</v>
+      </c>
+      <c r="B270" t="s">
+        <v>204</v>
+      </c>
+      <c r="C270" t="s">
+        <v>239</v>
+      </c>
+      <c r="D270">
+        <v>0.14</v>
+      </c>
+      <c r="E270">
+        <v>26.43</v>
+      </c>
+      <c r="F270">
+        <v>0</v>
+      </c>
+      <c r="G270">
+        <v>2.14</v>
+      </c>
+      <c r="K270">
+        <v>7</v>
+      </c>
+      <c r="L270" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12">
+      <c r="A271" t="s">
+        <v>164</v>
+      </c>
+      <c r="B271" t="s">
+        <v>204</v>
+      </c>
+      <c r="C271" t="s">
+        <v>239</v>
+      </c>
+      <c r="D271">
+        <v>0.21</v>
+      </c>
+      <c r="E271">
+        <v>7.14</v>
+      </c>
+      <c r="F271">
+        <v>0</v>
+      </c>
+      <c r="G271">
+        <v>0</v>
+      </c>
+      <c r="K271">
+        <v>7</v>
+      </c>
+      <c r="L271" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12">
+      <c r="A272" t="s">
+        <v>185</v>
+      </c>
+      <c r="B272" t="s">
+        <v>204</v>
+      </c>
+      <c r="C272" t="s">
+        <v>239</v>
+      </c>
+      <c r="D272">
+        <v>0.14</v>
+      </c>
+      <c r="E272">
+        <v>5.71</v>
+      </c>
+      <c r="F272">
+        <v>0</v>
+      </c>
+      <c r="G272">
+        <v>0</v>
+      </c>
+      <c r="K272">
+        <v>7</v>
+      </c>
+      <c r="L272" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12">
+      <c r="A273" t="s">
+        <v>186</v>
+      </c>
+      <c r="B273" t="s">
+        <v>214</v>
+      </c>
+      <c r="C273" t="s">
+        <v>241</v>
+      </c>
+      <c r="D273">
+        <v>0.15</v>
+      </c>
+      <c r="E273">
+        <v>3.85</v>
+      </c>
+      <c r="F273">
+        <v>0</v>
+      </c>
+      <c r="G273">
+        <v>1.54</v>
+      </c>
+      <c r="K273">
+        <v>6</v>
+      </c>
+      <c r="L273" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12">
+      <c r="A274" t="s">
+        <v>161</v>
+      </c>
+      <c r="B274" t="s">
+        <v>214</v>
+      </c>
+      <c r="C274" t="s">
+        <v>241</v>
+      </c>
+      <c r="D274">
+        <v>0.31</v>
+      </c>
+      <c r="E274">
+        <v>14.62</v>
+      </c>
+      <c r="F274">
+        <v>0</v>
+      </c>
+      <c r="G274">
+        <v>0</v>
+      </c>
+      <c r="K274">
+        <v>5</v>
+      </c>
+      <c r="L274" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12">
+      <c r="A275" t="s">
+        <v>187</v>
+      </c>
+      <c r="B275" t="s">
+        <v>214</v>
+      </c>
+      <c r="C275" t="s">
+        <v>241</v>
+      </c>
+      <c r="D275">
+        <v>0.46</v>
+      </c>
+      <c r="E275">
+        <v>27.69</v>
+      </c>
+      <c r="F275">
+        <v>0</v>
+      </c>
+      <c r="G275">
+        <v>2.31</v>
+      </c>
+      <c r="K275">
+        <v>5</v>
+      </c>
+      <c r="L275" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12">
+      <c r="A276" t="s">
+        <v>160</v>
+      </c>
+      <c r="B276" t="s">
+        <v>212</v>
+      </c>
+      <c r="C276" t="s">
+        <v>238</v>
+      </c>
+      <c r="D276">
+        <v>0.63</v>
+      </c>
+      <c r="E276">
+        <v>9.26</v>
+      </c>
+      <c r="F276">
+        <v>0</v>
+      </c>
+      <c r="G276">
+        <v>0</v>
+      </c>
+      <c r="K276">
+        <v>15</v>
+      </c>
+      <c r="L276" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12">
+      <c r="A277" t="s">
+        <v>188</v>
+      </c>
+      <c r="B277" t="s">
+        <v>212</v>
+      </c>
+      <c r="C277" t="s">
+        <v>238</v>
+      </c>
+      <c r="D277">
+        <v>1.52</v>
+      </c>
+      <c r="E277">
+        <v>17.78</v>
+      </c>
+      <c r="F277">
+        <v>0</v>
+      </c>
+      <c r="G277">
+        <v>1.11</v>
+      </c>
+      <c r="K277">
+        <v>15</v>
+      </c>
+      <c r="L277" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12">
+      <c r="A278" t="s">
+        <v>166</v>
+      </c>
+      <c r="B278" t="s">
+        <v>212</v>
+      </c>
+      <c r="C278" t="s">
+        <v>238</v>
+      </c>
+      <c r="D278">
+        <v>2.11</v>
+      </c>
+      <c r="E278">
+        <v>17.41</v>
+      </c>
+      <c r="F278">
+        <v>0</v>
+      </c>
+      <c r="G278">
+        <v>0</v>
+      </c>
+      <c r="K278">
+        <v>15</v>
+      </c>
+      <c r="L278" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12">
+      <c r="A279" t="s">
+        <v>172</v>
+      </c>
+      <c r="B279" t="s">
+        <v>209</v>
+      </c>
+      <c r="C279" t="s">
+        <v>240</v>
+      </c>
+      <c r="D279">
+        <v>0.18</v>
+      </c>
+      <c r="E279">
+        <v>1.43</v>
+      </c>
+      <c r="F279">
+        <v>0</v>
+      </c>
+      <c r="G279">
+        <v>0</v>
+      </c>
+      <c r="K279">
+        <v>12</v>
+      </c>
+      <c r="L279" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12">
+      <c r="A280" t="s">
+        <v>189</v>
+      </c>
+      <c r="B280" t="s">
+        <v>209</v>
+      </c>
+      <c r="C280" t="s">
+        <v>240</v>
+      </c>
+      <c r="D280">
+        <v>0.42</v>
+      </c>
+      <c r="E280">
+        <v>3.85</v>
+      </c>
+      <c r="F280">
+        <v>0</v>
+      </c>
+      <c r="G280">
+        <v>0.84</v>
+      </c>
+      <c r="K280">
+        <v>12</v>
+      </c>
+      <c r="L280" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12">
+      <c r="A281" t="s">
+        <v>190</v>
+      </c>
+      <c r="B281" t="s">
+        <v>209</v>
+      </c>
+      <c r="C281" t="s">
+        <v>240</v>
+      </c>
+      <c r="D281">
+        <v>1.07</v>
+      </c>
+      <c r="E281">
+        <v>13.85</v>
+      </c>
+      <c r="F281">
+        <v>0</v>
+      </c>
+      <c r="G281">
+        <v>0</v>
+      </c>
+      <c r="K281">
+        <v>12</v>
+      </c>
+      <c r="L281" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12">
+      <c r="A282" t="s">
+        <v>184</v>
+      </c>
+      <c r="B282" t="s">
+        <v>215</v>
+      </c>
+      <c r="C282" t="s">
+        <v>240</v>
+      </c>
+      <c r="D282">
+        <v>0.43</v>
+      </c>
+      <c r="E282">
+        <v>1.43</v>
+      </c>
+      <c r="F282">
+        <v>0</v>
+      </c>
+      <c r="G282">
+        <v>0</v>
+      </c>
+      <c r="K282">
+        <v>9</v>
+      </c>
+      <c r="L282" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12">
+      <c r="A283" t="s">
+        <v>189</v>
+      </c>
+      <c r="B283" t="s">
+        <v>215</v>
+      </c>
+      <c r="C283" t="s">
+        <v>240</v>
+      </c>
+      <c r="D283">
+        <v>0.33</v>
+      </c>
+      <c r="E283">
+        <v>1.9</v>
+      </c>
+      <c r="F283">
+        <v>0</v>
+      </c>
+      <c r="G283">
+        <v>0</v>
+      </c>
+      <c r="K283">
+        <v>9</v>
+      </c>
+      <c r="L283" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12">
+      <c r="A284" t="s">
+        <v>191</v>
+      </c>
+      <c r="B284" t="s">
+        <v>215</v>
+      </c>
+      <c r="C284" t="s">
+        <v>240</v>
+      </c>
+      <c r="D284">
+        <v>0.62</v>
+      </c>
+      <c r="E284">
+        <v>2.86</v>
+      </c>
+      <c r="F284">
+        <v>0</v>
+      </c>
+      <c r="G284">
+        <v>0.95</v>
+      </c>
+      <c r="K284">
+        <v>9</v>
+      </c>
+      <c r="L284" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12">
+      <c r="A285" t="s">
+        <v>177</v>
+      </c>
+      <c r="B285" t="s">
+        <v>199</v>
+      </c>
+      <c r="C285" t="s">
+        <v>239</v>
+      </c>
+      <c r="D285">
+        <v>0.11</v>
+      </c>
+      <c r="E285">
+        <v>3.33</v>
+      </c>
+      <c r="F285">
+        <v>0</v>
+      </c>
+      <c r="G285">
+        <v>0</v>
+      </c>
+      <c r="K285">
+        <v>11</v>
+      </c>
+      <c r="L285" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12">
+      <c r="A286" t="s">
+        <v>192</v>
+      </c>
+      <c r="B286" t="s">
+        <v>199</v>
+      </c>
+      <c r="C286" t="s">
+        <v>239</v>
+      </c>
+      <c r="D286">
+        <v>0.22</v>
+      </c>
+      <c r="E286">
+        <v>7.22</v>
+      </c>
+      <c r="F286">
+        <v>0</v>
+      </c>
+      <c r="G286">
+        <v>0</v>
+      </c>
+      <c r="K286">
+        <v>11</v>
+      </c>
+      <c r="L286" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12">
+      <c r="A287" t="s">
+        <v>192</v>
+      </c>
+      <c r="B287" t="s">
+        <v>199</v>
+      </c>
+      <c r="C287" t="s">
+        <v>239</v>
+      </c>
+      <c r="D287">
+        <v>0.22</v>
+      </c>
+      <c r="E287">
+        <v>7.22</v>
+      </c>
+      <c r="F287">
+        <v>0</v>
+      </c>
+      <c r="G287">
+        <v>0</v>
+      </c>
+      <c r="K287">
+        <v>9</v>
+      </c>
+      <c r="L287" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12">
+      <c r="A288" t="s">
+        <v>178</v>
+      </c>
+      <c r="B288" t="s">
+        <v>199</v>
+      </c>
+      <c r="C288" t="s">
+        <v>239</v>
+      </c>
+      <c r="D288">
+        <v>0.33</v>
+      </c>
+      <c r="E288">
+        <v>33.89</v>
+      </c>
+      <c r="F288">
+        <v>0</v>
+      </c>
+      <c r="G288">
+        <v>1.11</v>
+      </c>
+      <c r="K288">
+        <v>9</v>
+      </c>
+      <c r="L288" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12">
+      <c r="A289" t="s">
+        <v>193</v>
+      </c>
+      <c r="B289" t="s">
+        <v>199</v>
+      </c>
+      <c r="C289" t="s">
+        <v>239</v>
+      </c>
+      <c r="D289">
+        <v>0.11</v>
+      </c>
+      <c r="E289">
+        <v>48.33</v>
+      </c>
+      <c r="F289">
+        <v>0</v>
+      </c>
+      <c r="G289">
+        <v>0</v>
+      </c>
+      <c r="K289">
+        <v>9</v>
+      </c>
+      <c r="L289" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12">
+      <c r="A290" t="s">
+        <v>163</v>
+      </c>
+      <c r="B290" t="s">
         <v>219</v>
       </c>
+      <c r="C290" t="s">
+        <v>240</v>
+      </c>
+      <c r="D290">
+        <v>1.91</v>
+      </c>
+      <c r="E290">
+        <v>14.55</v>
+      </c>
+      <c r="F290">
+        <v>0</v>
+      </c>
+      <c r="G290">
+        <v>1.36</v>
+      </c>
+      <c r="K290">
+        <v>11</v>
+      </c>
+      <c r="L290" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="291" spans="1:12">
+      <c r="A291" t="s">
+        <v>194</v>
+      </c>
+      <c r="B291" t="s">
+        <v>219</v>
+      </c>
+      <c r="C291" t="s">
+        <v>240</v>
+      </c>
+      <c r="D291">
+        <v>2.27</v>
+      </c>
+      <c r="E291">
+        <v>20.91</v>
+      </c>
+      <c r="F291">
+        <v>0</v>
+      </c>
+      <c r="G291">
+        <v>0.45</v>
+      </c>
+      <c r="K291">
+        <v>12</v>
+      </c>
+      <c r="L291" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="292" spans="1:12">
+      <c r="A292" t="s">
+        <v>174</v>
+      </c>
+      <c r="B292" t="s">
+        <v>219</v>
+      </c>
+      <c r="C292" t="s">
+        <v>240</v>
+      </c>
+      <c r="D292">
+        <v>2.64</v>
+      </c>
+      <c r="E292">
+        <v>28.18</v>
+      </c>
+      <c r="F292">
+        <v>0</v>
+      </c>
+      <c r="G292">
+        <v>0</v>
+      </c>
+      <c r="K292">
+        <v>16</v>
+      </c>
+      <c r="L292" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12">
+      <c r="A293" t="s">
+        <v>195</v>
+      </c>
+      <c r="B293" t="s">
+        <v>229</v>
+      </c>
+      <c r="C293" t="s">
+        <v>239</v>
+      </c>
+      <c r="D293">
+        <v>0.71</v>
+      </c>
+      <c r="E293">
+        <v>32.86</v>
+      </c>
+      <c r="F293">
+        <v>0</v>
+      </c>
+      <c r="G293">
+        <v>0</v>
+      </c>
+      <c r="K293">
+        <v>5</v>
+      </c>
+      <c r="L293" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="294" spans="1:12">
+      <c r="A294" t="s">
+        <v>187</v>
+      </c>
+      <c r="B294" t="s">
+        <v>229</v>
+      </c>
+      <c r="C294" t="s">
+        <v>239</v>
+      </c>
+      <c r="D294">
+        <v>0.89</v>
+      </c>
+      <c r="E294">
+        <v>36.67</v>
+      </c>
+      <c r="F294">
+        <v>0</v>
+      </c>
+      <c r="G294">
+        <v>0</v>
+      </c>
+      <c r="K294">
+        <v>5</v>
+      </c>
+      <c r="L294" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="295" spans="1:12">
+      <c r="A295" t="s">
+        <v>196</v>
+      </c>
+      <c r="B295" t="s">
+        <v>225</v>
+      </c>
+      <c r="C295" t="s">
+        <v>240</v>
+      </c>
+      <c r="D295">
+        <v>0.15</v>
+      </c>
+      <c r="E295">
+        <v>4.62</v>
+      </c>
+      <c r="F295">
+        <v>0</v>
+      </c>
+      <c r="G295">
+        <v>0</v>
+      </c>
+      <c r="K295">
+        <v>6</v>
+      </c>
+      <c r="L295" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12">
+      <c r="A296" t="s">
+        <v>164</v>
+      </c>
+      <c r="B296" t="s">
+        <v>210</v>
+      </c>
+      <c r="C296" t="s">
+        <v>240</v>
+      </c>
+      <c r="D296">
+        <v>0.28</v>
+      </c>
+      <c r="E296">
+        <v>8.33</v>
+      </c>
+      <c r="F296">
+        <v>0</v>
+      </c>
+      <c r="G296">
+        <v>1.11</v>
+      </c>
+      <c r="K296">
+        <v>9</v>
+      </c>
+      <c r="L296" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="297" spans="1:12">
+      <c r="A297" t="s">
+        <v>190</v>
+      </c>
+      <c r="B297" t="s">
+        <v>210</v>
+      </c>
+      <c r="C297" t="s">
+        <v>240</v>
+      </c>
+      <c r="D297">
+        <v>5.56</v>
+      </c>
+      <c r="E297">
+        <v>23.89</v>
+      </c>
+      <c r="F297">
+        <v>0</v>
+      </c>
+      <c r="G297">
+        <v>0</v>
+      </c>
+      <c r="K297">
+        <v>13</v>
+      </c>
+      <c r="L297" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12">
+      <c r="A298" t="s">
+        <v>190</v>
+      </c>
+      <c r="B298" t="s">
+        <v>217</v>
+      </c>
+      <c r="C298" t="s">
+        <v>240</v>
+      </c>
+      <c r="D298">
+        <v>0.19</v>
+      </c>
+      <c r="E298">
+        <v>6.35</v>
+      </c>
+      <c r="F298">
+        <v>0</v>
+      </c>
+      <c r="G298">
+        <v>0</v>
+      </c>
+      <c r="K298">
+        <v>29</v>
+      </c>
+      <c r="L298" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="299" spans="1:12">
+      <c r="A299" t="s">
+        <v>167</v>
+      </c>
+      <c r="B299" t="s">
+        <v>217</v>
+      </c>
+      <c r="C299" t="s">
+        <v>240</v>
+      </c>
+      <c r="D299">
+        <v>0.52</v>
+      </c>
+      <c r="E299">
+        <v>41.52</v>
+      </c>
+      <c r="F299">
+        <v>0</v>
+      </c>
+      <c r="G299">
+        <v>0</v>
+      </c>
+      <c r="K299">
+        <v>29</v>
+      </c>
+      <c r="L299" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12">
+      <c r="A300" t="s">
+        <v>197</v>
+      </c>
+      <c r="B300" t="s">
+        <v>226</v>
+      </c>
+      <c r="C300" t="s">
+        <v>239</v>
+      </c>
+      <c r="D300">
+        <v>0.11</v>
+      </c>
+      <c r="E300">
+        <v>15.71</v>
+      </c>
+      <c r="F300">
+        <v>0</v>
+      </c>
+      <c r="G300">
+        <v>0</v>
+      </c>
+      <c r="K300">
+        <v>13</v>
+      </c>
+      <c r="L300" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12">
+      <c r="A301" t="s">
+        <v>185</v>
+      </c>
+      <c r="B301" t="s">
+        <v>202</v>
+      </c>
+      <c r="C301" t="s">
+        <v>241</v>
+      </c>
+      <c r="D301" t="s">
+        <v>243</v>
+      </c>
+      <c r="E301" t="s">
+        <v>244</v>
+      </c>
+      <c r="F301" t="s">
+        <v>245</v>
+      </c>
+      <c r="G301" t="s">
+        <v>245</v>
+      </c>
+      <c r="K301" t="s">
+        <v>246</v>
+      </c>
+      <c r="L301" t="s">
+        <v>248</v>
+      </c>
     </row>
   </sheetData>
-  <sortState ref="A2:L253">
-    <sortCondition ref="A196"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/pest_disease_control.xlsx
+++ b/data/pest_disease_control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="263">
   <si>
     <t>Date</t>
   </si>
@@ -520,9 +520,6 @@
     <t>2025-10-08</t>
   </si>
   <si>
-    <t>2025-10-18</t>
-  </si>
-  <si>
     <t>2025-07-24</t>
   </si>
   <si>
@@ -610,6 +607,51 @@
     <t>2025-10-02</t>
   </si>
   <si>
+    <t>2025-10-14</t>
+  </si>
+  <si>
+    <t>2025-11-11</t>
+  </si>
+  <si>
+    <t>2025-10-16</t>
+  </si>
+  <si>
+    <t>2025-10-22</t>
+  </si>
+  <si>
+    <t>2025-11-04</t>
+  </si>
+  <si>
+    <t>2025-10-21</t>
+  </si>
+  <si>
+    <t>2025-10-23</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>2025-10-27</t>
+  </si>
+  <si>
+    <t>2025-10-17</t>
+  </si>
+  <si>
+    <t>2025-10-28</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>2025-11-12</t>
+  </si>
+  <si>
+    <t>2025-11-06</t>
+  </si>
+  <si>
+    <t>2025-10-24</t>
+  </si>
+  <si>
     <t>DG01000</t>
   </si>
   <si>
@@ -745,16 +787,16 @@
     <t>MN1</t>
   </si>
   <si>
-    <t>0.09</t>
-  </si>
-  <si>
-    <t>10.87</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>33</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>12</t>
+    <t>4</t>
   </si>
   <si>
     <t>2024/25</t>
@@ -1118,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L301"/>
+  <dimension ref="A1:L338"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1164,10 +1206,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D2">
         <v>1.32</v>
@@ -1191,7 +1233,7 @@
         <v>10</v>
       </c>
       <c r="L2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1199,10 +1241,10 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C3" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D3">
         <v>0.47</v>
@@ -1226,7 +1268,7 @@
         <v>7</v>
       </c>
       <c r="L3" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1234,10 +1276,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D4">
         <v>0.06</v>
@@ -1261,7 +1303,7 @@
         <v>6</v>
       </c>
       <c r="L4" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1269,10 +1311,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C5" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D5">
         <v>0.32</v>
@@ -1296,7 +1338,7 @@
         <v>7</v>
       </c>
       <c r="L5" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1304,10 +1346,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C6" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D6">
         <v>0.6</v>
@@ -1331,7 +1373,7 @@
         <v>8</v>
       </c>
       <c r="L6" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1339,10 +1381,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C7" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D7">
         <v>0.16</v>
@@ -1366,7 +1408,7 @@
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1374,10 +1416,10 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C8" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D8">
         <v>0.47</v>
@@ -1401,7 +1443,7 @@
         <v>8</v>
       </c>
       <c r="L8" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1409,10 +1451,10 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C9" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D9">
         <v>0.28</v>
@@ -1436,7 +1478,7 @@
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1444,10 +1486,10 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C10" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D10">
         <v>0.16</v>
@@ -1471,7 +1513,7 @@
         <v>6</v>
       </c>
       <c r="L10" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1479,10 +1521,10 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C11" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D11">
         <v>0.5</v>
@@ -1506,7 +1548,7 @@
         <v>7</v>
       </c>
       <c r="L11" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1514,10 +1556,10 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C12" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D12">
         <v>0.2</v>
@@ -1541,7 +1583,7 @@
         <v>8</v>
       </c>
       <c r="L12" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1549,10 +1591,10 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C13" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D13">
         <v>0.6</v>
@@ -1576,7 +1618,7 @@
         <v>7</v>
       </c>
       <c r="L13" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1584,10 +1626,10 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C14" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D14">
         <v>1.07</v>
@@ -1611,7 +1653,7 @@
         <v>11</v>
       </c>
       <c r="L14" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1619,10 +1661,10 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C15" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D15">
         <v>0.43</v>
@@ -1646,7 +1688,7 @@
         <v>9</v>
       </c>
       <c r="L15" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1654,10 +1696,10 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C16" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D16">
         <v>1.05</v>
@@ -1681,7 +1723,7 @@
         <v>10</v>
       </c>
       <c r="L16" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1689,10 +1731,10 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C17" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D17">
         <v>0.11</v>
@@ -1716,7 +1758,7 @@
         <v>23</v>
       </c>
       <c r="L17" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1724,10 +1766,10 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="C18" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D18">
         <v>0.06</v>
@@ -1751,7 +1793,7 @@
         <v>27</v>
       </c>
       <c r="L18" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1759,10 +1801,10 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C19" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D19">
         <v>0.07000000000000001</v>
@@ -1786,7 +1828,7 @@
         <v>7</v>
       </c>
       <c r="L19" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1794,10 +1836,10 @@
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C20" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D20">
         <v>1.15</v>
@@ -1821,7 +1863,7 @@
         <v>17</v>
       </c>
       <c r="L20" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1829,10 +1871,10 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="C21" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D21">
         <v>0.08</v>
@@ -1856,7 +1898,7 @@
         <v>26</v>
       </c>
       <c r="L21" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1864,10 +1906,10 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C22" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D22">
         <v>0.45</v>
@@ -1891,7 +1933,7 @@
         <v>23</v>
       </c>
       <c r="L22" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -1899,10 +1941,10 @@
         <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C23" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D23">
         <v>0.38</v>
@@ -1926,7 +1968,7 @@
         <v>18</v>
       </c>
       <c r="L23" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1934,10 +1976,10 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="C24" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D24">
         <v>0.11</v>
@@ -1961,7 +2003,7 @@
         <v>27</v>
       </c>
       <c r="L24" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -1969,10 +2011,10 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C25" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D25">
         <v>0.09</v>
@@ -1996,7 +2038,7 @@
         <v>21</v>
       </c>
       <c r="L25" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2004,10 +2046,10 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C26" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D26">
         <v>0.17</v>
@@ -2031,7 +2073,7 @@
         <v>13</v>
       </c>
       <c r="L26" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2039,10 +2081,10 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="C27" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D27">
         <v>0.09</v>
@@ -2066,7 +2108,7 @@
         <v>17</v>
       </c>
       <c r="L27" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2074,10 +2116,10 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C28" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D28">
         <v>0.9399999999999999</v>
@@ -2101,7 +2143,7 @@
         <v>14</v>
       </c>
       <c r="L28" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2109,10 +2151,10 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C29" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D29">
         <v>0.9399999999999999</v>
@@ -2136,7 +2178,7 @@
         <v>12</v>
       </c>
       <c r="L29" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2144,10 +2186,10 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C30" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D30">
         <v>0.06</v>
@@ -2171,7 +2213,7 @@
         <v>21</v>
       </c>
       <c r="L30" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2179,10 +2221,10 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C31" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D31">
         <v>0.29</v>
@@ -2206,7 +2248,7 @@
         <v>19</v>
       </c>
       <c r="L31" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2214,10 +2256,10 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C32" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D32">
         <v>0.11</v>
@@ -2241,7 +2283,7 @@
         <v>16</v>
       </c>
       <c r="L32" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2249,10 +2291,10 @@
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C33" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D33">
         <v>0.15</v>
@@ -2276,7 +2318,7 @@
         <v>7</v>
       </c>
       <c r="L33" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2284,10 +2326,10 @@
         <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C34" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D34">
         <v>0.42</v>
@@ -2311,7 +2353,7 @@
         <v>21</v>
       </c>
       <c r="L34" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2319,10 +2361,10 @@
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="C35" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D35">
         <v>0.5600000000000001</v>
@@ -2346,7 +2388,7 @@
         <v>27</v>
       </c>
       <c r="L35" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2354,10 +2396,10 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="C36" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D36">
         <v>0.21</v>
@@ -2381,7 +2423,7 @@
         <v>7</v>
       </c>
       <c r="L36" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2389,10 +2431,10 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="C37" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D37">
         <v>0.24</v>
@@ -2416,7 +2458,7 @@
         <v>16</v>
       </c>
       <c r="L37" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2424,10 +2466,10 @@
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C38" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D38">
         <v>0.17</v>
@@ -2451,7 +2493,7 @@
         <v>4</v>
       </c>
       <c r="L38" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2459,10 +2501,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C39" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D39">
         <v>1.62</v>
@@ -2486,7 +2528,7 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2494,10 +2536,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="C40" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D40">
         <v>0.38</v>
@@ -2521,7 +2563,7 @@
         <v>18</v>
       </c>
       <c r="L40" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2529,10 +2571,10 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="C41" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D41">
         <v>0.09</v>
@@ -2556,7 +2598,7 @@
         <v>19</v>
       </c>
       <c r="L41" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2564,10 +2606,10 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="C42" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D42">
         <v>0.1</v>
@@ -2591,7 +2633,7 @@
         <v>17</v>
       </c>
       <c r="L42" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2599,10 +2641,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C43" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D43">
         <v>0.22</v>
@@ -2626,7 +2668,7 @@
         <v>21</v>
       </c>
       <c r="L43" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2634,10 +2676,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C44" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D44">
         <v>0.14</v>
@@ -2661,7 +2703,7 @@
         <v>23</v>
       </c>
       <c r="L44" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2669,10 +2711,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="C45" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D45">
         <v>0.09</v>
@@ -2696,7 +2738,7 @@
         <v>4</v>
       </c>
       <c r="L45" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2704,10 +2746,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C46" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D46">
         <v>0.22</v>
@@ -2731,7 +2773,7 @@
         <v>17</v>
       </c>
       <c r="L46" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2739,10 +2781,10 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C47" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D47">
         <v>0.23</v>
@@ -2766,7 +2808,7 @@
         <v>7</v>
       </c>
       <c r="L47" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2774,10 +2816,10 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C48" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D48">
         <v>0.29</v>
@@ -2801,7 +2843,7 @@
         <v>11</v>
       </c>
       <c r="L48" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2809,10 +2851,10 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="C49" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D49">
         <v>0.15</v>
@@ -2836,7 +2878,7 @@
         <v>9</v>
       </c>
       <c r="L49" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2844,10 +2886,10 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C50" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D50">
         <v>0.14</v>
@@ -2871,7 +2913,7 @@
         <v>23</v>
       </c>
       <c r="L50" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2879,10 +2921,10 @@
         <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="C51" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D51">
         <v>0.14</v>
@@ -2906,7 +2948,7 @@
         <v>7</v>
       </c>
       <c r="L51" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2914,10 +2956,10 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C52" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D52">
         <v>0.71</v>
@@ -2941,7 +2983,7 @@
         <v>12</v>
       </c>
       <c r="L52" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -2949,10 +2991,10 @@
         <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C53" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D53">
         <v>0.15</v>
@@ -2976,7 +3018,7 @@
         <v>13</v>
       </c>
       <c r="L53" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -2984,10 +3026,10 @@
         <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C54" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D54">
         <v>0.28</v>
@@ -3011,7 +3053,7 @@
         <v>14</v>
       </c>
       <c r="L54" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3019,10 +3061,10 @@
         <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="C55" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D55">
         <v>0.23</v>
@@ -3046,7 +3088,7 @@
         <v>4</v>
       </c>
       <c r="L55" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3054,10 +3096,10 @@
         <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C56" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D56">
         <v>0.29</v>
@@ -3081,7 +3123,7 @@
         <v>21</v>
       </c>
       <c r="L56" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3089,10 +3131,10 @@
         <v>50</v>
       </c>
       <c r="B57" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C57" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D57">
         <v>0.12</v>
@@ -3116,7 +3158,7 @@
         <v>13</v>
       </c>
       <c r="L57" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3124,10 +3166,10 @@
         <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="C58" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D58">
         <v>0.5</v>
@@ -3151,7 +3193,7 @@
         <v>17</v>
       </c>
       <c r="L58" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3159,10 +3201,10 @@
         <v>50</v>
       </c>
       <c r="B59" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="C59" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D59">
         <v>0.52</v>
@@ -3186,7 +3228,7 @@
         <v>17</v>
       </c>
       <c r="L59" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3194,10 +3236,10 @@
         <v>51</v>
       </c>
       <c r="B60" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C60" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D60">
         <v>0.28</v>
@@ -3221,7 +3263,7 @@
         <v>19</v>
       </c>
       <c r="L60" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3229,10 +3271,10 @@
         <v>52</v>
       </c>
       <c r="B61" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C61" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D61">
         <v>0.55</v>
@@ -3256,7 +3298,7 @@
         <v>23</v>
       </c>
       <c r="L61" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3264,10 +3306,10 @@
         <v>53</v>
       </c>
       <c r="B62" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C62" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D62">
         <v>0.26</v>
@@ -3291,7 +3333,7 @@
         <v>14</v>
       </c>
       <c r="L62" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3299,10 +3341,10 @@
         <v>54</v>
       </c>
       <c r="B63" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="C63" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D63">
         <v>0.08</v>
@@ -3326,7 +3368,7 @@
         <v>27</v>
       </c>
       <c r="L63" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3334,10 +3376,10 @@
         <v>55</v>
       </c>
       <c r="B64" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="C64" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D64">
         <v>1.04</v>
@@ -3361,7 +3403,7 @@
         <v>27</v>
       </c>
       <c r="L64" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3369,10 +3411,10 @@
         <v>55</v>
       </c>
       <c r="B65" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="C65" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D65">
         <v>0.07000000000000001</v>
@@ -3396,7 +3438,7 @@
         <v>26</v>
       </c>
       <c r="L65" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3404,10 +3446,10 @@
         <v>56</v>
       </c>
       <c r="B66" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="C66" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D66">
         <v>0.25</v>
@@ -3431,7 +3473,7 @@
         <v>7</v>
       </c>
       <c r="L66" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3439,10 +3481,10 @@
         <v>56</v>
       </c>
       <c r="B67" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C67" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D67">
         <v>0.03</v>
@@ -3466,7 +3508,7 @@
         <v>23</v>
       </c>
       <c r="L67" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3474,10 +3516,10 @@
         <v>57</v>
       </c>
       <c r="B68" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C68" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D68">
         <v>1.47</v>
@@ -3501,7 +3543,7 @@
         <v>17</v>
       </c>
       <c r="L68" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3509,10 +3551,10 @@
         <v>57</v>
       </c>
       <c r="B69" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C69" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D69">
         <v>0.13</v>
@@ -3536,7 +3578,7 @@
         <v>7</v>
       </c>
       <c r="L69" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3544,10 +3586,10 @@
         <v>58</v>
       </c>
       <c r="B70" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C70" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D70">
         <v>0.76</v>
@@ -3571,7 +3613,7 @@
         <v>21</v>
       </c>
       <c r="L70" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3579,10 +3621,10 @@
         <v>59</v>
       </c>
       <c r="B71" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C71" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D71">
         <v>0.2</v>
@@ -3606,7 +3648,7 @@
         <v>19</v>
       </c>
       <c r="L71" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3614,10 +3656,10 @@
         <v>59</v>
       </c>
       <c r="B72" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="C72" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D72">
         <v>2.19</v>
@@ -3641,7 +3683,7 @@
         <v>17</v>
       </c>
       <c r="L72" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3649,10 +3691,10 @@
         <v>60</v>
       </c>
       <c r="B73" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C73" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D73">
         <v>0.2</v>
@@ -3676,7 +3718,7 @@
         <v>4</v>
       </c>
       <c r="L73" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3684,10 +3726,10 @@
         <v>60</v>
       </c>
       <c r="B74" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C74" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D74">
         <v>2.26</v>
@@ -3711,7 +3753,7 @@
         <v>23</v>
       </c>
       <c r="L74" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3719,10 +3761,10 @@
         <v>61</v>
       </c>
       <c r="B75" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C75" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D75">
         <v>0.15</v>
@@ -3746,7 +3788,7 @@
         <v>13</v>
       </c>
       <c r="L75" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3754,10 +3796,10 @@
         <v>61</v>
       </c>
       <c r="B76" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C76" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D76">
         <v>0.17</v>
@@ -3781,7 +3823,7 @@
         <v>13</v>
       </c>
       <c r="L76" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3789,10 +3831,10 @@
         <v>62</v>
       </c>
       <c r="B77" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="C77" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D77">
         <v>0.64</v>
@@ -3816,7 +3858,7 @@
         <v>17</v>
       </c>
       <c r="L77" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3824,10 +3866,10 @@
         <v>63</v>
       </c>
       <c r="B78" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C78" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D78">
         <v>0.45</v>
@@ -3851,7 +3893,7 @@
         <v>12</v>
       </c>
       <c r="L78" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3859,10 +3901,10 @@
         <v>63</v>
       </c>
       <c r="B79" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C79" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D79">
         <v>0.64</v>
@@ -3886,7 +3928,7 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3894,10 +3936,10 @@
         <v>64</v>
       </c>
       <c r="B80" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C80" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D80">
         <v>0.28</v>
@@ -3921,7 +3963,7 @@
         <v>11</v>
       </c>
       <c r="L80" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3929,10 +3971,10 @@
         <v>64</v>
       </c>
       <c r="B81" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="C81" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D81">
         <v>0.31</v>
@@ -3956,7 +3998,7 @@
         <v>9</v>
       </c>
       <c r="L81" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3964,10 +4006,10 @@
         <v>65</v>
       </c>
       <c r="B82" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C82" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D82">
         <v>0.14</v>
@@ -3991,7 +4033,7 @@
         <v>21</v>
       </c>
       <c r="L82" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -3999,10 +4041,10 @@
         <v>65</v>
       </c>
       <c r="B83" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C83" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D83">
         <v>0.23</v>
@@ -4026,7 +4068,7 @@
         <v>16</v>
       </c>
       <c r="L83" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4034,10 +4076,10 @@
         <v>66</v>
       </c>
       <c r="B84" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C84" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D84">
         <v>0.21</v>
@@ -4061,7 +4103,7 @@
         <v>8</v>
       </c>
       <c r="L84" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4069,10 +4111,10 @@
         <v>66</v>
       </c>
       <c r="B85" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C85" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D85">
         <v>0.07000000000000001</v>
@@ -4096,7 +4138,7 @@
         <v>7</v>
       </c>
       <c r="L85" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4104,10 +4146,10 @@
         <v>67</v>
       </c>
       <c r="B86" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="C86" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D86">
         <v>0.11</v>
@@ -4131,7 +4173,7 @@
         <v>27</v>
       </c>
       <c r="L86" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4139,10 +4181,10 @@
         <v>67</v>
       </c>
       <c r="B87" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C87" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D87">
         <v>0.12</v>
@@ -4166,7 +4208,7 @@
         <v>14</v>
       </c>
       <c r="L87" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4174,10 +4216,10 @@
         <v>67</v>
       </c>
       <c r="B88" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="C88" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D88">
         <v>0.45</v>
@@ -4201,7 +4243,7 @@
         <v>4</v>
       </c>
       <c r="L88" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4209,10 +4251,10 @@
         <v>67</v>
       </c>
       <c r="B89" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C89" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D89">
         <v>0.33</v>
@@ -4236,7 +4278,7 @@
         <v>13</v>
       </c>
       <c r="L89" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4244,10 +4286,10 @@
         <v>67</v>
       </c>
       <c r="B90" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C90" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D90">
         <v>0.09</v>
@@ -4271,7 +4313,7 @@
         <v>19</v>
       </c>
       <c r="L90" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4279,10 +4321,10 @@
         <v>67</v>
       </c>
       <c r="B91" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C91" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D91">
         <v>0.15</v>
@@ -4306,7 +4348,7 @@
         <v>17</v>
       </c>
       <c r="L91" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4314,10 +4356,10 @@
         <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C92" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D92">
         <v>0.15</v>
@@ -4341,7 +4383,7 @@
         <v>17</v>
       </c>
       <c r="L92" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4349,10 +4391,10 @@
         <v>67</v>
       </c>
       <c r="B93" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C93" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D93">
         <v>0.15</v>
@@ -4376,7 +4418,7 @@
         <v>11</v>
       </c>
       <c r="L93" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4384,10 +4426,10 @@
         <v>68</v>
       </c>
       <c r="B94" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C94" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D94">
         <v>0.43</v>
@@ -4411,7 +4453,7 @@
         <v>23</v>
       </c>
       <c r="L94" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4419,10 +4461,10 @@
         <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C95" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D95">
         <v>0.19</v>
@@ -4446,7 +4488,7 @@
         <v>14</v>
       </c>
       <c r="L95" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4454,10 +4496,10 @@
         <v>68</v>
       </c>
       <c r="B96" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C96" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D96">
         <v>0.17</v>
@@ -4481,7 +4523,7 @@
         <v>13</v>
       </c>
       <c r="L96" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4489,10 +4531,10 @@
         <v>68</v>
       </c>
       <c r="B97" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C97" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D97">
         <v>0.27</v>
@@ -4516,7 +4558,7 @@
         <v>21</v>
       </c>
       <c r="L97" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4524,10 +4566,10 @@
         <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C98" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D98">
         <v>0.08</v>
@@ -4551,7 +4593,7 @@
         <v>18</v>
       </c>
       <c r="L98" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4559,10 +4601,10 @@
         <v>69</v>
       </c>
       <c r="B99" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C99" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D99">
         <v>0.1</v>
@@ -4586,7 +4628,7 @@
         <v>23</v>
       </c>
       <c r="L99" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4594,10 +4636,10 @@
         <v>69</v>
       </c>
       <c r="B100" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C100" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D100">
         <v>0.67</v>
@@ -4621,7 +4663,7 @@
         <v>19</v>
       </c>
       <c r="L100" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4629,10 +4671,10 @@
         <v>69</v>
       </c>
       <c r="B101" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C101" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D101">
         <v>0.14</v>
@@ -4656,7 +4698,7 @@
         <v>19</v>
       </c>
       <c r="L101" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4664,10 +4706,10 @@
         <v>69</v>
       </c>
       <c r="B102" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C102" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D102">
         <v>0.12</v>
@@ -4691,7 +4733,7 @@
         <v>7</v>
       </c>
       <c r="L102" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4699,10 +4741,10 @@
         <v>69</v>
       </c>
       <c r="B103" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C103" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D103">
         <v>0.24</v>
@@ -4726,7 +4768,7 @@
         <v>19</v>
       </c>
       <c r="L103" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4734,10 +4776,10 @@
         <v>69</v>
       </c>
       <c r="B104" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C104" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D104">
         <v>0.11</v>
@@ -4761,7 +4803,7 @@
         <v>19</v>
       </c>
       <c r="L104" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4769,10 +4811,10 @@
         <v>70</v>
       </c>
       <c r="B105" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="C105" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D105">
         <v>0.12</v>
@@ -4796,7 +4838,7 @@
         <v>17</v>
       </c>
       <c r="L105" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -4804,10 +4846,10 @@
         <v>70</v>
       </c>
       <c r="B106" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C106" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D106">
         <v>0.57</v>
@@ -4831,7 +4873,7 @@
         <v>21</v>
       </c>
       <c r="L106" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -4839,10 +4881,10 @@
         <v>71</v>
       </c>
       <c r="B107" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C107" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D107">
         <v>0.14</v>
@@ -4866,7 +4908,7 @@
         <v>19</v>
       </c>
       <c r="L107" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -4874,10 +4916,10 @@
         <v>71</v>
       </c>
       <c r="B108" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C108" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D108">
         <v>0.32</v>
@@ -4901,7 +4943,7 @@
         <v>17</v>
       </c>
       <c r="L108" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -4909,10 +4951,10 @@
         <v>71</v>
       </c>
       <c r="B109" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="C109" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D109">
         <v>0.19</v>
@@ -4936,7 +4978,7 @@
         <v>27</v>
       </c>
       <c r="L109" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -4944,10 +4986,10 @@
         <v>72</v>
       </c>
       <c r="B110" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C110" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D110">
         <v>0.1</v>
@@ -4971,7 +5013,7 @@
         <v>4</v>
       </c>
       <c r="L110" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -4979,10 +5021,10 @@
         <v>72</v>
       </c>
       <c r="B111" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C111" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D111">
         <v>0.17</v>
@@ -5006,7 +5048,7 @@
         <v>13</v>
       </c>
       <c r="L111" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -5014,10 +5056,10 @@
         <v>72</v>
       </c>
       <c r="B112" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C112" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D112">
         <v>0.18</v>
@@ -5041,7 +5083,7 @@
         <v>19</v>
       </c>
       <c r="L112" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -5049,10 +5091,10 @@
         <v>72</v>
       </c>
       <c r="B113" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C113" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D113">
         <v>0.25</v>
@@ -5076,7 +5118,7 @@
         <v>17</v>
       </c>
       <c r="L113" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -5084,10 +5126,10 @@
         <v>72</v>
       </c>
       <c r="B114" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C114" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D114">
         <v>0.25</v>
@@ -5111,7 +5153,7 @@
         <v>17</v>
       </c>
       <c r="L114" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -5119,10 +5161,10 @@
         <v>72</v>
       </c>
       <c r="B115" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C115" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D115">
         <v>0.24</v>
@@ -5146,7 +5188,7 @@
         <v>11</v>
       </c>
       <c r="L115" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -5154,10 +5196,10 @@
         <v>73</v>
       </c>
       <c r="B116" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C116" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D116">
         <v>0.22</v>
@@ -5181,7 +5223,7 @@
         <v>23</v>
       </c>
       <c r="L116" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -5189,10 +5231,10 @@
         <v>73</v>
       </c>
       <c r="B117" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="C117" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D117">
         <v>0.71</v>
@@ -5216,7 +5258,7 @@
         <v>19</v>
       </c>
       <c r="L117" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -5224,10 +5266,10 @@
         <v>74</v>
       </c>
       <c r="B118" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C118" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D118">
         <v>0.11</v>
@@ -5251,7 +5293,7 @@
         <v>11</v>
       </c>
       <c r="L118" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -5259,10 +5301,10 @@
         <v>74</v>
       </c>
       <c r="B119" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C119" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D119">
         <v>0.21</v>
@@ -5286,7 +5328,7 @@
         <v>8</v>
       </c>
       <c r="L119" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -5294,10 +5336,10 @@
         <v>74</v>
       </c>
       <c r="B120" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="C120" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D120">
         <v>0.23</v>
@@ -5321,7 +5363,7 @@
         <v>8</v>
       </c>
       <c r="L120" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -5329,10 +5371,10 @@
         <v>74</v>
       </c>
       <c r="B121" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C121" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D121">
         <v>0.2</v>
@@ -5356,7 +5398,7 @@
         <v>7</v>
       </c>
       <c r="L121" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -5364,10 +5406,10 @@
         <v>74</v>
       </c>
       <c r="B122" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C122" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D122">
         <v>0.07000000000000001</v>
@@ -5391,7 +5433,7 @@
         <v>23</v>
       </c>
       <c r="L122" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -5399,10 +5441,10 @@
         <v>74</v>
       </c>
       <c r="B123" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C123" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D123">
         <v>0.39</v>
@@ -5426,7 +5468,7 @@
         <v>17</v>
       </c>
       <c r="L123" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -5434,10 +5476,10 @@
         <v>75</v>
       </c>
       <c r="B124" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C124" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D124">
         <v>0.41</v>
@@ -5461,7 +5503,7 @@
         <v>17</v>
       </c>
       <c r="L124" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5469,10 +5511,10 @@
         <v>75</v>
       </c>
       <c r="B125" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C125" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D125">
         <v>0.23</v>
@@ -5496,7 +5538,7 @@
         <v>19</v>
       </c>
       <c r="L125" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -5504,10 +5546,10 @@
         <v>76</v>
       </c>
       <c r="B126" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C126" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D126">
         <v>0.22</v>
@@ -5531,7 +5573,7 @@
         <v>7</v>
       </c>
       <c r="L126" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -5539,10 +5581,10 @@
         <v>76</v>
       </c>
       <c r="B127" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C127" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D127">
         <v>0.29</v>
@@ -5566,7 +5608,7 @@
         <v>19</v>
       </c>
       <c r="L127" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -5574,10 +5616,10 @@
         <v>77</v>
       </c>
       <c r="B128" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="C128" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D128">
         <v>0.23</v>
@@ -5601,7 +5643,7 @@
         <v>17</v>
       </c>
       <c r="L128" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -5609,10 +5651,10 @@
         <v>77</v>
       </c>
       <c r="B129" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="C129" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D129">
         <v>0.3</v>
@@ -5636,7 +5678,7 @@
         <v>17</v>
       </c>
       <c r="L129" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="130" spans="1:12">
@@ -5644,10 +5686,10 @@
         <v>78</v>
       </c>
       <c r="B130" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C130" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D130">
         <v>0.2</v>
@@ -5671,7 +5713,7 @@
         <v>7</v>
       </c>
       <c r="L130" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -5679,10 +5721,10 @@
         <v>79</v>
       </c>
       <c r="B131" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C131" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D131">
         <v>0.15</v>
@@ -5706,7 +5748,7 @@
         <v>7</v>
       </c>
       <c r="L131" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="132" spans="1:12">
@@ -5714,10 +5756,10 @@
         <v>80</v>
       </c>
       <c r="B132" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C132" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D132">
         <v>0.08</v>
@@ -5741,7 +5783,7 @@
         <v>18</v>
       </c>
       <c r="L132" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="133" spans="1:12">
@@ -5749,10 +5791,10 @@
         <v>81</v>
       </c>
       <c r="B133" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C133" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D133">
         <v>0.4</v>
@@ -5776,7 +5818,7 @@
         <v>23</v>
       </c>
       <c r="L133" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="134" spans="1:12">
@@ -5784,10 +5826,10 @@
         <v>82</v>
       </c>
       <c r="B134" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C134" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D134">
         <v>0.43</v>
@@ -5811,7 +5853,7 @@
         <v>11</v>
       </c>
       <c r="L134" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="135" spans="1:12">
@@ -5819,10 +5861,10 @@
         <v>83</v>
       </c>
       <c r="B135" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C135" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D135">
         <v>0.26</v>
@@ -5846,7 +5888,7 @@
         <v>17</v>
       </c>
       <c r="L135" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="136" spans="1:12">
@@ -5854,10 +5896,10 @@
         <v>84</v>
       </c>
       <c r="B136" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C136" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D136">
         <v>0.29</v>
@@ -5881,7 +5923,7 @@
         <v>23</v>
       </c>
       <c r="L136" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="137" spans="1:12">
@@ -5889,10 +5931,10 @@
         <v>85</v>
       </c>
       <c r="B137" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C137" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D137">
         <v>0.52</v>
@@ -5916,7 +5958,7 @@
         <v>18</v>
       </c>
       <c r="L137" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="138" spans="1:12">
@@ -5924,10 +5966,10 @@
         <v>86</v>
       </c>
       <c r="B138" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C138" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D138">
         <v>0.16</v>
@@ -5951,7 +5993,7 @@
         <v>3</v>
       </c>
       <c r="L138" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="139" spans="1:12">
@@ -5959,10 +6001,10 @@
         <v>86</v>
       </c>
       <c r="B139" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C139" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D139">
         <v>1.28</v>
@@ -5986,7 +6028,7 @@
         <v>11</v>
       </c>
       <c r="L139" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="140" spans="1:12">
@@ -5994,10 +6036,10 @@
         <v>87</v>
       </c>
       <c r="B140" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C140" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D140">
         <v>0.33</v>
@@ -6021,7 +6063,7 @@
         <v>11</v>
       </c>
       <c r="L140" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="141" spans="1:12">
@@ -6029,10 +6071,10 @@
         <v>88</v>
       </c>
       <c r="B141" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C141" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D141">
         <v>0.57</v>
@@ -6056,7 +6098,7 @@
         <v>13</v>
       </c>
       <c r="L141" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="142" spans="1:12">
@@ -6064,10 +6106,10 @@
         <v>89</v>
       </c>
       <c r="B142" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C142" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D142">
         <v>0.95</v>
@@ -6091,7 +6133,7 @@
         <v>16</v>
       </c>
       <c r="L142" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="143" spans="1:12">
@@ -6099,10 +6141,10 @@
         <v>90</v>
       </c>
       <c r="B143" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C143" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D143">
         <v>0.67</v>
@@ -6126,7 +6168,7 @@
         <v>11</v>
       </c>
       <c r="L143" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="144" spans="1:12">
@@ -6134,10 +6176,10 @@
         <v>91</v>
       </c>
       <c r="B144" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C144" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D144">
         <v>0.12</v>
@@ -6161,7 +6203,7 @@
         <v>9</v>
       </c>
       <c r="L144" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="145" spans="1:12">
@@ -6169,10 +6211,10 @@
         <v>92</v>
       </c>
       <c r="B145" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C145" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D145">
         <v>0.49</v>
@@ -6196,7 +6238,7 @@
         <v>18</v>
       </c>
       <c r="L145" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="146" spans="1:12">
@@ -6204,10 +6246,10 @@
         <v>93</v>
       </c>
       <c r="B146" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C146" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D146">
         <v>0.83</v>
@@ -6231,7 +6273,7 @@
         <v>19</v>
       </c>
       <c r="L146" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="147" spans="1:12">
@@ -6239,10 +6281,10 @@
         <v>94</v>
       </c>
       <c r="B147" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C147" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D147">
         <v>0.64</v>
@@ -6266,7 +6308,7 @@
         <v>23</v>
       </c>
       <c r="L147" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="148" spans="1:12">
@@ -6274,10 +6316,10 @@
         <v>95</v>
       </c>
       <c r="B148" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C148" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D148">
         <v>0.4</v>
@@ -6301,7 +6343,7 @@
         <v>18</v>
       </c>
       <c r="L148" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:12">
@@ -6309,10 +6351,10 @@
         <v>95</v>
       </c>
       <c r="B149" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C149" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D149">
         <v>1.02</v>
@@ -6336,7 +6378,7 @@
         <v>13</v>
       </c>
       <c r="L149" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="150" spans="1:12">
@@ -6344,10 +6386,10 @@
         <v>96</v>
       </c>
       <c r="B150" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C150" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D150">
         <v>0.6899999999999999</v>
@@ -6371,7 +6413,7 @@
         <v>13</v>
       </c>
       <c r="L150" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="151" spans="1:12">
@@ -6379,10 +6421,10 @@
         <v>97</v>
       </c>
       <c r="B151" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C151" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D151">
         <v>1.36</v>
@@ -6406,7 +6448,7 @@
         <v>17</v>
       </c>
       <c r="L151" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="152" spans="1:12">
@@ -6414,10 +6456,10 @@
         <v>98</v>
       </c>
       <c r="B152" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="C152" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D152">
         <v>0.14</v>
@@ -6441,7 +6483,7 @@
         <v>9</v>
       </c>
       <c r="L152" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="153" spans="1:12">
@@ -6449,10 +6491,10 @@
         <v>99</v>
       </c>
       <c r="B153" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C153" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D153">
         <v>0.08</v>
@@ -6476,7 +6518,7 @@
         <v>4</v>
       </c>
       <c r="L153" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="154" spans="1:12">
@@ -6484,10 +6526,10 @@
         <v>99</v>
       </c>
       <c r="B154" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C154" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D154">
         <v>0.77</v>
@@ -6511,7 +6553,7 @@
         <v>11</v>
       </c>
       <c r="L154" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="155" spans="1:12">
@@ -6519,10 +6561,10 @@
         <v>100</v>
       </c>
       <c r="B155" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C155" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D155">
         <v>0.76</v>
@@ -6546,7 +6588,7 @@
         <v>10</v>
       </c>
       <c r="L155" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="156" spans="1:12">
@@ -6554,10 +6596,10 @@
         <v>101</v>
       </c>
       <c r="B156" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="C156" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D156">
         <v>0.14</v>
@@ -6581,7 +6623,7 @@
         <v>9</v>
       </c>
       <c r="L156" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="157" spans="1:12">
@@ -6589,10 +6631,10 @@
         <v>102</v>
       </c>
       <c r="B157" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C157" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D157">
         <v>0.05</v>
@@ -6616,7 +6658,7 @@
         <v>7</v>
       </c>
       <c r="L157" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="158" spans="1:12">
@@ -6624,10 +6666,10 @@
         <v>103</v>
       </c>
       <c r="B158" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C158" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D158">
         <v>0.83</v>
@@ -6651,7 +6693,7 @@
         <v>18</v>
       </c>
       <c r="L158" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="159" spans="1:12">
@@ -6659,10 +6701,10 @@
         <v>104</v>
       </c>
       <c r="B159" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C159" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D159">
         <v>1.31</v>
@@ -6686,7 +6728,7 @@
         <v>14</v>
       </c>
       <c r="L159" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="160" spans="1:12">
@@ -6694,10 +6736,10 @@
         <v>105</v>
       </c>
       <c r="B160" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C160" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D160">
         <v>0.68</v>
@@ -6721,7 +6763,7 @@
         <v>23</v>
       </c>
       <c r="L160" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="161" spans="1:12">
@@ -6729,10 +6771,10 @@
         <v>106</v>
       </c>
       <c r="B161" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C161" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D161">
         <v>0.18</v>
@@ -6756,7 +6798,7 @@
         <v>13</v>
       </c>
       <c r="L161" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="162" spans="1:12">
@@ -6764,10 +6806,10 @@
         <v>107</v>
       </c>
       <c r="B162" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="C162" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D162">
         <v>0.38</v>
@@ -6791,7 +6833,7 @@
         <v>17</v>
       </c>
       <c r="L162" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="163" spans="1:12">
@@ -6799,10 +6841,10 @@
         <v>108</v>
       </c>
       <c r="B163" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C163" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D163">
         <v>0.07000000000000001</v>
@@ -6826,7 +6868,7 @@
         <v>17</v>
       </c>
       <c r="L163" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="164" spans="1:12">
@@ -6834,10 +6876,10 @@
         <v>109</v>
       </c>
       <c r="B164" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C164" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D164">
         <v>1.03</v>
@@ -6861,7 +6903,7 @@
         <v>19</v>
       </c>
       <c r="L164" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="165" spans="1:12">
@@ -6869,10 +6911,10 @@
         <v>110</v>
       </c>
       <c r="B165" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C165" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D165">
         <v>0.13</v>
@@ -6896,7 +6938,7 @@
         <v>17</v>
       </c>
       <c r="L165" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="166" spans="1:12">
@@ -6904,10 +6946,10 @@
         <v>110</v>
       </c>
       <c r="B166" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C166" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D166">
         <v>0.07000000000000001</v>
@@ -6931,7 +6973,7 @@
         <v>7</v>
       </c>
       <c r="L166" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="167" spans="1:12">
@@ -6939,10 +6981,10 @@
         <v>111</v>
       </c>
       <c r="B167" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C167" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D167">
         <v>1.73</v>
@@ -6966,7 +7008,7 @@
         <v>17</v>
       </c>
       <c r="L167" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="168" spans="1:12">
@@ -6974,10 +7016,10 @@
         <v>111</v>
       </c>
       <c r="B168" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C168" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D168">
         <v>0.75</v>
@@ -7001,7 +7043,7 @@
         <v>19</v>
       </c>
       <c r="L168" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="169" spans="1:12">
@@ -7009,10 +7051,10 @@
         <v>112</v>
       </c>
       <c r="B169" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C169" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D169">
         <v>0.89</v>
@@ -7036,7 +7078,7 @@
         <v>13</v>
       </c>
       <c r="L169" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="170" spans="1:12">
@@ -7044,10 +7086,10 @@
         <v>113</v>
       </c>
       <c r="B170" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C170" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D170">
         <v>1.22</v>
@@ -7071,7 +7113,7 @@
         <v>12</v>
       </c>
       <c r="L170" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="171" spans="1:12">
@@ -7079,10 +7121,10 @@
         <v>114</v>
       </c>
       <c r="B171" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C171" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D171">
         <v>0.16</v>
@@ -7106,7 +7148,7 @@
         <v>4</v>
       </c>
       <c r="L171" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="172" spans="1:12">
@@ -7114,10 +7156,10 @@
         <v>115</v>
       </c>
       <c r="B172" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C172" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D172">
         <v>0.52</v>
@@ -7141,7 +7183,7 @@
         <v>11</v>
       </c>
       <c r="L172" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="173" spans="1:12">
@@ -7149,10 +7191,10 @@
         <v>115</v>
       </c>
       <c r="B173" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C173" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D173">
         <v>0.13</v>
@@ -7176,7 +7218,7 @@
         <v>17</v>
       </c>
       <c r="L173" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="174" spans="1:12">
@@ -7184,10 +7226,10 @@
         <v>116</v>
       </c>
       <c r="B174" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C174" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D174">
         <v>0.17</v>
@@ -7211,7 +7253,7 @@
         <v>21</v>
       </c>
       <c r="L174" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="175" spans="1:12">
@@ -7219,10 +7261,10 @@
         <v>117</v>
       </c>
       <c r="B175" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="C175" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D175">
         <v>0.29</v>
@@ -7246,7 +7288,7 @@
         <v>9</v>
       </c>
       <c r="L175" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="176" spans="1:12">
@@ -7254,10 +7296,10 @@
         <v>118</v>
       </c>
       <c r="B176" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C176" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D176">
         <v>0.75</v>
@@ -7281,7 +7323,7 @@
         <v>21</v>
       </c>
       <c r="L176" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="177" spans="1:12">
@@ -7289,10 +7331,10 @@
         <v>119</v>
       </c>
       <c r="B177" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C177" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D177">
         <v>0.63</v>
@@ -7316,7 +7358,7 @@
         <v>17</v>
       </c>
       <c r="L177" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -7324,10 +7366,10 @@
         <v>120</v>
       </c>
       <c r="B178" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C178" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D178">
         <v>0.95</v>
@@ -7351,7 +7393,7 @@
         <v>14</v>
       </c>
       <c r="L178" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="179" spans="1:12">
@@ -7359,10 +7401,10 @@
         <v>121</v>
       </c>
       <c r="B179" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C179" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D179">
         <v>0.8100000000000001</v>
@@ -7386,7 +7428,7 @@
         <v>18</v>
       </c>
       <c r="L179" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="180" spans="1:12">
@@ -7394,10 +7436,10 @@
         <v>122</v>
       </c>
       <c r="B180" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C180" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D180">
         <v>0.27</v>
@@ -7421,7 +7463,7 @@
         <v>13</v>
       </c>
       <c r="L180" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="181" spans="1:12">
@@ -7429,10 +7471,10 @@
         <v>123</v>
       </c>
       <c r="B181" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C181" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D181">
         <v>0.07000000000000001</v>
@@ -7456,7 +7498,7 @@
         <v>23</v>
       </c>
       <c r="L181" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="182" spans="1:12">
@@ -7464,10 +7506,10 @@
         <v>124</v>
       </c>
       <c r="B182" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C182" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D182">
         <v>1.66</v>
@@ -7491,7 +7533,7 @@
         <v>13</v>
       </c>
       <c r="L182" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="183" spans="1:12">
@@ -7499,10 +7541,10 @@
         <v>125</v>
       </c>
       <c r="B183" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C183" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D183">
         <v>0.49</v>
@@ -7526,7 +7568,7 @@
         <v>23</v>
       </c>
       <c r="L183" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="184" spans="1:12">
@@ -7534,10 +7576,10 @@
         <v>125</v>
       </c>
       <c r="B184" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C184" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D184">
         <v>0.49</v>
@@ -7561,7 +7603,7 @@
         <v>23</v>
       </c>
       <c r="L184" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -7569,10 +7611,10 @@
         <v>126</v>
       </c>
       <c r="B185" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C185" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D185">
         <v>1.73</v>
@@ -7596,7 +7638,7 @@
         <v>17</v>
       </c>
       <c r="L185" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="186" spans="1:12">
@@ -7604,10 +7646,10 @@
         <v>127</v>
       </c>
       <c r="B186" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C186" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D186">
         <v>0.27</v>
@@ -7631,7 +7673,7 @@
         <v>17</v>
       </c>
       <c r="L186" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="187" spans="1:12">
@@ -7639,10 +7681,10 @@
         <v>127</v>
       </c>
       <c r="B187" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C187" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D187">
         <v>0.14</v>
@@ -7666,7 +7708,7 @@
         <v>7</v>
       </c>
       <c r="L187" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="188" spans="1:12">
@@ -7674,10 +7716,10 @@
         <v>128</v>
       </c>
       <c r="B188" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="C188" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D188">
         <v>0.15</v>
@@ -7701,7 +7743,7 @@
         <v>16</v>
       </c>
       <c r="L188" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -7709,10 +7751,10 @@
         <v>128</v>
       </c>
       <c r="B189" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C189" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D189">
         <v>0.13</v>
@@ -7736,7 +7778,7 @@
         <v>21</v>
       </c>
       <c r="L189" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -7744,10 +7786,10 @@
         <v>129</v>
       </c>
       <c r="B190" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C190" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D190">
         <v>0.89</v>
@@ -7771,7 +7813,7 @@
         <v>18</v>
       </c>
       <c r="L190" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -7779,10 +7821,10 @@
         <v>130</v>
       </c>
       <c r="B191" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C191" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D191">
         <v>0.25</v>
@@ -7806,7 +7848,7 @@
         <v>4</v>
       </c>
       <c r="L191" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -7814,10 +7856,10 @@
         <v>130</v>
       </c>
       <c r="B192" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C192" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D192">
         <v>0.91</v>
@@ -7841,7 +7883,7 @@
         <v>11</v>
       </c>
       <c r="L192" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -7849,10 +7891,10 @@
         <v>131</v>
       </c>
       <c r="B193" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C193" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D193">
         <v>2.38</v>
@@ -7876,7 +7918,7 @@
         <v>15</v>
       </c>
       <c r="L193" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -7884,10 +7926,10 @@
         <v>132</v>
       </c>
       <c r="B194" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C194" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D194">
         <v>0.18</v>
@@ -7911,7 +7953,7 @@
         <v>7</v>
       </c>
       <c r="L194" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -7919,10 +7961,10 @@
         <v>132</v>
       </c>
       <c r="B195" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="C195" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D195">
         <v>0.29</v>
@@ -7946,7 +7988,7 @@
         <v>7</v>
       </c>
       <c r="L195" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -7954,10 +7996,10 @@
         <v>133</v>
       </c>
       <c r="B196" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C196" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D196">
         <v>0.38</v>
@@ -7981,7 +8023,7 @@
         <v>15</v>
       </c>
       <c r="L196" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -7989,10 +8031,10 @@
         <v>134</v>
       </c>
       <c r="B197" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C197" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D197">
         <v>0.38</v>
@@ -8016,7 +8058,7 @@
         <v>21</v>
       </c>
       <c r="L197" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="198" spans="1:12">
@@ -8024,10 +8066,10 @@
         <v>134</v>
       </c>
       <c r="B198" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C198" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D198">
         <v>0.5600000000000001</v>
@@ -8051,7 +8093,7 @@
         <v>19</v>
       </c>
       <c r="L198" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="199" spans="1:12">
@@ -8059,10 +8101,10 @@
         <v>134</v>
       </c>
       <c r="B199" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C199" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D199">
         <v>0.58</v>
@@ -8086,7 +8128,7 @@
         <v>19</v>
       </c>
       <c r="L199" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -8094,10 +8136,10 @@
         <v>135</v>
       </c>
       <c r="B200" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C200" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D200">
         <v>0.14</v>
@@ -8121,7 +8163,7 @@
         <v>5</v>
       </c>
       <c r="L200" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -8129,10 +8171,10 @@
         <v>135</v>
       </c>
       <c r="B201" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="C201" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D201">
         <v>0.21</v>
@@ -8156,7 +8198,7 @@
         <v>27</v>
       </c>
       <c r="L201" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -8164,10 +8206,10 @@
         <v>136</v>
       </c>
       <c r="B202" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C202" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D202">
         <v>0.45</v>
@@ -8191,7 +8233,7 @@
         <v>17</v>
       </c>
       <c r="L202" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="203" spans="1:12">
@@ -8199,10 +8241,10 @@
         <v>136</v>
       </c>
       <c r="B203" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C203" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D203">
         <v>0.45</v>
@@ -8226,7 +8268,7 @@
         <v>17</v>
       </c>
       <c r="L203" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="204" spans="1:12">
@@ -8234,10 +8276,10 @@
         <v>136</v>
       </c>
       <c r="B204" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C204" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D204">
         <v>0.3</v>
@@ -8261,7 +8303,7 @@
         <v>7</v>
       </c>
       <c r="L204" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -8269,10 +8311,10 @@
         <v>137</v>
       </c>
       <c r="B205" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C205" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D205">
         <v>0.13</v>
@@ -8296,7 +8338,7 @@
         <v>23</v>
       </c>
       <c r="L205" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="206" spans="1:12">
@@ -8304,10 +8346,10 @@
         <v>137</v>
       </c>
       <c r="B206" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C206" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D206">
         <v>0.27</v>
@@ -8331,7 +8373,7 @@
         <v>19</v>
       </c>
       <c r="L206" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="207" spans="1:12">
@@ -8339,10 +8381,10 @@
         <v>138</v>
       </c>
       <c r="B207" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C207" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D207">
         <v>0.33</v>
@@ -8366,7 +8408,7 @@
         <v>11</v>
       </c>
       <c r="L207" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -8374,10 +8416,10 @@
         <v>139</v>
       </c>
       <c r="B208" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="C208" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D208">
         <v>0.15</v>
@@ -8401,7 +8443,7 @@
         <v>27</v>
       </c>
       <c r="L208" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -8409,10 +8451,10 @@
         <v>139</v>
       </c>
       <c r="B209" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C209" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D209">
         <v>0.17</v>
@@ -8436,7 +8478,7 @@
         <v>19</v>
       </c>
       <c r="L209" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -8444,10 +8486,10 @@
         <v>140</v>
       </c>
       <c r="B210" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C210" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D210">
         <v>0.23</v>
@@ -8471,7 +8513,7 @@
         <v>17</v>
       </c>
       <c r="L210" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -8479,10 +8521,10 @@
         <v>140</v>
       </c>
       <c r="B211" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C211" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D211">
         <v>0.36</v>
@@ -8506,7 +8548,7 @@
         <v>19</v>
       </c>
       <c r="L211" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -8514,10 +8556,10 @@
         <v>141</v>
       </c>
       <c r="B212" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C212" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D212">
         <v>0.21</v>
@@ -8541,7 +8583,7 @@
         <v>23</v>
       </c>
       <c r="L212" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -8549,10 +8591,10 @@
         <v>142</v>
       </c>
       <c r="B213" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C213" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D213">
         <v>0.21</v>
@@ -8576,7 +8618,7 @@
         <v>23</v>
       </c>
       <c r="L213" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -8584,10 +8626,10 @@
         <v>143</v>
       </c>
       <c r="B214" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="C214" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D214">
         <v>0.35</v>
@@ -8611,7 +8653,7 @@
         <v>17</v>
       </c>
       <c r="L214" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -8619,10 +8661,10 @@
         <v>143</v>
       </c>
       <c r="B215" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="C215" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D215">
         <v>1.43</v>
@@ -8646,7 +8688,7 @@
         <v>17</v>
       </c>
       <c r="L215" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -8654,10 +8696,10 @@
         <v>144</v>
       </c>
       <c r="B216" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C216" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D216">
         <v>0.21</v>
@@ -8681,7 +8723,7 @@
         <v>21</v>
       </c>
       <c r="L216" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="217" spans="1:12">
@@ -8689,10 +8731,10 @@
         <v>144</v>
       </c>
       <c r="B217" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="C217" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D217">
         <v>0.23</v>
@@ -8716,7 +8758,7 @@
         <v>5</v>
       </c>
       <c r="L217" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -8724,10 +8766,10 @@
         <v>144</v>
       </c>
       <c r="B218" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C218" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D218">
         <v>0.5</v>
@@ -8751,7 +8793,7 @@
         <v>13</v>
       </c>
       <c r="L218" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="219" spans="1:12">
@@ -8759,10 +8801,10 @@
         <v>145</v>
       </c>
       <c r="B219" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C219" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D219">
         <v>0.26</v>
@@ -8786,7 +8828,7 @@
         <v>14</v>
       </c>
       <c r="L219" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="220" spans="1:12">
@@ -8794,10 +8836,10 @@
         <v>145</v>
       </c>
       <c r="B220" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C220" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D220">
         <v>0.18</v>
@@ -8821,7 +8863,7 @@
         <v>15</v>
       </c>
       <c r="L220" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="221" spans="1:12">
@@ -8829,10 +8871,10 @@
         <v>146</v>
       </c>
       <c r="B221" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C221" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D221">
         <v>0.14</v>
@@ -8856,7 +8898,7 @@
         <v>23</v>
       </c>
       <c r="L221" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="222" spans="1:12">
@@ -8864,10 +8906,10 @@
         <v>146</v>
       </c>
       <c r="B222" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C222" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D222">
         <v>0.39</v>
@@ -8891,7 +8933,7 @@
         <v>19</v>
       </c>
       <c r="L222" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="223" spans="1:12">
@@ -8899,10 +8941,10 @@
         <v>146</v>
       </c>
       <c r="B223" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C223" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D223">
         <v>0.47</v>
@@ -8926,7 +8968,7 @@
         <v>19</v>
       </c>
       <c r="L223" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="224" spans="1:12">
@@ -8934,10 +8976,10 @@
         <v>147</v>
       </c>
       <c r="B224" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="C224" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D224">
         <v>0.42</v>
@@ -8961,7 +9003,7 @@
         <v>7</v>
       </c>
       <c r="L224" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="225" spans="1:12">
@@ -8969,10 +9011,10 @@
         <v>148</v>
       </c>
       <c r="B225" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C225" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D225">
         <v>0.18</v>
@@ -8996,7 +9038,7 @@
         <v>19</v>
       </c>
       <c r="L225" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="226" spans="1:12">
@@ -9004,10 +9046,10 @@
         <v>148</v>
       </c>
       <c r="B226" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C226" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D226">
         <v>0.24</v>
@@ -9031,7 +9073,7 @@
         <v>11</v>
       </c>
       <c r="L226" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="227" spans="1:12">
@@ -9039,10 +9081,10 @@
         <v>149</v>
       </c>
       <c r="B227" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C227" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D227">
         <v>0.09</v>
@@ -9066,7 +9108,7 @@
         <v>23</v>
       </c>
       <c r="L227" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="228" spans="1:12">
@@ -9074,10 +9116,10 @@
         <v>149</v>
       </c>
       <c r="B228" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C228" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D228">
         <v>0.35</v>
@@ -9101,7 +9143,7 @@
         <v>17</v>
       </c>
       <c r="L228" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="229" spans="1:12">
@@ -9109,10 +9151,10 @@
         <v>149</v>
       </c>
       <c r="B229" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C229" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D229">
         <v>0.35</v>
@@ -9136,7 +9178,7 @@
         <v>17</v>
       </c>
       <c r="L229" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="230" spans="1:12">
@@ -9144,10 +9186,10 @@
         <v>150</v>
       </c>
       <c r="B230" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C230" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D230">
         <v>0.28</v>
@@ -9171,7 +9213,7 @@
         <v>19</v>
       </c>
       <c r="L230" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="231" spans="1:12">
@@ -9179,10 +9221,10 @@
         <v>150</v>
       </c>
       <c r="B231" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C231" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D231">
         <v>0.27</v>
@@ -9206,7 +9248,7 @@
         <v>19</v>
       </c>
       <c r="L231" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="232" spans="1:12">
@@ -9214,10 +9256,10 @@
         <v>150</v>
       </c>
       <c r="B232" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="C232" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D232">
         <v>0.12</v>
@@ -9241,7 +9283,7 @@
         <v>7</v>
       </c>
       <c r="L232" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="233" spans="1:12">
@@ -9249,10 +9291,10 @@
         <v>150</v>
       </c>
       <c r="B233" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C233" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D233">
         <v>0.14</v>
@@ -9276,7 +9318,7 @@
         <v>19</v>
       </c>
       <c r="L233" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="234" spans="1:12">
@@ -9284,10 +9326,10 @@
         <v>151</v>
       </c>
       <c r="B234" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="C234" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D234">
         <v>1.14</v>
@@ -9311,7 +9353,7 @@
         <v>27</v>
       </c>
       <c r="L234" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="235" spans="1:12">
@@ -9319,10 +9361,10 @@
         <v>151</v>
       </c>
       <c r="B235" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C235" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D235">
         <v>0.33</v>
@@ -9346,7 +9388,7 @@
         <v>13</v>
       </c>
       <c r="L235" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="236" spans="1:12">
@@ -9354,10 +9396,10 @@
         <v>152</v>
       </c>
       <c r="B236" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="C236" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D236">
         <v>0.09</v>
@@ -9381,7 +9423,7 @@
         <v>23</v>
       </c>
       <c r="L236" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="237" spans="1:12">
@@ -9389,10 +9431,10 @@
         <v>153</v>
       </c>
       <c r="B237" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="C237" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D237">
         <v>0.28</v>
@@ -9416,7 +9458,7 @@
         <v>19</v>
       </c>
       <c r="L237" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="238" spans="1:12">
@@ -9424,10 +9466,10 @@
         <v>154</v>
       </c>
       <c r="B238" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C238" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D238">
         <v>0.32</v>
@@ -9451,7 +9493,7 @@
         <v>19</v>
       </c>
       <c r="L238" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
     </row>
     <row r="239" spans="1:12">
@@ -9459,10 +9501,10 @@
         <v>155</v>
       </c>
       <c r="B239" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C239" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D239">
         <v>3.29</v>
@@ -9486,7 +9528,7 @@
         <v>3</v>
       </c>
       <c r="L239" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="240" spans="1:12">
@@ -9494,10 +9536,10 @@
         <v>155</v>
       </c>
       <c r="B240" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C240" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D240">
         <v>0.2</v>
@@ -9521,7 +9563,7 @@
         <v>3</v>
       </c>
       <c r="L240" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="241" spans="1:12">
@@ -9529,10 +9571,10 @@
         <v>156</v>
       </c>
       <c r="B241" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C241" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D241">
         <v>0.76</v>
@@ -9556,7 +9598,7 @@
         <v>23</v>
       </c>
       <c r="L241" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="242" spans="1:12">
@@ -9564,10 +9606,10 @@
         <v>157</v>
       </c>
       <c r="B242" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C242" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D242">
         <v>0.32</v>
@@ -9591,7 +9633,7 @@
         <v>12</v>
       </c>
       <c r="L242" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="243" spans="1:12">
@@ -9599,10 +9641,10 @@
         <v>158</v>
       </c>
       <c r="B243" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C243" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D243">
         <v>5.43</v>
@@ -9626,7 +9668,7 @@
         <v>5</v>
       </c>
       <c r="L243" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="244" spans="1:12">
@@ -9634,10 +9676,10 @@
         <v>159</v>
       </c>
       <c r="B244" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C244" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D244">
         <v>0.4</v>
@@ -9661,7 +9703,7 @@
         <v>5</v>
       </c>
       <c r="L244" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="245" spans="1:12">
@@ -9669,10 +9711,10 @@
         <v>160</v>
       </c>
       <c r="B245" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C245" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D245">
         <v>0.11</v>
@@ -9696,7 +9738,7 @@
         <v>18</v>
       </c>
       <c r="L245" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="246" spans="1:12">
@@ -9704,10 +9746,10 @@
         <v>161</v>
       </c>
       <c r="B246" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C246" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D246">
         <v>2.57</v>
@@ -9731,7 +9773,7 @@
         <v>5</v>
       </c>
       <c r="L246" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="247" spans="1:12">
@@ -9739,10 +9781,10 @@
         <v>162</v>
       </c>
       <c r="B247" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C247" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D247">
         <v>0.5</v>
@@ -9766,7 +9808,7 @@
         <v>4</v>
       </c>
       <c r="L247" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="248" spans="1:12">
@@ -9774,10 +9816,10 @@
         <v>163</v>
       </c>
       <c r="B248" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C248" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D248">
         <v>0.22</v>
@@ -9801,7 +9843,7 @@
         <v>18</v>
       </c>
       <c r="L248" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="249" spans="1:12">
@@ -9809,10 +9851,10 @@
         <v>164</v>
       </c>
       <c r="B249" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C249" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D249">
         <v>0.17</v>
@@ -9836,7 +9878,7 @@
         <v>18</v>
       </c>
       <c r="L249" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="250" spans="1:12">
@@ -9844,10 +9886,10 @@
         <v>165</v>
       </c>
       <c r="B250" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C250" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D250">
         <v>0.6</v>
@@ -9871,7 +9913,7 @@
         <v>3</v>
       </c>
       <c r="L250" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="251" spans="1:12">
@@ -9879,10 +9921,10 @@
         <v>166</v>
       </c>
       <c r="B251" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C251" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D251">
         <v>0.28</v>
@@ -9906,7 +9948,7 @@
         <v>18</v>
       </c>
       <c r="L251" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="252" spans="1:12">
@@ -9914,10 +9956,10 @@
         <v>167</v>
       </c>
       <c r="B252" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="C252" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D252">
         <v>0.11</v>
@@ -9941,18 +9983,18 @@
         <v>18</v>
       </c>
       <c r="L252" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="253" spans="1:12">
       <c r="A253" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B253" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="C253" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D253">
         <v>2.86</v>
@@ -9976,18 +10018,18 @@
         <v>5</v>
       </c>
       <c r="L253" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="254" spans="1:12">
       <c r="A254" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B254" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C254" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D254">
         <v>0.79</v>
@@ -10005,7 +10047,7 @@
         <v>29</v>
       </c>
       <c r="L254" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="255" spans="1:12">
@@ -10013,10 +10055,10 @@
         <v>162</v>
       </c>
       <c r="B255" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C255" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D255">
         <v>0.83</v>
@@ -10034,18 +10076,18 @@
         <v>29</v>
       </c>
       <c r="L255" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="256" spans="1:12">
       <c r="A256" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B256" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C256" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="D256">
         <v>0.88</v>
@@ -10063,18 +10105,18 @@
         <v>27</v>
       </c>
       <c r="L256" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="257" spans="1:12">
       <c r="A257" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B257" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C257" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D257">
         <v>0.72</v>
@@ -10092,18 +10134,18 @@
         <v>18</v>
       </c>
       <c r="L257" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="258" spans="1:12">
       <c r="A258" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B258" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C258" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D258">
         <v>1.6</v>
@@ -10121,18 +10163,18 @@
         <v>18</v>
       </c>
       <c r="L258" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="259" spans="1:12">
       <c r="A259" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B259" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C259" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D259">
         <v>1.72</v>
@@ -10150,18 +10192,18 @@
         <v>19</v>
       </c>
       <c r="L259" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="260" spans="1:12">
       <c r="A260" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B260" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C260" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D260">
         <v>1.4</v>
@@ -10179,18 +10221,18 @@
         <v>18</v>
       </c>
       <c r="L260" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="261" spans="1:12">
       <c r="A261" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B261" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C261" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D261">
         <v>0.65</v>
@@ -10208,18 +10250,18 @@
         <v>13</v>
       </c>
       <c r="L261" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="262" spans="1:12">
       <c r="A262" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B262" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C262" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D262">
         <v>0.9399999999999999</v>
@@ -10237,18 +10279,18 @@
         <v>13</v>
       </c>
       <c r="L262" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="263" spans="1:12">
       <c r="A263" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B263" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C263" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D263">
         <v>1.88</v>
@@ -10266,18 +10308,18 @@
         <v>13</v>
       </c>
       <c r="L263" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="264" spans="1:12">
       <c r="A264" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B264" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C264" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="D264">
         <v>2.18</v>
@@ -10295,18 +10337,18 @@
         <v>12</v>
       </c>
       <c r="L264" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="265" spans="1:12">
       <c r="A265" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B265" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C265" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D265">
         <v>0.36</v>
@@ -10324,18 +10366,18 @@
         <v>18</v>
       </c>
       <c r="L265" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="266" spans="1:12">
       <c r="A266" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B266" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C266" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D266">
         <v>2.08</v>
@@ -10353,18 +10395,18 @@
         <v>18</v>
       </c>
       <c r="L266" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="267" spans="1:12">
       <c r="A267" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B267" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C267" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D267">
         <v>2.24</v>
@@ -10382,18 +10424,18 @@
         <v>18</v>
       </c>
       <c r="L267" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="268" spans="1:12">
       <c r="A268" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B268" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C268" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D268">
         <v>2</v>
@@ -10411,18 +10453,18 @@
         <v>18</v>
       </c>
       <c r="L268" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="269" spans="1:12">
       <c r="A269" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B269" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C269" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D269">
         <v>0.14</v>
@@ -10440,18 +10482,18 @@
         <v>7</v>
       </c>
       <c r="L269" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="270" spans="1:12">
       <c r="A270" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B270" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C270" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D270">
         <v>0.14</v>
@@ -10469,7 +10511,7 @@
         <v>7</v>
       </c>
       <c r="L270" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="271" spans="1:12">
@@ -10477,10 +10519,10 @@
         <v>164</v>
       </c>
       <c r="B271" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C271" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D271">
         <v>0.21</v>
@@ -10498,18 +10540,18 @@
         <v>7</v>
       </c>
       <c r="L271" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="272" spans="1:12">
       <c r="A272" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B272" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="C272" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D272">
         <v>0.14</v>
@@ -10527,18 +10569,18 @@
         <v>7</v>
       </c>
       <c r="L272" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="273" spans="1:12">
       <c r="A273" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B273" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C273" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D273">
         <v>0.15</v>
@@ -10556,7 +10598,7 @@
         <v>6</v>
       </c>
       <c r="L273" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="274" spans="1:12">
@@ -10564,10 +10606,10 @@
         <v>161</v>
       </c>
       <c r="B274" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C274" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D274">
         <v>0.31</v>
@@ -10585,18 +10627,18 @@
         <v>5</v>
       </c>
       <c r="L274" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="275" spans="1:12">
       <c r="A275" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B275" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C275" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D275">
         <v>0.46</v>
@@ -10614,7 +10656,7 @@
         <v>5</v>
       </c>
       <c r="L275" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="276" spans="1:12">
@@ -10622,10 +10664,10 @@
         <v>160</v>
       </c>
       <c r="B276" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C276" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D276">
         <v>0.63</v>
@@ -10643,18 +10685,18 @@
         <v>15</v>
       </c>
       <c r="L276" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="277" spans="1:12">
       <c r="A277" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B277" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C277" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D277">
         <v>1.52</v>
@@ -10672,7 +10714,7 @@
         <v>15</v>
       </c>
       <c r="L277" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="278" spans="1:12">
@@ -10680,10 +10722,10 @@
         <v>166</v>
       </c>
       <c r="B278" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C278" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D278">
         <v>2.11</v>
@@ -10701,18 +10743,18 @@
         <v>15</v>
       </c>
       <c r="L278" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="279" spans="1:12">
       <c r="A279" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B279" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C279" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D279">
         <v>0.18</v>
@@ -10730,18 +10772,18 @@
         <v>12</v>
       </c>
       <c r="L279" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="280" spans="1:12">
       <c r="A280" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B280" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C280" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D280">
         <v>0.42</v>
@@ -10759,18 +10801,18 @@
         <v>12</v>
       </c>
       <c r="L280" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="281" spans="1:12">
       <c r="A281" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B281" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="C281" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D281">
         <v>1.07</v>
@@ -10788,18 +10830,18 @@
         <v>12</v>
       </c>
       <c r="L281" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="282" spans="1:12">
       <c r="A282" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B282" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C282" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D282">
         <v>0.43</v>
@@ -10817,18 +10859,18 @@
         <v>9</v>
       </c>
       <c r="L282" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="283" spans="1:12">
       <c r="A283" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B283" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C283" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D283">
         <v>0.33</v>
@@ -10846,18 +10888,18 @@
         <v>9</v>
       </c>
       <c r="L283" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="284" spans="1:12">
       <c r="A284" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B284" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C284" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D284">
         <v>0.62</v>
@@ -10875,18 +10917,18 @@
         <v>9</v>
       </c>
       <c r="L284" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="285" spans="1:12">
       <c r="A285" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B285" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C285" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D285">
         <v>0.11</v>
@@ -10904,18 +10946,18 @@
         <v>11</v>
       </c>
       <c r="L285" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="286" spans="1:12">
       <c r="A286" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B286" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C286" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D286">
         <v>0.22</v>
@@ -10933,18 +10975,18 @@
         <v>11</v>
       </c>
       <c r="L286" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="287" spans="1:12">
       <c r="A287" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B287" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C287" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D287">
         <v>0.22</v>
@@ -10962,18 +11004,18 @@
         <v>9</v>
       </c>
       <c r="L287" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="288" spans="1:12">
       <c r="A288" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B288" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C288" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D288">
         <v>0.33</v>
@@ -10991,18 +11033,18 @@
         <v>9</v>
       </c>
       <c r="L288" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="289" spans="1:12">
       <c r="A289" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B289" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C289" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D289">
         <v>0.11</v>
@@ -11020,7 +11062,7 @@
         <v>9</v>
       </c>
       <c r="L289" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="290" spans="1:12">
@@ -11028,10 +11070,10 @@
         <v>163</v>
       </c>
       <c r="B290" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C290" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D290">
         <v>1.91</v>
@@ -11049,18 +11091,18 @@
         <v>11</v>
       </c>
       <c r="L290" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="291" spans="1:12">
       <c r="A291" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B291" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C291" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D291">
         <v>2.27</v>
@@ -11078,18 +11120,18 @@
         <v>12</v>
       </c>
       <c r="L291" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="292" spans="1:12">
       <c r="A292" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B292" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C292" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D292">
         <v>2.64</v>
@@ -11107,18 +11149,18 @@
         <v>16</v>
       </c>
       <c r="L292" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="293" spans="1:12">
       <c r="A293" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B293" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C293" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D293">
         <v>0.71</v>
@@ -11136,18 +11178,18 @@
         <v>5</v>
       </c>
       <c r="L293" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="294" spans="1:12">
       <c r="A294" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B294" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="C294" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D294">
         <v>0.89</v>
@@ -11165,18 +11207,18 @@
         <v>5</v>
       </c>
       <c r="L294" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="295" spans="1:12">
       <c r="A295" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B295" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="C295" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D295">
         <v>0.15</v>
@@ -11194,7 +11236,7 @@
         <v>6</v>
       </c>
       <c r="L295" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="296" spans="1:12">
@@ -11202,10 +11244,10 @@
         <v>164</v>
       </c>
       <c r="B296" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C296" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D296">
         <v>0.28</v>
@@ -11223,18 +11265,18 @@
         <v>9</v>
       </c>
       <c r="L296" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="297" spans="1:12">
       <c r="A297" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B297" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C297" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D297">
         <v>5.56</v>
@@ -11252,18 +11294,18 @@
         <v>13</v>
       </c>
       <c r="L297" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="298" spans="1:12">
       <c r="A298" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B298" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="C298" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D298">
         <v>0.19</v>
@@ -11281,7 +11323,7 @@
         <v>29</v>
       </c>
       <c r="L298" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="299" spans="1:12">
@@ -11289,10 +11331,10 @@
         <v>167</v>
       </c>
       <c r="B299" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="C299" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D299">
         <v>0.52</v>
@@ -11310,18 +11352,18 @@
         <v>29</v>
       </c>
       <c r="L299" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="300" spans="1:12">
       <c r="A300" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B300" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C300" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D300">
         <v>0.11</v>
@@ -11339,36 +11381,1109 @@
         <v>13</v>
       </c>
       <c r="L300" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
     </row>
     <row r="301" spans="1:12">
       <c r="A301" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B301" t="s">
+        <v>216</v>
+      </c>
+      <c r="C301" t="s">
+        <v>255</v>
+      </c>
+      <c r="D301">
+        <v>0.09</v>
+      </c>
+      <c r="E301">
+        <v>10.87</v>
+      </c>
+      <c r="F301">
+        <v>0</v>
+      </c>
+      <c r="G301">
+        <v>0</v>
+      </c>
+      <c r="K301">
+        <v>12</v>
+      </c>
+      <c r="L301" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="302" spans="1:12">
+      <c r="A302" t="s">
+        <v>197</v>
+      </c>
+      <c r="B302" t="s">
+        <v>219</v>
+      </c>
+      <c r="C302" t="s">
+        <v>254</v>
+      </c>
+      <c r="D302">
+        <v>2</v>
+      </c>
+      <c r="E302">
+        <v>15.7</v>
+      </c>
+      <c r="F302">
+        <v>0</v>
+      </c>
+      <c r="G302">
+        <v>4.29</v>
+      </c>
+      <c r="K302">
+        <v>9</v>
+      </c>
+      <c r="L302" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12">
+      <c r="A303" t="s">
+        <v>198</v>
+      </c>
+      <c r="B303" t="s">
+        <v>219</v>
+      </c>
+      <c r="C303" t="s">
+        <v>254</v>
+      </c>
+      <c r="D303">
+        <v>1.29</v>
+      </c>
+      <c r="E303">
+        <v>47.14</v>
+      </c>
+      <c r="F303">
+        <v>0</v>
+      </c>
+      <c r="G303">
+        <v>0</v>
+      </c>
+      <c r="K303">
+        <v>9</v>
+      </c>
+      <c r="L303" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="304" spans="1:12">
+      <c r="A304" t="s">
+        <v>199</v>
+      </c>
+      <c r="B304" t="s">
+        <v>212</v>
+      </c>
+      <c r="C304" t="s">
+        <v>251</v>
+      </c>
+      <c r="D304">
+        <v>1.76</v>
+      </c>
+      <c r="E304">
+        <v>7.06</v>
+      </c>
+      <c r="F304">
+        <v>0</v>
+      </c>
+      <c r="G304">
+        <v>0</v>
+      </c>
+      <c r="K304">
+        <v>11</v>
+      </c>
+      <c r="L304" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12">
+      <c r="A305" t="s">
+        <v>198</v>
+      </c>
+      <c r="B305" t="s">
+        <v>212</v>
+      </c>
+      <c r="C305" t="s">
+        <v>251</v>
+      </c>
+      <c r="D305">
+        <v>1.24</v>
+      </c>
+      <c r="E305">
+        <v>8.24</v>
+      </c>
+      <c r="F305">
+        <v>0</v>
+      </c>
+      <c r="G305">
+        <v>0</v>
+      </c>
+      <c r="K305">
+        <v>9</v>
+      </c>
+      <c r="L305" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12">
+      <c r="A306" t="s">
+        <v>200</v>
+      </c>
+      <c r="B306" t="s">
+        <v>238</v>
+      </c>
+      <c r="C306" t="s">
+        <v>253</v>
+      </c>
+      <c r="D306">
+        <v>0.11</v>
+      </c>
+      <c r="E306">
+        <v>6.11</v>
+      </c>
+      <c r="F306">
+        <v>0</v>
+      </c>
+      <c r="G306">
+        <v>0</v>
+      </c>
+      <c r="K306">
+        <v>7</v>
+      </c>
+      <c r="L306" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12">
+      <c r="A307" t="s">
+        <v>201</v>
+      </c>
+      <c r="B307" t="s">
+        <v>238</v>
+      </c>
+      <c r="C307" t="s">
+        <v>253</v>
+      </c>
+      <c r="D307">
+        <v>0.06</v>
+      </c>
+      <c r="E307">
+        <v>12.78</v>
+      </c>
+      <c r="F307">
+        <v>0</v>
+      </c>
+      <c r="G307">
+        <v>0</v>
+      </c>
+      <c r="K307">
+        <v>6</v>
+      </c>
+      <c r="L307" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12">
+      <c r="A308" t="s">
         <v>202</v>
       </c>
-      <c r="C301" t="s">
+      <c r="B308" t="s">
+        <v>232</v>
+      </c>
+      <c r="C308" t="s">
+        <v>255</v>
+      </c>
+      <c r="D308">
+        <v>0.3</v>
+      </c>
+      <c r="E308">
+        <v>50</v>
+      </c>
+      <c r="F308">
+        <v>0</v>
+      </c>
+      <c r="G308">
+        <v>0</v>
+      </c>
+      <c r="K308">
+        <v>3</v>
+      </c>
+      <c r="L308" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12">
+      <c r="A309" t="s">
+        <v>203</v>
+      </c>
+      <c r="B309" t="s">
+        <v>221</v>
+      </c>
+      <c r="C309" t="s">
+        <v>256</v>
+      </c>
+      <c r="D309">
+        <v>0.53</v>
+      </c>
+      <c r="E309">
+        <v>34.83</v>
+      </c>
+      <c r="F309">
+        <v>0</v>
+      </c>
+      <c r="G309">
+        <v>0</v>
+      </c>
+      <c r="K309">
+        <v>18</v>
+      </c>
+      <c r="L309" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12">
+      <c r="A310" t="s">
+        <v>204</v>
+      </c>
+      <c r="B310" t="s">
+        <v>222</v>
+      </c>
+      <c r="C310" t="s">
+        <v>252</v>
+      </c>
+      <c r="D310">
+        <v>0.5</v>
+      </c>
+      <c r="E310">
+        <v>18</v>
+      </c>
+      <c r="F310">
+        <v>0</v>
+      </c>
+      <c r="G310">
+        <v>0</v>
+      </c>
+      <c r="K310">
+        <v>12</v>
+      </c>
+      <c r="L310" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12">
+      <c r="A311" t="s">
+        <v>205</v>
+      </c>
+      <c r="B311" t="s">
+        <v>227</v>
+      </c>
+      <c r="C311" t="s">
+        <v>252</v>
+      </c>
+      <c r="D311">
+        <v>1.36</v>
+      </c>
+      <c r="E311">
+        <v>22</v>
+      </c>
+      <c r="F311">
+        <v>0</v>
+      </c>
+      <c r="G311">
+        <v>0</v>
+      </c>
+      <c r="K311">
+        <v>13</v>
+      </c>
+      <c r="L311" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12">
+      <c r="A312" t="s">
+        <v>204</v>
+      </c>
+      <c r="B312" t="s">
+        <v>218</v>
+      </c>
+      <c r="C312" t="s">
+        <v>253</v>
+      </c>
+      <c r="D312">
+        <v>0.21</v>
+      </c>
+      <c r="E312">
+        <v>33.57</v>
+      </c>
+      <c r="F312">
+        <v>0</v>
+      </c>
+      <c r="G312">
+        <v>0</v>
+      </c>
+      <c r="K312">
+        <v>6</v>
+      </c>
+      <c r="L312" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12">
+      <c r="A313" t="s">
+        <v>197</v>
+      </c>
+      <c r="B313" t="s">
+        <v>228</v>
+      </c>
+      <c r="C313" t="s">
+        <v>255</v>
+      </c>
+      <c r="D313">
+        <v>0.23</v>
+      </c>
+      <c r="E313">
+        <v>7.69</v>
+      </c>
+      <c r="F313">
+        <v>0</v>
+      </c>
+      <c r="G313">
+        <v>0</v>
+      </c>
+      <c r="K313">
+        <v>5</v>
+      </c>
+      <c r="L313" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12">
+      <c r="A314" t="s">
+        <v>202</v>
+      </c>
+      <c r="B314" t="s">
+        <v>226</v>
+      </c>
+      <c r="C314" t="s">
+        <v>252</v>
+      </c>
+      <c r="D314">
+        <v>1.22</v>
+      </c>
+      <c r="E314">
+        <v>2.96</v>
+      </c>
+      <c r="F314">
+        <v>0</v>
+      </c>
+      <c r="G314">
+        <v>0</v>
+      </c>
+      <c r="K314">
+        <v>13</v>
+      </c>
+      <c r="L314" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12">
+      <c r="A315" t="s">
+        <v>202</v>
+      </c>
+      <c r="B315" t="s">
+        <v>223</v>
+      </c>
+      <c r="C315" t="s">
+        <v>254</v>
+      </c>
+      <c r="D315">
+        <v>0.27</v>
+      </c>
+      <c r="E315">
+        <v>14.23</v>
+      </c>
+      <c r="F315">
+        <v>0</v>
+      </c>
+      <c r="G315">
+        <v>0</v>
+      </c>
+      <c r="K315">
+        <v>9</v>
+      </c>
+      <c r="L315" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12">
+      <c r="A316" t="s">
+        <v>200</v>
+      </c>
+      <c r="B316" t="s">
+        <v>229</v>
+      </c>
+      <c r="C316" t="s">
+        <v>254</v>
+      </c>
+      <c r="D316">
+        <v>1.05</v>
+      </c>
+      <c r="E316">
+        <v>1.43</v>
+      </c>
+      <c r="F316">
+        <v>0</v>
+      </c>
+      <c r="G316">
+        <v>0</v>
+      </c>
+      <c r="K316">
+        <v>6</v>
+      </c>
+      <c r="L316" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12">
+      <c r="A317" t="s">
+        <v>206</v>
+      </c>
+      <c r="B317" t="s">
+        <v>213</v>
+      </c>
+      <c r="C317" t="s">
+        <v>253</v>
+      </c>
+      <c r="D317">
+        <v>0.11</v>
+      </c>
+      <c r="E317">
+        <v>9.44</v>
+      </c>
+      <c r="F317">
+        <v>0</v>
+      </c>
+      <c r="G317">
+        <v>0</v>
+      </c>
+      <c r="K317">
+        <v>8</v>
+      </c>
+      <c r="L317" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="318" spans="1:12">
+      <c r="A318" t="s">
+        <v>207</v>
+      </c>
+      <c r="B318" t="s">
+        <v>213</v>
+      </c>
+      <c r="C318" t="s">
+        <v>253</v>
+      </c>
+      <c r="D318">
+        <v>0.11</v>
+      </c>
+      <c r="E318">
+        <v>8.33</v>
+      </c>
+      <c r="F318">
+        <v>0</v>
+      </c>
+      <c r="G318">
+        <v>0</v>
+      </c>
+      <c r="K318">
+        <v>9</v>
+      </c>
+      <c r="L318" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12">
+      <c r="A319" t="s">
+        <v>198</v>
+      </c>
+      <c r="B319" t="s">
+        <v>213</v>
+      </c>
+      <c r="C319" t="s">
+        <v>253</v>
+      </c>
+      <c r="D319">
+        <v>0.06</v>
+      </c>
+      <c r="E319">
+        <v>16.11</v>
+      </c>
+      <c r="F319">
+        <v>0</v>
+      </c>
+      <c r="G319">
+        <v>0</v>
+      </c>
+      <c r="K319">
+        <v>9</v>
+      </c>
+      <c r="L319" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12">
+      <c r="A320" t="s">
+        <v>204</v>
+      </c>
+      <c r="B320" t="s">
+        <v>233</v>
+      </c>
+      <c r="C320" t="s">
+        <v>254</v>
+      </c>
+      <c r="D320">
+        <v>1.91</v>
+      </c>
+      <c r="E320">
+        <v>10</v>
+      </c>
+      <c r="F320">
+        <v>0</v>
+      </c>
+      <c r="G320">
+        <v>0</v>
+      </c>
+      <c r="K320">
+        <v>16</v>
+      </c>
+      <c r="L320" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="321" spans="1:12">
+      <c r="A321" t="s">
+        <v>197</v>
+      </c>
+      <c r="B321" t="s">
+        <v>243</v>
+      </c>
+      <c r="C321" t="s">
+        <v>253</v>
+      </c>
+      <c r="D321">
+        <v>0.4</v>
+      </c>
+      <c r="E321">
+        <v>7</v>
+      </c>
+      <c r="F321">
+        <v>0</v>
+      </c>
+      <c r="G321">
+        <v>0</v>
+      </c>
+      <c r="K321">
+        <v>5</v>
+      </c>
+      <c r="L321" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12">
+      <c r="A322" t="s">
+        <v>208</v>
+      </c>
+      <c r="B322" t="s">
+        <v>243</v>
+      </c>
+      <c r="C322" t="s">
+        <v>253</v>
+      </c>
+      <c r="D322">
+        <v>0.5</v>
+      </c>
+      <c r="E322">
+        <v>15.83</v>
+      </c>
+      <c r="F322">
+        <v>0</v>
+      </c>
+      <c r="G322">
+        <v>0</v>
+      </c>
+      <c r="K322">
+        <v>5</v>
+      </c>
+      <c r="L322" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12">
+      <c r="A323" t="s">
+        <v>197</v>
+      </c>
+      <c r="B323" t="s">
+        <v>239</v>
+      </c>
+      <c r="C323" t="s">
+        <v>254</v>
+      </c>
+      <c r="D323">
+        <v>1.15</v>
+      </c>
+      <c r="E323">
+        <v>39.23</v>
+      </c>
+      <c r="F323">
+        <v>0</v>
+      </c>
+      <c r="G323">
+        <v>0</v>
+      </c>
+      <c r="K323">
+        <v>4</v>
+      </c>
+      <c r="L323" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="324" spans="1:12">
+      <c r="A324" t="s">
+        <v>209</v>
+      </c>
+      <c r="B324" t="s">
+        <v>239</v>
+      </c>
+      <c r="C324" t="s">
+        <v>254</v>
+      </c>
+      <c r="D324">
+        <v>1.38</v>
+      </c>
+      <c r="E324">
+        <v>62.31</v>
+      </c>
+      <c r="F324">
+        <v>0</v>
+      </c>
+      <c r="G324">
+        <v>0</v>
+      </c>
+      <c r="K324">
+        <v>5</v>
+      </c>
+      <c r="L324" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12">
+      <c r="A325" t="s">
+        <v>202</v>
+      </c>
+      <c r="B325" t="s">
+        <v>224</v>
+      </c>
+      <c r="C325" t="s">
+        <v>254</v>
+      </c>
+      <c r="D325">
+        <v>1.5</v>
+      </c>
+      <c r="E325">
+        <v>5</v>
+      </c>
+      <c r="F325">
+        <v>0</v>
+      </c>
+      <c r="G325">
+        <v>0</v>
+      </c>
+      <c r="K325">
+        <v>8</v>
+      </c>
+      <c r="L325" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="326" spans="1:12">
+      <c r="A326" t="s">
+        <v>210</v>
+      </c>
+      <c r="B326" t="s">
+        <v>231</v>
+      </c>
+      <c r="C326" t="s">
+        <v>254</v>
+      </c>
+      <c r="D326">
+        <v>0.38</v>
+      </c>
+      <c r="E326">
+        <v>3.85</v>
+      </c>
+      <c r="F326">
+        <v>0</v>
+      </c>
+      <c r="G326">
+        <v>0</v>
+      </c>
+      <c r="K326">
+        <v>17</v>
+      </c>
+      <c r="L326" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12">
+      <c r="A327" t="s">
+        <v>211</v>
+      </c>
+      <c r="B327" t="s">
+        <v>240</v>
+      </c>
+      <c r="C327" t="s">
+        <v>253</v>
+      </c>
+      <c r="D327">
+        <v>0.14</v>
+      </c>
+      <c r="E327">
+        <v>25.36</v>
+      </c>
+      <c r="F327">
+        <v>0</v>
+      </c>
+      <c r="G327">
+        <v>0</v>
+      </c>
+      <c r="K327">
+        <v>11</v>
+      </c>
+      <c r="L327" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="328" spans="1:12">
+      <c r="A328" t="s">
+        <v>209</v>
+      </c>
+      <c r="B328" t="s">
+        <v>240</v>
+      </c>
+      <c r="C328" t="s">
+        <v>253</v>
+      </c>
+      <c r="D328">
+        <v>0.21</v>
+      </c>
+      <c r="E328">
+        <v>37.86</v>
+      </c>
+      <c r="F328">
+        <v>3</v>
+      </c>
+      <c r="G328">
+        <v>0</v>
+      </c>
+      <c r="K328">
+        <v>13</v>
+      </c>
+      <c r="L328" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12">
+      <c r="A329" t="s">
+        <v>200</v>
+      </c>
+      <c r="B329" t="s">
+        <v>216</v>
+      </c>
+      <c r="C329" t="s">
+        <v>255</v>
+      </c>
+      <c r="D329">
+        <v>0.17</v>
+      </c>
+      <c r="E329">
+        <v>36.52</v>
+      </c>
+      <c r="F329">
+        <v>0</v>
+      </c>
+      <c r="G329">
+        <v>0</v>
+      </c>
+      <c r="K329">
+        <v>9</v>
+      </c>
+      <c r="L329" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="330" spans="1:12">
+      <c r="A330" t="s">
+        <v>199</v>
+      </c>
+      <c r="B330" t="s">
+        <v>214</v>
+      </c>
+      <c r="C330" t="s">
+        <v>255</v>
+      </c>
+      <c r="D330">
+        <v>0.23</v>
+      </c>
+      <c r="E330">
+        <v>12.31</v>
+      </c>
+      <c r="F330">
+        <v>0</v>
+      </c>
+      <c r="G330">
+        <v>0</v>
+      </c>
+      <c r="K330">
+        <v>4</v>
+      </c>
+      <c r="L330" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="331" spans="1:12">
+      <c r="A331" t="s">
+        <v>207</v>
+      </c>
+      <c r="B331" t="s">
+        <v>214</v>
+      </c>
+      <c r="C331" t="s">
+        <v>255</v>
+      </c>
+      <c r="D331">
+        <v>0.31</v>
+      </c>
+      <c r="E331">
+        <v>14.62</v>
+      </c>
+      <c r="F331">
+        <v>0</v>
+      </c>
+      <c r="G331">
+        <v>0</v>
+      </c>
+      <c r="K331">
+        <v>4</v>
+      </c>
+      <c r="L331" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12">
+      <c r="A332" t="s">
+        <v>200</v>
+      </c>
+      <c r="B332" t="s">
         <v>241</v>
       </c>
-      <c r="D301" t="s">
-        <v>243</v>
-      </c>
-      <c r="E301" t="s">
-        <v>244</v>
-      </c>
-      <c r="F301" t="s">
+      <c r="C332" t="s">
+        <v>253</v>
+      </c>
+      <c r="D332">
+        <v>0.08</v>
+      </c>
+      <c r="E332">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="F332">
+        <v>0</v>
+      </c>
+      <c r="G332">
+        <v>0</v>
+      </c>
+      <c r="K332">
+        <v>12</v>
+      </c>
+      <c r="L332" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="333" spans="1:12">
+      <c r="A333" t="s">
+        <v>201</v>
+      </c>
+      <c r="B333" t="s">
+        <v>241</v>
+      </c>
+      <c r="C333" t="s">
+        <v>253</v>
+      </c>
+      <c r="D333">
+        <v>0.12</v>
+      </c>
+      <c r="E333">
+        <v>33.08</v>
+      </c>
+      <c r="F333">
+        <v>7</v>
+      </c>
+      <c r="G333">
+        <v>0</v>
+      </c>
+      <c r="K333">
+        <v>13</v>
+      </c>
+      <c r="L333" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="334" spans="1:12">
+      <c r="A334" t="s">
+        <v>208</v>
+      </c>
+      <c r="B334" t="s">
+        <v>220</v>
+      </c>
+      <c r="C334" t="s">
+        <v>251</v>
+      </c>
+      <c r="D334">
+        <v>0.14</v>
+      </c>
+      <c r="E334">
+        <v>20</v>
+      </c>
+      <c r="F334">
+        <v>0</v>
+      </c>
+      <c r="G334">
+        <v>0</v>
+      </c>
+      <c r="K334">
+        <v>10</v>
+      </c>
+      <c r="L334" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="335" spans="1:12">
+      <c r="A335" t="s">
+        <v>198</v>
+      </c>
+      <c r="B335" t="s">
+        <v>220</v>
+      </c>
+      <c r="C335" t="s">
+        <v>251</v>
+      </c>
+      <c r="D335">
+        <v>0.18</v>
+      </c>
+      <c r="E335">
+        <v>29.29</v>
+      </c>
+      <c r="F335">
+        <v>0</v>
+      </c>
+      <c r="G335">
+        <v>0</v>
+      </c>
+      <c r="K335">
+        <v>11</v>
+      </c>
+      <c r="L335" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="336" spans="1:12">
+      <c r="A336" t="s">
+        <v>201</v>
+      </c>
+      <c r="B336" t="s">
+        <v>219</v>
+      </c>
+      <c r="C336" t="s">
+        <v>254</v>
+      </c>
+      <c r="D336">
+        <v>1.47</v>
+      </c>
+      <c r="E336">
+        <v>32</v>
+      </c>
+      <c r="F336">
+        <v>0</v>
+      </c>
+      <c r="G336">
+        <v>0</v>
+      </c>
+      <c r="K336">
+        <v>10</v>
+      </c>
+      <c r="L336" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="337" spans="1:12">
+      <c r="A337" t="s">
+        <v>209</v>
+      </c>
+      <c r="B337" t="s">
         <v>245</v>
       </c>
-      <c r="G301" t="s">
-        <v>245</v>
-      </c>
-      <c r="K301" t="s">
-        <v>246</v>
-      </c>
-      <c r="L301" t="s">
-        <v>248</v>
+      <c r="C337" t="s">
+        <v>254</v>
+      </c>
+      <c r="D337">
+        <v>0.25</v>
+      </c>
+      <c r="E337">
+        <v>34</v>
+      </c>
+      <c r="F337">
+        <v>0</v>
+      </c>
+      <c r="G337">
+        <v>0</v>
+      </c>
+      <c r="K337">
+        <v>9</v>
+      </c>
+      <c r="L337" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="338" spans="1:12">
+      <c r="A338" t="s">
+        <v>209</v>
+      </c>
+      <c r="B338" t="s">
+        <v>247</v>
+      </c>
+      <c r="C338" t="s">
+        <v>254</v>
+      </c>
+      <c r="D338" t="s">
+        <v>257</v>
+      </c>
+      <c r="E338" t="s">
+        <v>258</v>
+      </c>
+      <c r="F338" t="s">
+        <v>259</v>
+      </c>
+      <c r="G338" t="s">
+        <v>259</v>
+      </c>
+      <c r="K338" t="s">
+        <v>260</v>
+      </c>
+      <c r="L338" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/data/pest_disease_control.xlsx
+++ b/data/pest_disease_control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="297">
   <si>
     <t>Date</t>
   </si>
@@ -742,6 +742,15 @@
     <t>2025-12-13</t>
   </si>
   <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-02-04</t>
+  </si>
+  <si>
     <t>DG01000</t>
   </si>
   <si>
@@ -877,19 +886,19 @@
     <t>MN1</t>
   </si>
   <si>
-    <t>0.11</t>
-  </si>
-  <si>
-    <t>56.79</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1.43</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>0.18</t>
+  </si>
+  <si>
+    <t>82.86</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>2024/25</t>
@@ -1253,7 +1262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L406"/>
+  <dimension ref="A1:L409"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -1299,10 +1308,10 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D2">
         <v>1.32</v>
@@ -1326,7 +1335,7 @@
         <v>10</v>
       </c>
       <c r="L2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1334,10 +1343,10 @@
         <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C3" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D3">
         <v>0.47</v>
@@ -1361,7 +1370,7 @@
         <v>7</v>
       </c>
       <c r="L3" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1369,10 +1378,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D4">
         <v>0.06</v>
@@ -1396,7 +1405,7 @@
         <v>6</v>
       </c>
       <c r="L4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1404,10 +1413,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C5" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D5">
         <v>0.32</v>
@@ -1431,7 +1440,7 @@
         <v>7</v>
       </c>
       <c r="L5" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1439,10 +1448,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D6">
         <v>0.6</v>
@@ -1466,7 +1475,7 @@
         <v>8</v>
       </c>
       <c r="L6" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1474,10 +1483,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C7" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D7">
         <v>0.16</v>
@@ -1501,7 +1510,7 @@
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1509,10 +1518,10 @@
         <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C8" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D8">
         <v>0.47</v>
@@ -1536,7 +1545,7 @@
         <v>8</v>
       </c>
       <c r="L8" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1544,10 +1553,10 @@
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D9">
         <v>0.28</v>
@@ -1571,7 +1580,7 @@
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1579,10 +1588,10 @@
         <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C10" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D10">
         <v>0.16</v>
@@ -1606,7 +1615,7 @@
         <v>6</v>
       </c>
       <c r="L10" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1614,10 +1623,10 @@
         <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D11">
         <v>0.5</v>
@@ -1641,7 +1650,7 @@
         <v>7</v>
       </c>
       <c r="L11" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1649,10 +1658,10 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C12" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D12">
         <v>0.2</v>
@@ -1676,7 +1685,7 @@
         <v>8</v>
       </c>
       <c r="L12" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1684,10 +1693,10 @@
         <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C13" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D13">
         <v>0.6</v>
@@ -1711,7 +1720,7 @@
         <v>7</v>
       </c>
       <c r="L13" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1719,10 +1728,10 @@
         <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C14" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D14">
         <v>1.07</v>
@@ -1746,7 +1755,7 @@
         <v>11</v>
       </c>
       <c r="L14" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1754,10 +1763,10 @@
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C15" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D15">
         <v>0.43</v>
@@ -1781,7 +1790,7 @@
         <v>9</v>
       </c>
       <c r="L15" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -1789,10 +1798,10 @@
         <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C16" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D16">
         <v>1.05</v>
@@ -1816,7 +1825,7 @@
         <v>10</v>
       </c>
       <c r="L16" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1824,10 +1833,10 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D17">
         <v>0.11</v>
@@ -1851,7 +1860,7 @@
         <v>23</v>
       </c>
       <c r="L17" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1859,10 +1868,10 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C18" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D18">
         <v>0.06</v>
@@ -1886,7 +1895,7 @@
         <v>27</v>
       </c>
       <c r="L18" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" spans="1:12">
@@ -1894,10 +1903,10 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D19">
         <v>0.07000000000000001</v>
@@ -1921,7 +1930,7 @@
         <v>7</v>
       </c>
       <c r="L19" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1929,10 +1938,10 @@
         <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C20" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D20">
         <v>1.15</v>
@@ -1956,7 +1965,7 @@
         <v>17</v>
       </c>
       <c r="L20" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21" spans="1:12">
@@ -1964,10 +1973,10 @@
         <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C21" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D21">
         <v>0.08</v>
@@ -1991,7 +2000,7 @@
         <v>26</v>
       </c>
       <c r="L21" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22" spans="1:12">
@@ -1999,10 +2008,10 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C22" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D22">
         <v>0.45</v>
@@ -2026,7 +2035,7 @@
         <v>23</v>
       </c>
       <c r="L22" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="23" spans="1:12">
@@ -2034,10 +2043,10 @@
         <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C23" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D23">
         <v>0.38</v>
@@ -2061,7 +2070,7 @@
         <v>18</v>
       </c>
       <c r="L23" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -2069,10 +2078,10 @@
         <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C24" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D24">
         <v>0.11</v>
@@ -2096,7 +2105,7 @@
         <v>27</v>
       </c>
       <c r="L24" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2104,10 +2113,10 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C25" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D25">
         <v>0.09</v>
@@ -2131,7 +2140,7 @@
         <v>21</v>
       </c>
       <c r="L25" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2139,10 +2148,10 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C26" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D26">
         <v>0.17</v>
@@ -2166,7 +2175,7 @@
         <v>13</v>
       </c>
       <c r="L26" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2174,10 +2183,10 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C27" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D27">
         <v>0.09</v>
@@ -2201,7 +2210,7 @@
         <v>17</v>
       </c>
       <c r="L27" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28" spans="1:12">
@@ -2209,10 +2218,10 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C28" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D28">
         <v>0.9399999999999999</v>
@@ -2236,7 +2245,7 @@
         <v>14</v>
       </c>
       <c r="L28" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:12">
@@ -2244,10 +2253,10 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C29" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D29">
         <v>0.9399999999999999</v>
@@ -2271,7 +2280,7 @@
         <v>12</v>
       </c>
       <c r="L29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2279,10 +2288,10 @@
         <v>35</v>
       </c>
       <c r="B30" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C30" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D30">
         <v>0.06</v>
@@ -2306,7 +2315,7 @@
         <v>21</v>
       </c>
       <c r="L30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:12">
@@ -2314,10 +2323,10 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C31" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D31">
         <v>0.29</v>
@@ -2341,7 +2350,7 @@
         <v>19</v>
       </c>
       <c r="L31" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2349,10 +2358,10 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C32" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D32">
         <v>0.11</v>
@@ -2376,7 +2385,7 @@
         <v>16</v>
       </c>
       <c r="L32" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:12">
@@ -2384,10 +2393,10 @@
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C33" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D33">
         <v>0.15</v>
@@ -2411,7 +2420,7 @@
         <v>7</v>
       </c>
       <c r="L33" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2419,10 +2428,10 @@
         <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C34" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D34">
         <v>0.42</v>
@@ -2446,7 +2455,7 @@
         <v>21</v>
       </c>
       <c r="L34" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2454,10 +2463,10 @@
         <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C35" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D35">
         <v>0.5600000000000001</v>
@@ -2481,7 +2490,7 @@
         <v>27</v>
       </c>
       <c r="L35" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2489,10 +2498,10 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C36" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D36">
         <v>0.21</v>
@@ -2516,7 +2525,7 @@
         <v>7</v>
       </c>
       <c r="L36" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2524,10 +2533,10 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C37" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D37">
         <v>0.24</v>
@@ -2551,7 +2560,7 @@
         <v>16</v>
       </c>
       <c r="L37" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2559,10 +2568,10 @@
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C38" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D38">
         <v>0.17</v>
@@ -2586,7 +2595,7 @@
         <v>4</v>
       </c>
       <c r="L38" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2594,10 +2603,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C39" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D39">
         <v>1.62</v>
@@ -2621,7 +2630,7 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -2629,10 +2638,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C40" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D40">
         <v>0.38</v>
@@ -2656,7 +2665,7 @@
         <v>18</v>
       </c>
       <c r="L40" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -2664,10 +2673,10 @@
         <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C41" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D41">
         <v>0.09</v>
@@ -2691,7 +2700,7 @@
         <v>19</v>
       </c>
       <c r="L41" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="42" spans="1:12">
@@ -2699,10 +2708,10 @@
         <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C42" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D42">
         <v>0.1</v>
@@ -2726,7 +2735,7 @@
         <v>17</v>
       </c>
       <c r="L42" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="43" spans="1:12">
@@ -2734,10 +2743,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C43" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D43">
         <v>0.22</v>
@@ -2761,7 +2770,7 @@
         <v>21</v>
       </c>
       <c r="L43" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44" spans="1:12">
@@ -2769,10 +2778,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C44" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D44">
         <v>0.14</v>
@@ -2796,7 +2805,7 @@
         <v>23</v>
       </c>
       <c r="L44" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2804,10 +2813,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C45" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D45">
         <v>0.09</v>
@@ -2831,7 +2840,7 @@
         <v>4</v>
       </c>
       <c r="L45" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="46" spans="1:12">
@@ -2839,10 +2848,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C46" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D46">
         <v>0.22</v>
@@ -2866,7 +2875,7 @@
         <v>17</v>
       </c>
       <c r="L46" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2874,10 +2883,10 @@
         <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C47" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D47">
         <v>0.23</v>
@@ -2901,7 +2910,7 @@
         <v>7</v>
       </c>
       <c r="L47" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2909,10 +2918,10 @@
         <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C48" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D48">
         <v>0.29</v>
@@ -2936,7 +2945,7 @@
         <v>11</v>
       </c>
       <c r="L48" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2944,10 +2953,10 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C49" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D49">
         <v>0.15</v>
@@ -2971,7 +2980,7 @@
         <v>9</v>
       </c>
       <c r="L49" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2979,10 +2988,10 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C50" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D50">
         <v>0.14</v>
@@ -3006,7 +3015,7 @@
         <v>23</v>
       </c>
       <c r="L50" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -3014,10 +3023,10 @@
         <v>46</v>
       </c>
       <c r="B51" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C51" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D51">
         <v>0.14</v>
@@ -3041,7 +3050,7 @@
         <v>7</v>
       </c>
       <c r="L51" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -3049,10 +3058,10 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C52" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D52">
         <v>0.71</v>
@@ -3076,7 +3085,7 @@
         <v>12</v>
       </c>
       <c r="L52" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -3084,10 +3093,10 @@
         <v>47</v>
       </c>
       <c r="B53" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C53" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D53">
         <v>0.15</v>
@@ -3111,7 +3120,7 @@
         <v>13</v>
       </c>
       <c r="L53" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3119,10 +3128,10 @@
         <v>48</v>
       </c>
       <c r="B54" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C54" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D54">
         <v>0.28</v>
@@ -3146,7 +3155,7 @@
         <v>14</v>
       </c>
       <c r="L54" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3154,10 +3163,10 @@
         <v>48</v>
       </c>
       <c r="B55" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C55" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D55">
         <v>0.23</v>
@@ -3181,7 +3190,7 @@
         <v>4</v>
       </c>
       <c r="L55" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="56" spans="1:12">
@@ -3189,10 +3198,10 @@
         <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C56" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D56">
         <v>0.29</v>
@@ -3216,7 +3225,7 @@
         <v>21</v>
       </c>
       <c r="L56" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="57" spans="1:12">
@@ -3224,10 +3233,10 @@
         <v>50</v>
       </c>
       <c r="B57" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C57" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D57">
         <v>0.12</v>
@@ -3251,7 +3260,7 @@
         <v>13</v>
       </c>
       <c r="L57" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="58" spans="1:12">
@@ -3259,10 +3268,10 @@
         <v>50</v>
       </c>
       <c r="B58" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C58" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D58">
         <v>0.5</v>
@@ -3286,7 +3295,7 @@
         <v>17</v>
       </c>
       <c r="L58" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3294,10 +3303,10 @@
         <v>50</v>
       </c>
       <c r="B59" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C59" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D59">
         <v>0.52</v>
@@ -3321,7 +3330,7 @@
         <v>17</v>
       </c>
       <c r="L59" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3329,10 +3338,10 @@
         <v>51</v>
       </c>
       <c r="B60" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C60" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D60">
         <v>0.28</v>
@@ -3356,7 +3365,7 @@
         <v>19</v>
       </c>
       <c r="L60" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3364,10 +3373,10 @@
         <v>52</v>
       </c>
       <c r="B61" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C61" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D61">
         <v>0.55</v>
@@ -3391,7 +3400,7 @@
         <v>23</v>
       </c>
       <c r="L61" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3399,10 +3408,10 @@
         <v>53</v>
       </c>
       <c r="B62" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C62" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D62">
         <v>0.26</v>
@@ -3426,7 +3435,7 @@
         <v>14</v>
       </c>
       <c r="L62" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="63" spans="1:12">
@@ -3434,10 +3443,10 @@
         <v>54</v>
       </c>
       <c r="B63" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C63" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D63">
         <v>0.08</v>
@@ -3461,7 +3470,7 @@
         <v>27</v>
       </c>
       <c r="L63" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3469,10 +3478,10 @@
         <v>55</v>
       </c>
       <c r="B64" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C64" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D64">
         <v>1.04</v>
@@ -3496,7 +3505,7 @@
         <v>27</v>
       </c>
       <c r="L64" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3504,10 +3513,10 @@
         <v>55</v>
       </c>
       <c r="B65" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C65" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D65">
         <v>0.07000000000000001</v>
@@ -3531,7 +3540,7 @@
         <v>26</v>
       </c>
       <c r="L65" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3539,10 +3548,10 @@
         <v>56</v>
       </c>
       <c r="B66" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D66">
         <v>0.25</v>
@@ -3566,7 +3575,7 @@
         <v>7</v>
       </c>
       <c r="L66" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3574,10 +3583,10 @@
         <v>56</v>
       </c>
       <c r="B67" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C67" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D67">
         <v>0.03</v>
@@ -3601,7 +3610,7 @@
         <v>23</v>
       </c>
       <c r="L67" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3609,10 +3618,10 @@
         <v>57</v>
       </c>
       <c r="B68" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C68" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D68">
         <v>1.47</v>
@@ -3636,7 +3645,7 @@
         <v>17</v>
       </c>
       <c r="L68" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3644,10 +3653,10 @@
         <v>57</v>
       </c>
       <c r="B69" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C69" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D69">
         <v>0.13</v>
@@ -3671,7 +3680,7 @@
         <v>7</v>
       </c>
       <c r="L69" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3679,10 +3688,10 @@
         <v>58</v>
       </c>
       <c r="B70" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C70" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D70">
         <v>0.76</v>
@@ -3706,7 +3715,7 @@
         <v>21</v>
       </c>
       <c r="L70" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -3714,10 +3723,10 @@
         <v>59</v>
       </c>
       <c r="B71" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C71" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D71">
         <v>0.2</v>
@@ -3741,7 +3750,7 @@
         <v>19</v>
       </c>
       <c r="L71" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="72" spans="1:12">
@@ -3749,10 +3758,10 @@
         <v>59</v>
       </c>
       <c r="B72" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C72" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D72">
         <v>2.19</v>
@@ -3776,7 +3785,7 @@
         <v>17</v>
       </c>
       <c r="L72" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="73" spans="1:12">
@@ -3784,10 +3793,10 @@
         <v>60</v>
       </c>
       <c r="B73" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C73" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D73">
         <v>0.2</v>
@@ -3811,7 +3820,7 @@
         <v>4</v>
       </c>
       <c r="L73" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="74" spans="1:12">
@@ -3819,10 +3828,10 @@
         <v>60</v>
       </c>
       <c r="B74" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C74" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D74">
         <v>2.26</v>
@@ -3846,7 +3855,7 @@
         <v>23</v>
       </c>
       <c r="L74" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="75" spans="1:12">
@@ -3854,10 +3863,10 @@
         <v>61</v>
       </c>
       <c r="B75" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C75" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D75">
         <v>0.15</v>
@@ -3881,7 +3890,7 @@
         <v>13</v>
       </c>
       <c r="L75" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3889,10 +3898,10 @@
         <v>61</v>
       </c>
       <c r="B76" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C76" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D76">
         <v>0.17</v>
@@ -3916,7 +3925,7 @@
         <v>13</v>
       </c>
       <c r="L76" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3924,10 +3933,10 @@
         <v>62</v>
       </c>
       <c r="B77" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C77" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D77">
         <v>0.64</v>
@@ -3951,7 +3960,7 @@
         <v>17</v>
       </c>
       <c r="L77" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -3959,10 +3968,10 @@
         <v>63</v>
       </c>
       <c r="B78" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C78" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D78">
         <v>0.45</v>
@@ -3986,7 +3995,7 @@
         <v>12</v>
       </c>
       <c r="L78" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3994,10 +4003,10 @@
         <v>63</v>
       </c>
       <c r="B79" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C79" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D79">
         <v>0.64</v>
@@ -4021,7 +4030,7 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -4029,10 +4038,10 @@
         <v>64</v>
       </c>
       <c r="B80" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C80" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D80">
         <v>0.28</v>
@@ -4056,7 +4065,7 @@
         <v>11</v>
       </c>
       <c r="L80" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -4064,10 +4073,10 @@
         <v>64</v>
       </c>
       <c r="B81" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C81" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D81">
         <v>0.31</v>
@@ -4091,7 +4100,7 @@
         <v>9</v>
       </c>
       <c r="L81" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -4099,10 +4108,10 @@
         <v>65</v>
       </c>
       <c r="B82" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C82" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D82">
         <v>0.14</v>
@@ -4126,7 +4135,7 @@
         <v>21</v>
       </c>
       <c r="L82" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -4134,10 +4143,10 @@
         <v>65</v>
       </c>
       <c r="B83" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C83" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D83">
         <v>0.23</v>
@@ -4161,7 +4170,7 @@
         <v>16</v>
       </c>
       <c r="L83" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4169,10 +4178,10 @@
         <v>66</v>
       </c>
       <c r="B84" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C84" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D84">
         <v>0.21</v>
@@ -4196,7 +4205,7 @@
         <v>8</v>
       </c>
       <c r="L84" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4204,10 +4213,10 @@
         <v>66</v>
       </c>
       <c r="B85" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C85" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D85">
         <v>0.07000000000000001</v>
@@ -4231,7 +4240,7 @@
         <v>7</v>
       </c>
       <c r="L85" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4239,10 +4248,10 @@
         <v>67</v>
       </c>
       <c r="B86" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C86" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D86">
         <v>0.11</v>
@@ -4266,7 +4275,7 @@
         <v>27</v>
       </c>
       <c r="L86" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4274,10 +4283,10 @@
         <v>67</v>
       </c>
       <c r="B87" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C87" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D87">
         <v>0.12</v>
@@ -4301,7 +4310,7 @@
         <v>14</v>
       </c>
       <c r="L87" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4309,10 +4318,10 @@
         <v>67</v>
       </c>
       <c r="B88" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C88" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D88">
         <v>0.45</v>
@@ -4336,7 +4345,7 @@
         <v>4</v>
       </c>
       <c r="L88" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -4344,10 +4353,10 @@
         <v>67</v>
       </c>
       <c r="B89" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C89" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D89">
         <v>0.33</v>
@@ -4371,7 +4380,7 @@
         <v>13</v>
       </c>
       <c r="L89" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4379,10 +4388,10 @@
         <v>67</v>
       </c>
       <c r="B90" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C90" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D90">
         <v>0.09</v>
@@ -4406,7 +4415,7 @@
         <v>19</v>
       </c>
       <c r="L90" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4414,10 +4423,10 @@
         <v>67</v>
       </c>
       <c r="B91" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C91" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D91">
         <v>0.15</v>
@@ -4441,7 +4450,7 @@
         <v>17</v>
       </c>
       <c r="L91" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4449,10 +4458,10 @@
         <v>67</v>
       </c>
       <c r="B92" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C92" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D92">
         <v>0.15</v>
@@ -4476,7 +4485,7 @@
         <v>17</v>
       </c>
       <c r="L92" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -4484,10 +4493,10 @@
         <v>67</v>
       </c>
       <c r="B93" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C93" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D93">
         <v>0.15</v>
@@ -4511,7 +4520,7 @@
         <v>11</v>
       </c>
       <c r="L93" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4519,10 +4528,10 @@
         <v>68</v>
       </c>
       <c r="B94" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C94" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D94">
         <v>0.43</v>
@@ -4546,7 +4555,7 @@
         <v>23</v>
       </c>
       <c r="L94" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4554,10 +4563,10 @@
         <v>68</v>
       </c>
       <c r="B95" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D95">
         <v>0.19</v>
@@ -4581,7 +4590,7 @@
         <v>14</v>
       </c>
       <c r="L95" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4589,10 +4598,10 @@
         <v>68</v>
       </c>
       <c r="B96" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C96" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D96">
         <v>0.17</v>
@@ -4616,7 +4625,7 @@
         <v>13</v>
       </c>
       <c r="L96" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4624,10 +4633,10 @@
         <v>68</v>
       </c>
       <c r="B97" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C97" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D97">
         <v>0.27</v>
@@ -4651,7 +4660,7 @@
         <v>21</v>
       </c>
       <c r="L97" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4659,10 +4668,10 @@
         <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C98" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D98">
         <v>0.08</v>
@@ -4686,7 +4695,7 @@
         <v>18</v>
       </c>
       <c r="L98" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4694,10 +4703,10 @@
         <v>69</v>
       </c>
       <c r="B99" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C99" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D99">
         <v>0.1</v>
@@ -4721,7 +4730,7 @@
         <v>23</v>
       </c>
       <c r="L99" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4729,10 +4738,10 @@
         <v>69</v>
       </c>
       <c r="B100" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C100" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D100">
         <v>0.67</v>
@@ -4756,7 +4765,7 @@
         <v>19</v>
       </c>
       <c r="L100" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -4764,10 +4773,10 @@
         <v>69</v>
       </c>
       <c r="B101" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C101" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D101">
         <v>0.14</v>
@@ -4791,7 +4800,7 @@
         <v>19</v>
       </c>
       <c r="L101" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="102" spans="1:12">
@@ -4799,10 +4808,10 @@
         <v>69</v>
       </c>
       <c r="B102" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C102" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D102">
         <v>0.12</v>
@@ -4826,7 +4835,7 @@
         <v>7</v>
       </c>
       <c r="L102" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4834,10 +4843,10 @@
         <v>69</v>
       </c>
       <c r="B103" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C103" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D103">
         <v>0.24</v>
@@ -4861,7 +4870,7 @@
         <v>19</v>
       </c>
       <c r="L103" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4869,10 +4878,10 @@
         <v>69</v>
       </c>
       <c r="B104" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C104" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D104">
         <v>0.11</v>
@@ -4896,7 +4905,7 @@
         <v>19</v>
       </c>
       <c r="L104" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4904,10 +4913,10 @@
         <v>70</v>
       </c>
       <c r="B105" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C105" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D105">
         <v>0.12</v>
@@ -4931,7 +4940,7 @@
         <v>17</v>
       </c>
       <c r="L105" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="106" spans="1:12">
@@ -4939,10 +4948,10 @@
         <v>70</v>
       </c>
       <c r="B106" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C106" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D106">
         <v>0.57</v>
@@ -4966,7 +4975,7 @@
         <v>21</v>
       </c>
       <c r="L106" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="107" spans="1:12">
@@ -4974,10 +4983,10 @@
         <v>71</v>
       </c>
       <c r="B107" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C107" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D107">
         <v>0.14</v>
@@ -5001,7 +5010,7 @@
         <v>19</v>
       </c>
       <c r="L107" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -5009,10 +5018,10 @@
         <v>71</v>
       </c>
       <c r="B108" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C108" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D108">
         <v>0.32</v>
@@ -5036,7 +5045,7 @@
         <v>17</v>
       </c>
       <c r="L108" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -5044,10 +5053,10 @@
         <v>71</v>
       </c>
       <c r="B109" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C109" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D109">
         <v>0.19</v>
@@ -5071,7 +5080,7 @@
         <v>27</v>
       </c>
       <c r="L109" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="110" spans="1:12">
@@ -5079,10 +5088,10 @@
         <v>72</v>
       </c>
       <c r="B110" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C110" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D110">
         <v>0.1</v>
@@ -5106,7 +5115,7 @@
         <v>4</v>
       </c>
       <c r="L110" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -5114,10 +5123,10 @@
         <v>72</v>
       </c>
       <c r="B111" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C111" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D111">
         <v>0.17</v>
@@ -5141,7 +5150,7 @@
         <v>13</v>
       </c>
       <c r="L111" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -5149,10 +5158,10 @@
         <v>72</v>
       </c>
       <c r="B112" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C112" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D112">
         <v>0.18</v>
@@ -5176,7 +5185,7 @@
         <v>19</v>
       </c>
       <c r="L112" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -5184,10 +5193,10 @@
         <v>72</v>
       </c>
       <c r="B113" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C113" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D113">
         <v>0.25</v>
@@ -5211,7 +5220,7 @@
         <v>17</v>
       </c>
       <c r="L113" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -5219,10 +5228,10 @@
         <v>72</v>
       </c>
       <c r="B114" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C114" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D114">
         <v>0.25</v>
@@ -5246,7 +5255,7 @@
         <v>17</v>
       </c>
       <c r="L114" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -5254,10 +5263,10 @@
         <v>72</v>
       </c>
       <c r="B115" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C115" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D115">
         <v>0.24</v>
@@ -5281,7 +5290,7 @@
         <v>11</v>
       </c>
       <c r="L115" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -5289,10 +5298,10 @@
         <v>73</v>
       </c>
       <c r="B116" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C116" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D116">
         <v>0.22</v>
@@ -5316,7 +5325,7 @@
         <v>23</v>
       </c>
       <c r="L116" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="117" spans="1:12">
@@ -5324,10 +5333,10 @@
         <v>73</v>
       </c>
       <c r="B117" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C117" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D117">
         <v>0.71</v>
@@ -5351,7 +5360,7 @@
         <v>19</v>
       </c>
       <c r="L117" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="118" spans="1:12">
@@ -5359,10 +5368,10 @@
         <v>74</v>
       </c>
       <c r="B118" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C118" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D118">
         <v>0.11</v>
@@ -5386,7 +5395,7 @@
         <v>11</v>
       </c>
       <c r="L118" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -5394,10 +5403,10 @@
         <v>74</v>
       </c>
       <c r="B119" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C119" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D119">
         <v>0.21</v>
@@ -5421,7 +5430,7 @@
         <v>8</v>
       </c>
       <c r="L119" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="120" spans="1:12">
@@ -5429,10 +5438,10 @@
         <v>74</v>
       </c>
       <c r="B120" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C120" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D120">
         <v>0.23</v>
@@ -5456,7 +5465,7 @@
         <v>8</v>
       </c>
       <c r="L120" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -5464,10 +5473,10 @@
         <v>74</v>
       </c>
       <c r="B121" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C121" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D121">
         <v>0.2</v>
@@ -5491,7 +5500,7 @@
         <v>7</v>
       </c>
       <c r="L121" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -5499,10 +5508,10 @@
         <v>74</v>
       </c>
       <c r="B122" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C122" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D122">
         <v>0.07000000000000001</v>
@@ -5526,7 +5535,7 @@
         <v>23</v>
       </c>
       <c r="L122" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -5534,10 +5543,10 @@
         <v>74</v>
       </c>
       <c r="B123" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C123" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D123">
         <v>0.39</v>
@@ -5561,7 +5570,7 @@
         <v>17</v>
       </c>
       <c r="L123" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -5569,10 +5578,10 @@
         <v>75</v>
       </c>
       <c r="B124" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C124" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D124">
         <v>0.41</v>
@@ -5596,7 +5605,7 @@
         <v>17</v>
       </c>
       <c r="L124" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5604,10 +5613,10 @@
         <v>75</v>
       </c>
       <c r="B125" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C125" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D125">
         <v>0.23</v>
@@ -5631,7 +5640,7 @@
         <v>19</v>
       </c>
       <c r="L125" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -5639,10 +5648,10 @@
         <v>76</v>
       </c>
       <c r="B126" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C126" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D126">
         <v>0.22</v>
@@ -5666,7 +5675,7 @@
         <v>7</v>
       </c>
       <c r="L126" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -5674,10 +5683,10 @@
         <v>76</v>
       </c>
       <c r="B127" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C127" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D127">
         <v>0.29</v>
@@ -5701,7 +5710,7 @@
         <v>19</v>
       </c>
       <c r="L127" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="128" spans="1:12">
@@ -5709,10 +5718,10 @@
         <v>77</v>
       </c>
       <c r="B128" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C128" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D128">
         <v>0.23</v>
@@ -5736,7 +5745,7 @@
         <v>17</v>
       </c>
       <c r="L128" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="129" spans="1:12">
@@ -5744,10 +5753,10 @@
         <v>77</v>
       </c>
       <c r="B129" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C129" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D129">
         <v>0.3</v>
@@ -5771,7 +5780,7 @@
         <v>17</v>
       </c>
       <c r="L129" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="130" spans="1:12">
@@ -5779,10 +5788,10 @@
         <v>78</v>
       </c>
       <c r="B130" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C130" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D130">
         <v>0.2</v>
@@ -5806,7 +5815,7 @@
         <v>7</v>
       </c>
       <c r="L130" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="131" spans="1:12">
@@ -5814,10 +5823,10 @@
         <v>79</v>
       </c>
       <c r="B131" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C131" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D131">
         <v>0.15</v>
@@ -5841,7 +5850,7 @@
         <v>7</v>
       </c>
       <c r="L131" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="132" spans="1:12">
@@ -5849,10 +5858,10 @@
         <v>80</v>
       </c>
       <c r="B132" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C132" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D132">
         <v>0.08</v>
@@ -5876,7 +5885,7 @@
         <v>18</v>
       </c>
       <c r="L132" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="133" spans="1:12">
@@ -5884,10 +5893,10 @@
         <v>81</v>
       </c>
       <c r="B133" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C133" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D133">
         <v>0.4</v>
@@ -5911,7 +5920,7 @@
         <v>23</v>
       </c>
       <c r="L133" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="134" spans="1:12">
@@ -5919,10 +5928,10 @@
         <v>82</v>
       </c>
       <c r="B134" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C134" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D134">
         <v>0.43</v>
@@ -5946,7 +5955,7 @@
         <v>11</v>
       </c>
       <c r="L134" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="135" spans="1:12">
@@ -5954,10 +5963,10 @@
         <v>83</v>
       </c>
       <c r="B135" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C135" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D135">
         <v>0.26</v>
@@ -5981,7 +5990,7 @@
         <v>17</v>
       </c>
       <c r="L135" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="136" spans="1:12">
@@ -5989,10 +5998,10 @@
         <v>84</v>
       </c>
       <c r="B136" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C136" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D136">
         <v>0.29</v>
@@ -6016,7 +6025,7 @@
         <v>23</v>
       </c>
       <c r="L136" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="137" spans="1:12">
@@ -6024,10 +6033,10 @@
         <v>85</v>
       </c>
       <c r="B137" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C137" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D137">
         <v>0.52</v>
@@ -6051,7 +6060,7 @@
         <v>18</v>
       </c>
       <c r="L137" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="138" spans="1:12">
@@ -6059,10 +6068,10 @@
         <v>86</v>
       </c>
       <c r="B138" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C138" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D138">
         <v>0.16</v>
@@ -6086,7 +6095,7 @@
         <v>3</v>
       </c>
       <c r="L138" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="139" spans="1:12">
@@ -6094,10 +6103,10 @@
         <v>86</v>
       </c>
       <c r="B139" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C139" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D139">
         <v>1.28</v>
@@ -6121,7 +6130,7 @@
         <v>11</v>
       </c>
       <c r="L139" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="140" spans="1:12">
@@ -6129,10 +6138,10 @@
         <v>87</v>
       </c>
       <c r="B140" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C140" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D140">
         <v>0.33</v>
@@ -6156,7 +6165,7 @@
         <v>11</v>
       </c>
       <c r="L140" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="141" spans="1:12">
@@ -6164,10 +6173,10 @@
         <v>88</v>
       </c>
       <c r="B141" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D141">
         <v>0.57</v>
@@ -6191,7 +6200,7 @@
         <v>13</v>
       </c>
       <c r="L141" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="142" spans="1:12">
@@ -6199,10 +6208,10 @@
         <v>89</v>
       </c>
       <c r="B142" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C142" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D142">
         <v>0.95</v>
@@ -6226,7 +6235,7 @@
         <v>16</v>
       </c>
       <c r="L142" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="143" spans="1:12">
@@ -6234,10 +6243,10 @@
         <v>90</v>
       </c>
       <c r="B143" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C143" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D143">
         <v>0.67</v>
@@ -6261,7 +6270,7 @@
         <v>11</v>
       </c>
       <c r="L143" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="144" spans="1:12">
@@ -6269,10 +6278,10 @@
         <v>91</v>
       </c>
       <c r="B144" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C144" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D144">
         <v>0.12</v>
@@ -6296,7 +6305,7 @@
         <v>9</v>
       </c>
       <c r="L144" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="145" spans="1:12">
@@ -6304,10 +6313,10 @@
         <v>92</v>
       </c>
       <c r="B145" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D145">
         <v>0.49</v>
@@ -6331,7 +6340,7 @@
         <v>18</v>
       </c>
       <c r="L145" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="146" spans="1:12">
@@ -6339,10 +6348,10 @@
         <v>93</v>
       </c>
       <c r="B146" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C146" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D146">
         <v>0.83</v>
@@ -6366,7 +6375,7 @@
         <v>19</v>
       </c>
       <c r="L146" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="147" spans="1:12">
@@ -6374,10 +6383,10 @@
         <v>94</v>
       </c>
       <c r="B147" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C147" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D147">
         <v>0.64</v>
@@ -6401,7 +6410,7 @@
         <v>23</v>
       </c>
       <c r="L147" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="148" spans="1:12">
@@ -6409,10 +6418,10 @@
         <v>95</v>
       </c>
       <c r="B148" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C148" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D148">
         <v>0.4</v>
@@ -6436,7 +6445,7 @@
         <v>18</v>
       </c>
       <c r="L148" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="149" spans="1:12">
@@ -6444,10 +6453,10 @@
         <v>95</v>
       </c>
       <c r="B149" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C149" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D149">
         <v>1.02</v>
@@ -6471,7 +6480,7 @@
         <v>13</v>
       </c>
       <c r="L149" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="150" spans="1:12">
@@ -6479,10 +6488,10 @@
         <v>96</v>
       </c>
       <c r="B150" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C150" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D150">
         <v>0.6899999999999999</v>
@@ -6506,7 +6515,7 @@
         <v>13</v>
       </c>
       <c r="L150" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="151" spans="1:12">
@@ -6514,10 +6523,10 @@
         <v>97</v>
       </c>
       <c r="B151" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C151" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D151">
         <v>1.36</v>
@@ -6541,7 +6550,7 @@
         <v>17</v>
       </c>
       <c r="L151" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="152" spans="1:12">
@@ -6549,10 +6558,10 @@
         <v>98</v>
       </c>
       <c r="B152" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C152" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D152">
         <v>0.14</v>
@@ -6576,7 +6585,7 @@
         <v>9</v>
       </c>
       <c r="L152" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="153" spans="1:12">
@@ -6584,10 +6593,10 @@
         <v>99</v>
       </c>
       <c r="B153" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C153" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D153">
         <v>0.08</v>
@@ -6611,7 +6620,7 @@
         <v>4</v>
       </c>
       <c r="L153" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="154" spans="1:12">
@@ -6619,10 +6628,10 @@
         <v>99</v>
       </c>
       <c r="B154" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C154" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D154">
         <v>0.77</v>
@@ -6646,7 +6655,7 @@
         <v>11</v>
       </c>
       <c r="L154" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="155" spans="1:12">
@@ -6654,10 +6663,10 @@
         <v>100</v>
       </c>
       <c r="B155" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C155" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D155">
         <v>0.76</v>
@@ -6681,7 +6690,7 @@
         <v>10</v>
       </c>
       <c r="L155" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="156" spans="1:12">
@@ -6689,10 +6698,10 @@
         <v>101</v>
       </c>
       <c r="B156" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C156" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D156">
         <v>0.14</v>
@@ -6716,7 +6725,7 @@
         <v>9</v>
       </c>
       <c r="L156" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="157" spans="1:12">
@@ -6724,10 +6733,10 @@
         <v>102</v>
       </c>
       <c r="B157" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C157" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D157">
         <v>0.05</v>
@@ -6751,7 +6760,7 @@
         <v>7</v>
       </c>
       <c r="L157" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="158" spans="1:12">
@@ -6759,10 +6768,10 @@
         <v>103</v>
       </c>
       <c r="B158" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C158" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D158">
         <v>0.83</v>
@@ -6786,7 +6795,7 @@
         <v>18</v>
       </c>
       <c r="L158" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="159" spans="1:12">
@@ -6794,10 +6803,10 @@
         <v>104</v>
       </c>
       <c r="B159" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D159">
         <v>1.31</v>
@@ -6821,7 +6830,7 @@
         <v>14</v>
       </c>
       <c r="L159" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="160" spans="1:12">
@@ -6829,10 +6838,10 @@
         <v>105</v>
       </c>
       <c r="B160" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C160" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D160">
         <v>0.68</v>
@@ -6856,7 +6865,7 @@
         <v>23</v>
       </c>
       <c r="L160" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="161" spans="1:12">
@@ -6864,10 +6873,10 @@
         <v>106</v>
       </c>
       <c r="B161" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C161" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D161">
         <v>0.18</v>
@@ -6891,7 +6900,7 @@
         <v>13</v>
       </c>
       <c r="L161" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="162" spans="1:12">
@@ -6899,10 +6908,10 @@
         <v>107</v>
       </c>
       <c r="B162" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C162" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D162">
         <v>0.38</v>
@@ -6926,7 +6935,7 @@
         <v>17</v>
       </c>
       <c r="L162" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="163" spans="1:12">
@@ -6934,10 +6943,10 @@
         <v>108</v>
       </c>
       <c r="B163" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C163" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D163">
         <v>0.07000000000000001</v>
@@ -6961,7 +6970,7 @@
         <v>17</v>
       </c>
       <c r="L163" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="164" spans="1:12">
@@ -6969,10 +6978,10 @@
         <v>109</v>
       </c>
       <c r="B164" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C164" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D164">
         <v>1.03</v>
@@ -6996,7 +7005,7 @@
         <v>19</v>
       </c>
       <c r="L164" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="165" spans="1:12">
@@ -7004,10 +7013,10 @@
         <v>110</v>
       </c>
       <c r="B165" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C165" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D165">
         <v>0.13</v>
@@ -7031,7 +7040,7 @@
         <v>17</v>
       </c>
       <c r="L165" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="166" spans="1:12">
@@ -7039,10 +7048,10 @@
         <v>110</v>
       </c>
       <c r="B166" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C166" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D166">
         <v>0.07000000000000001</v>
@@ -7066,7 +7075,7 @@
         <v>7</v>
       </c>
       <c r="L166" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="167" spans="1:12">
@@ -7074,10 +7083,10 @@
         <v>111</v>
       </c>
       <c r="B167" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C167" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D167">
         <v>1.73</v>
@@ -7101,7 +7110,7 @@
         <v>17</v>
       </c>
       <c r="L167" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="168" spans="1:12">
@@ -7109,10 +7118,10 @@
         <v>111</v>
       </c>
       <c r="B168" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C168" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D168">
         <v>0.75</v>
@@ -7136,7 +7145,7 @@
         <v>19</v>
       </c>
       <c r="L168" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="169" spans="1:12">
@@ -7144,10 +7153,10 @@
         <v>112</v>
       </c>
       <c r="B169" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C169" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D169">
         <v>0.89</v>
@@ -7171,7 +7180,7 @@
         <v>13</v>
       </c>
       <c r="L169" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="170" spans="1:12">
@@ -7179,10 +7188,10 @@
         <v>113</v>
       </c>
       <c r="B170" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C170" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D170">
         <v>1.22</v>
@@ -7206,7 +7215,7 @@
         <v>12</v>
       </c>
       <c r="L170" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="171" spans="1:12">
@@ -7214,10 +7223,10 @@
         <v>114</v>
       </c>
       <c r="B171" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C171" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D171">
         <v>0.16</v>
@@ -7241,7 +7250,7 @@
         <v>4</v>
       </c>
       <c r="L171" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="172" spans="1:12">
@@ -7249,10 +7258,10 @@
         <v>115</v>
       </c>
       <c r="B172" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C172" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D172">
         <v>0.52</v>
@@ -7276,7 +7285,7 @@
         <v>11</v>
       </c>
       <c r="L172" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:12">
@@ -7284,10 +7293,10 @@
         <v>115</v>
       </c>
       <c r="B173" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C173" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D173">
         <v>0.13</v>
@@ -7311,7 +7320,7 @@
         <v>17</v>
       </c>
       <c r="L173" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="174" spans="1:12">
@@ -7319,10 +7328,10 @@
         <v>116</v>
       </c>
       <c r="B174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C174" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D174">
         <v>0.17</v>
@@ -7346,7 +7355,7 @@
         <v>21</v>
       </c>
       <c r="L174" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="175" spans="1:12">
@@ -7354,10 +7363,10 @@
         <v>117</v>
       </c>
       <c r="B175" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C175" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D175">
         <v>0.29</v>
@@ -7381,7 +7390,7 @@
         <v>9</v>
       </c>
       <c r="L175" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="176" spans="1:12">
@@ -7389,10 +7398,10 @@
         <v>118</v>
       </c>
       <c r="B176" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C176" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D176">
         <v>0.75</v>
@@ -7416,7 +7425,7 @@
         <v>21</v>
       </c>
       <c r="L176" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="177" spans="1:12">
@@ -7424,10 +7433,10 @@
         <v>119</v>
       </c>
       <c r="B177" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C177" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D177">
         <v>0.63</v>
@@ -7451,7 +7460,7 @@
         <v>17</v>
       </c>
       <c r="L177" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="178" spans="1:12">
@@ -7459,10 +7468,10 @@
         <v>120</v>
       </c>
       <c r="B178" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C178" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D178">
         <v>0.95</v>
@@ -7486,7 +7495,7 @@
         <v>14</v>
       </c>
       <c r="L178" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="179" spans="1:12">
@@ -7494,10 +7503,10 @@
         <v>121</v>
       </c>
       <c r="B179" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C179" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D179">
         <v>0.8100000000000001</v>
@@ -7521,7 +7530,7 @@
         <v>18</v>
       </c>
       <c r="L179" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="180" spans="1:12">
@@ -7529,10 +7538,10 @@
         <v>122</v>
       </c>
       <c r="B180" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C180" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D180">
         <v>0.27</v>
@@ -7556,7 +7565,7 @@
         <v>13</v>
       </c>
       <c r="L180" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="181" spans="1:12">
@@ -7564,10 +7573,10 @@
         <v>123</v>
       </c>
       <c r="B181" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C181" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D181">
         <v>0.07000000000000001</v>
@@ -7591,7 +7600,7 @@
         <v>23</v>
       </c>
       <c r="L181" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="182" spans="1:12">
@@ -7599,10 +7608,10 @@
         <v>124</v>
       </c>
       <c r="B182" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C182" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D182">
         <v>1.66</v>
@@ -7626,7 +7635,7 @@
         <v>13</v>
       </c>
       <c r="L182" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="183" spans="1:12">
@@ -7634,10 +7643,10 @@
         <v>125</v>
       </c>
       <c r="B183" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C183" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D183">
         <v>0.49</v>
@@ -7661,7 +7670,7 @@
         <v>23</v>
       </c>
       <c r="L183" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="184" spans="1:12">
@@ -7669,10 +7678,10 @@
         <v>125</v>
       </c>
       <c r="B184" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C184" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D184">
         <v>0.49</v>
@@ -7696,7 +7705,7 @@
         <v>23</v>
       </c>
       <c r="L184" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="185" spans="1:12">
@@ -7704,10 +7713,10 @@
         <v>126</v>
       </c>
       <c r="B185" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C185" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D185">
         <v>1.73</v>
@@ -7731,7 +7740,7 @@
         <v>17</v>
       </c>
       <c r="L185" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="186" spans="1:12">
@@ -7739,10 +7748,10 @@
         <v>127</v>
       </c>
       <c r="B186" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D186">
         <v>0.27</v>
@@ -7766,7 +7775,7 @@
         <v>17</v>
       </c>
       <c r="L186" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="187" spans="1:12">
@@ -7774,10 +7783,10 @@
         <v>127</v>
       </c>
       <c r="B187" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C187" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D187">
         <v>0.14</v>
@@ -7801,7 +7810,7 @@
         <v>7</v>
       </c>
       <c r="L187" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="188" spans="1:12">
@@ -7809,10 +7818,10 @@
         <v>128</v>
       </c>
       <c r="B188" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C188" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D188">
         <v>0.15</v>
@@ -7836,7 +7845,7 @@
         <v>16</v>
       </c>
       <c r="L188" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -7844,10 +7853,10 @@
         <v>128</v>
       </c>
       <c r="B189" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C189" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D189">
         <v>0.13</v>
@@ -7871,7 +7880,7 @@
         <v>21</v>
       </c>
       <c r="L189" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -7879,10 +7888,10 @@
         <v>129</v>
       </c>
       <c r="B190" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C190" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D190">
         <v>0.89</v>
@@ -7906,7 +7915,7 @@
         <v>18</v>
       </c>
       <c r="L190" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="191" spans="1:12">
@@ -7914,10 +7923,10 @@
         <v>130</v>
       </c>
       <c r="B191" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C191" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D191">
         <v>0.25</v>
@@ -7941,7 +7950,7 @@
         <v>4</v>
       </c>
       <c r="L191" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -7949,10 +7958,10 @@
         <v>130</v>
       </c>
       <c r="B192" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C192" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D192">
         <v>0.91</v>
@@ -7976,7 +7985,7 @@
         <v>11</v>
       </c>
       <c r="L192" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -7984,10 +7993,10 @@
         <v>131</v>
       </c>
       <c r="B193" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C193" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D193">
         <v>2.38</v>
@@ -8011,7 +8020,7 @@
         <v>15</v>
       </c>
       <c r="L193" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -8019,10 +8028,10 @@
         <v>132</v>
       </c>
       <c r="B194" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C194" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D194">
         <v>0.18</v>
@@ -8046,7 +8055,7 @@
         <v>7</v>
       </c>
       <c r="L194" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -8054,10 +8063,10 @@
         <v>132</v>
       </c>
       <c r="B195" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C195" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D195">
         <v>0.29</v>
@@ -8081,7 +8090,7 @@
         <v>7</v>
       </c>
       <c r="L195" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -8089,10 +8098,10 @@
         <v>133</v>
       </c>
       <c r="B196" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C196" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D196">
         <v>0.38</v>
@@ -8116,7 +8125,7 @@
         <v>15</v>
       </c>
       <c r="L196" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -8124,10 +8133,10 @@
         <v>134</v>
       </c>
       <c r="B197" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C197" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D197">
         <v>0.38</v>
@@ -8151,7 +8160,7 @@
         <v>21</v>
       </c>
       <c r="L197" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="198" spans="1:12">
@@ -8159,10 +8168,10 @@
         <v>134</v>
       </c>
       <c r="B198" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C198" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D198">
         <v>0.5600000000000001</v>
@@ -8186,7 +8195,7 @@
         <v>19</v>
       </c>
       <c r="L198" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="199" spans="1:12">
@@ -8194,10 +8203,10 @@
         <v>134</v>
       </c>
       <c r="B199" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C199" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D199">
         <v>0.58</v>
@@ -8221,7 +8230,7 @@
         <v>19</v>
       </c>
       <c r="L199" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -8229,10 +8238,10 @@
         <v>135</v>
       </c>
       <c r="B200" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C200" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D200">
         <v>0.14</v>
@@ -8256,7 +8265,7 @@
         <v>5</v>
       </c>
       <c r="L200" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -8264,10 +8273,10 @@
         <v>135</v>
       </c>
       <c r="B201" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C201" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D201">
         <v>0.21</v>
@@ -8291,7 +8300,7 @@
         <v>27</v>
       </c>
       <c r="L201" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -8299,10 +8308,10 @@
         <v>136</v>
       </c>
       <c r="B202" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C202" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D202">
         <v>0.45</v>
@@ -8326,7 +8335,7 @@
         <v>17</v>
       </c>
       <c r="L202" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="203" spans="1:12">
@@ -8334,10 +8343,10 @@
         <v>136</v>
       </c>
       <c r="B203" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C203" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D203">
         <v>0.45</v>
@@ -8361,7 +8370,7 @@
         <v>17</v>
       </c>
       <c r="L203" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="204" spans="1:12">
@@ -8369,10 +8378,10 @@
         <v>136</v>
       </c>
       <c r="B204" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C204" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D204">
         <v>0.3</v>
@@ -8396,7 +8405,7 @@
         <v>7</v>
       </c>
       <c r="L204" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -8404,10 +8413,10 @@
         <v>137</v>
       </c>
       <c r="B205" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C205" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D205">
         <v>0.13</v>
@@ -8431,7 +8440,7 @@
         <v>23</v>
       </c>
       <c r="L205" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="206" spans="1:12">
@@ -8439,10 +8448,10 @@
         <v>137</v>
       </c>
       <c r="B206" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C206" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D206">
         <v>0.27</v>
@@ -8466,7 +8475,7 @@
         <v>19</v>
       </c>
       <c r="L206" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="207" spans="1:12">
@@ -8474,10 +8483,10 @@
         <v>138</v>
       </c>
       <c r="B207" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C207" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D207">
         <v>0.33</v>
@@ -8501,7 +8510,7 @@
         <v>11</v>
       </c>
       <c r="L207" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -8509,10 +8518,10 @@
         <v>139</v>
       </c>
       <c r="B208" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C208" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D208">
         <v>0.15</v>
@@ -8536,7 +8545,7 @@
         <v>27</v>
       </c>
       <c r="L208" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -8544,10 +8553,10 @@
         <v>139</v>
       </c>
       <c r="B209" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C209" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D209">
         <v>0.17</v>
@@ -8571,7 +8580,7 @@
         <v>19</v>
       </c>
       <c r="L209" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -8579,10 +8588,10 @@
         <v>140</v>
       </c>
       <c r="B210" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D210">
         <v>0.23</v>
@@ -8606,7 +8615,7 @@
         <v>17</v>
       </c>
       <c r="L210" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -8614,10 +8623,10 @@
         <v>140</v>
       </c>
       <c r="B211" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C211" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D211">
         <v>0.36</v>
@@ -8641,7 +8650,7 @@
         <v>19</v>
       </c>
       <c r="L211" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -8649,10 +8658,10 @@
         <v>141</v>
       </c>
       <c r="B212" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C212" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D212">
         <v>0.21</v>
@@ -8676,7 +8685,7 @@
         <v>23</v>
       </c>
       <c r="L212" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -8684,10 +8693,10 @@
         <v>142</v>
       </c>
       <c r="B213" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C213" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D213">
         <v>0.21</v>
@@ -8711,7 +8720,7 @@
         <v>23</v>
       </c>
       <c r="L213" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -8719,10 +8728,10 @@
         <v>143</v>
       </c>
       <c r="B214" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C214" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D214">
         <v>0.35</v>
@@ -8746,7 +8755,7 @@
         <v>17</v>
       </c>
       <c r="L214" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -8754,10 +8763,10 @@
         <v>143</v>
       </c>
       <c r="B215" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C215" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D215">
         <v>1.43</v>
@@ -8781,7 +8790,7 @@
         <v>17</v>
       </c>
       <c r="L215" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -8789,10 +8798,10 @@
         <v>144</v>
       </c>
       <c r="B216" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C216" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D216">
         <v>0.21</v>
@@ -8816,7 +8825,7 @@
         <v>21</v>
       </c>
       <c r="L216" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="217" spans="1:12">
@@ -8824,10 +8833,10 @@
         <v>144</v>
       </c>
       <c r="B217" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C217" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D217">
         <v>0.23</v>
@@ -8851,7 +8860,7 @@
         <v>5</v>
       </c>
       <c r="L217" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -8859,10 +8868,10 @@
         <v>144</v>
       </c>
       <c r="B218" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C218" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D218">
         <v>0.5</v>
@@ -8886,7 +8895,7 @@
         <v>13</v>
       </c>
       <c r="L218" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="219" spans="1:12">
@@ -8894,10 +8903,10 @@
         <v>145</v>
       </c>
       <c r="B219" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C219" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D219">
         <v>0.26</v>
@@ -8921,7 +8930,7 @@
         <v>14</v>
       </c>
       <c r="L219" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="220" spans="1:12">
@@ -8929,10 +8938,10 @@
         <v>145</v>
       </c>
       <c r="B220" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C220" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D220">
         <v>0.18</v>
@@ -8956,7 +8965,7 @@
         <v>15</v>
       </c>
       <c r="L220" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="221" spans="1:12">
@@ -8964,10 +8973,10 @@
         <v>146</v>
       </c>
       <c r="B221" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C221" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D221">
         <v>0.14</v>
@@ -8991,7 +9000,7 @@
         <v>23</v>
       </c>
       <c r="L221" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="222" spans="1:12">
@@ -8999,10 +9008,10 @@
         <v>146</v>
       </c>
       <c r="B222" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C222" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D222">
         <v>0.39</v>
@@ -9026,7 +9035,7 @@
         <v>19</v>
       </c>
       <c r="L222" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="223" spans="1:12">
@@ -9034,10 +9043,10 @@
         <v>146</v>
       </c>
       <c r="B223" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C223" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D223">
         <v>0.47</v>
@@ -9061,7 +9070,7 @@
         <v>19</v>
       </c>
       <c r="L223" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="224" spans="1:12">
@@ -9069,10 +9078,10 @@
         <v>147</v>
       </c>
       <c r="B224" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C224" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D224">
         <v>0.42</v>
@@ -9096,7 +9105,7 @@
         <v>7</v>
       </c>
       <c r="L224" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="225" spans="1:12">
@@ -9104,10 +9113,10 @@
         <v>148</v>
       </c>
       <c r="B225" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C225" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D225">
         <v>0.18</v>
@@ -9131,7 +9140,7 @@
         <v>19</v>
       </c>
       <c r="L225" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="226" spans="1:12">
@@ -9139,10 +9148,10 @@
         <v>148</v>
       </c>
       <c r="B226" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C226" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D226">
         <v>0.24</v>
@@ -9166,7 +9175,7 @@
         <v>11</v>
       </c>
       <c r="L226" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="227" spans="1:12">
@@ -9174,10 +9183,10 @@
         <v>149</v>
       </c>
       <c r="B227" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C227" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D227">
         <v>0.09</v>
@@ -9201,7 +9210,7 @@
         <v>23</v>
       </c>
       <c r="L227" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="228" spans="1:12">
@@ -9209,10 +9218,10 @@
         <v>149</v>
       </c>
       <c r="B228" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C228" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D228">
         <v>0.35</v>
@@ -9236,7 +9245,7 @@
         <v>17</v>
       </c>
       <c r="L228" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="229" spans="1:12">
@@ -9244,10 +9253,10 @@
         <v>149</v>
       </c>
       <c r="B229" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C229" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D229">
         <v>0.35</v>
@@ -9271,7 +9280,7 @@
         <v>17</v>
       </c>
       <c r="L229" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="230" spans="1:12">
@@ -9279,10 +9288,10 @@
         <v>150</v>
       </c>
       <c r="B230" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C230" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D230">
         <v>0.28</v>
@@ -9306,7 +9315,7 @@
         <v>19</v>
       </c>
       <c r="L230" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="231" spans="1:12">
@@ -9314,10 +9323,10 @@
         <v>150</v>
       </c>
       <c r="B231" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C231" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D231">
         <v>0.27</v>
@@ -9341,7 +9350,7 @@
         <v>19</v>
       </c>
       <c r="L231" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="232" spans="1:12">
@@ -9349,10 +9358,10 @@
         <v>150</v>
       </c>
       <c r="B232" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C232" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D232">
         <v>0.12</v>
@@ -9376,7 +9385,7 @@
         <v>7</v>
       </c>
       <c r="L232" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="233" spans="1:12">
@@ -9384,10 +9393,10 @@
         <v>150</v>
       </c>
       <c r="B233" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C233" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D233">
         <v>0.14</v>
@@ -9411,7 +9420,7 @@
         <v>19</v>
       </c>
       <c r="L233" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="234" spans="1:12">
@@ -9419,10 +9428,10 @@
         <v>151</v>
       </c>
       <c r="B234" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C234" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D234">
         <v>1.14</v>
@@ -9446,7 +9455,7 @@
         <v>27</v>
       </c>
       <c r="L234" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="235" spans="1:12">
@@ -9454,10 +9463,10 @@
         <v>151</v>
       </c>
       <c r="B235" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C235" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D235">
         <v>0.33</v>
@@ -9481,7 +9490,7 @@
         <v>13</v>
       </c>
       <c r="L235" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="236" spans="1:12">
@@ -9489,10 +9498,10 @@
         <v>152</v>
       </c>
       <c r="B236" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C236" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D236">
         <v>0.09</v>
@@ -9516,7 +9525,7 @@
         <v>23</v>
       </c>
       <c r="L236" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="237" spans="1:12">
@@ -9524,10 +9533,10 @@
         <v>153</v>
       </c>
       <c r="B237" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C237" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D237">
         <v>0.28</v>
@@ -9551,7 +9560,7 @@
         <v>19</v>
       </c>
       <c r="L237" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="238" spans="1:12">
@@ -9559,10 +9568,10 @@
         <v>154</v>
       </c>
       <c r="B238" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C238" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D238">
         <v>0.32</v>
@@ -9586,7 +9595,7 @@
         <v>19</v>
       </c>
       <c r="L238" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="239" spans="1:12">
@@ -9594,10 +9603,10 @@
         <v>155</v>
       </c>
       <c r="B239" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C239" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D239">
         <v>3.29</v>
@@ -9621,7 +9630,7 @@
         <v>3</v>
       </c>
       <c r="L239" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="240" spans="1:12">
@@ -9629,10 +9638,10 @@
         <v>155</v>
       </c>
       <c r="B240" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C240" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D240">
         <v>0.2</v>
@@ -9656,7 +9665,7 @@
         <v>3</v>
       </c>
       <c r="L240" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="241" spans="1:12">
@@ -9664,10 +9673,10 @@
         <v>156</v>
       </c>
       <c r="B241" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C241" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D241">
         <v>0.76</v>
@@ -9691,7 +9700,7 @@
         <v>23</v>
       </c>
       <c r="L241" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="242" spans="1:12">
@@ -9699,10 +9708,10 @@
         <v>157</v>
       </c>
       <c r="B242" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C242" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D242">
         <v>0.32</v>
@@ -9726,7 +9735,7 @@
         <v>12</v>
       </c>
       <c r="L242" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="243" spans="1:12">
@@ -9734,10 +9743,10 @@
         <v>158</v>
       </c>
       <c r="B243" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C243" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D243">
         <v>5.43</v>
@@ -9761,7 +9770,7 @@
         <v>5</v>
       </c>
       <c r="L243" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="244" spans="1:12">
@@ -9769,10 +9778,10 @@
         <v>159</v>
       </c>
       <c r="B244" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C244" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D244">
         <v>0.4</v>
@@ -9796,7 +9805,7 @@
         <v>5</v>
       </c>
       <c r="L244" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="245" spans="1:12">
@@ -9804,10 +9813,10 @@
         <v>160</v>
       </c>
       <c r="B245" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C245" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D245">
         <v>0.11</v>
@@ -9831,7 +9840,7 @@
         <v>18</v>
       </c>
       <c r="L245" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="246" spans="1:12">
@@ -9839,10 +9848,10 @@
         <v>161</v>
       </c>
       <c r="B246" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C246" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D246">
         <v>2.57</v>
@@ -9866,7 +9875,7 @@
         <v>5</v>
       </c>
       <c r="L246" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="247" spans="1:12">
@@ -9874,10 +9883,10 @@
         <v>162</v>
       </c>
       <c r="B247" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C247" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D247">
         <v>0.5</v>
@@ -9901,7 +9910,7 @@
         <v>4</v>
       </c>
       <c r="L247" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="248" spans="1:12">
@@ -9909,10 +9918,10 @@
         <v>163</v>
       </c>
       <c r="B248" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C248" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D248">
         <v>0.22</v>
@@ -9936,7 +9945,7 @@
         <v>18</v>
       </c>
       <c r="L248" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="249" spans="1:12">
@@ -9944,10 +9953,10 @@
         <v>164</v>
       </c>
       <c r="B249" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C249" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D249">
         <v>0.17</v>
@@ -9971,7 +9980,7 @@
         <v>18</v>
       </c>
       <c r="L249" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="250" spans="1:12">
@@ -9979,10 +9988,10 @@
         <v>165</v>
       </c>
       <c r="B250" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C250" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D250">
         <v>0.6</v>
@@ -10006,7 +10015,7 @@
         <v>3</v>
       </c>
       <c r="L250" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="251" spans="1:12">
@@ -10014,10 +10023,10 @@
         <v>166</v>
       </c>
       <c r="B251" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C251" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D251">
         <v>0.28</v>
@@ -10041,7 +10050,7 @@
         <v>18</v>
       </c>
       <c r="L251" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="252" spans="1:12">
@@ -10049,10 +10058,10 @@
         <v>167</v>
       </c>
       <c r="B252" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C252" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D252">
         <v>0.11</v>
@@ -10076,7 +10085,7 @@
         <v>18</v>
       </c>
       <c r="L252" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="253" spans="1:12">
@@ -10084,10 +10093,10 @@
         <v>165</v>
       </c>
       <c r="B253" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C253" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D253">
         <v>2.86</v>
@@ -10111,7 +10120,7 @@
         <v>5</v>
       </c>
       <c r="L253" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="254" spans="1:12">
@@ -10119,10 +10128,10 @@
         <v>168</v>
       </c>
       <c r="B254" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C254" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D254">
         <v>0.79</v>
@@ -10140,7 +10149,7 @@
         <v>29</v>
       </c>
       <c r="L254" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="255" spans="1:12">
@@ -10148,10 +10157,10 @@
         <v>162</v>
       </c>
       <c r="B255" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C255" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D255">
         <v>0.83</v>
@@ -10169,7 +10178,7 @@
         <v>29</v>
       </c>
       <c r="L255" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="256" spans="1:12">
@@ -10177,10 +10186,10 @@
         <v>169</v>
       </c>
       <c r="B256" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C256" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D256">
         <v>0.88</v>
@@ -10198,7 +10207,7 @@
         <v>27</v>
       </c>
       <c r="L256" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="257" spans="1:12">
@@ -10206,10 +10215,10 @@
         <v>170</v>
       </c>
       <c r="B257" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C257" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D257">
         <v>0.72</v>
@@ -10227,7 +10236,7 @@
         <v>18</v>
       </c>
       <c r="L257" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="258" spans="1:12">
@@ -10235,10 +10244,10 @@
         <v>171</v>
       </c>
       <c r="B258" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C258" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D258">
         <v>1.6</v>
@@ -10256,7 +10265,7 @@
         <v>18</v>
       </c>
       <c r="L258" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="259" spans="1:12">
@@ -10264,10 +10273,10 @@
         <v>172</v>
       </c>
       <c r="B259" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C259" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D259">
         <v>1.72</v>
@@ -10285,7 +10294,7 @@
         <v>19</v>
       </c>
       <c r="L259" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="260" spans="1:12">
@@ -10293,10 +10302,10 @@
         <v>173</v>
       </c>
       <c r="B260" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C260" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D260">
         <v>1.4</v>
@@ -10314,7 +10323,7 @@
         <v>18</v>
       </c>
       <c r="L260" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="261" spans="1:12">
@@ -10322,10 +10331,10 @@
         <v>174</v>
       </c>
       <c r="B261" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C261" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D261">
         <v>0.65</v>
@@ -10343,7 +10352,7 @@
         <v>13</v>
       </c>
       <c r="L261" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="262" spans="1:12">
@@ -10351,10 +10360,10 @@
         <v>175</v>
       </c>
       <c r="B262" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C262" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D262">
         <v>0.9399999999999999</v>
@@ -10372,7 +10381,7 @@
         <v>13</v>
       </c>
       <c r="L262" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="263" spans="1:12">
@@ -10380,10 +10389,10 @@
         <v>176</v>
       </c>
       <c r="B263" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C263" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D263">
         <v>1.88</v>
@@ -10401,7 +10410,7 @@
         <v>13</v>
       </c>
       <c r="L263" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="264" spans="1:12">
@@ -10409,10 +10418,10 @@
         <v>177</v>
       </c>
       <c r="B264" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C264" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D264">
         <v>2.18</v>
@@ -10430,7 +10439,7 @@
         <v>12</v>
       </c>
       <c r="L264" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="265" spans="1:12">
@@ -10438,10 +10447,10 @@
         <v>178</v>
       </c>
       <c r="B265" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C265" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D265">
         <v>0.36</v>
@@ -10459,7 +10468,7 @@
         <v>18</v>
       </c>
       <c r="L265" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="266" spans="1:12">
@@ -10467,10 +10476,10 @@
         <v>179</v>
       </c>
       <c r="B266" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C266" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D266">
         <v>2.08</v>
@@ -10488,7 +10497,7 @@
         <v>18</v>
       </c>
       <c r="L266" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="267" spans="1:12">
@@ -10496,10 +10505,10 @@
         <v>180</v>
       </c>
       <c r="B267" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C267" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D267">
         <v>2.24</v>
@@ -10517,7 +10526,7 @@
         <v>18</v>
       </c>
       <c r="L267" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="268" spans="1:12">
@@ -10525,10 +10534,10 @@
         <v>181</v>
       </c>
       <c r="B268" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C268" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D268">
         <v>2</v>
@@ -10546,7 +10555,7 @@
         <v>18</v>
       </c>
       <c r="L268" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="269" spans="1:12">
@@ -10554,10 +10563,10 @@
         <v>182</v>
       </c>
       <c r="B269" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C269" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D269">
         <v>0.14</v>
@@ -10575,7 +10584,7 @@
         <v>7</v>
       </c>
       <c r="L269" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="270" spans="1:12">
@@ -10583,10 +10592,10 @@
         <v>183</v>
       </c>
       <c r="B270" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C270" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D270">
         <v>0.14</v>
@@ -10604,7 +10613,7 @@
         <v>7</v>
       </c>
       <c r="L270" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="271" spans="1:12">
@@ -10612,10 +10621,10 @@
         <v>164</v>
       </c>
       <c r="B271" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C271" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D271">
         <v>0.21</v>
@@ -10633,7 +10642,7 @@
         <v>7</v>
       </c>
       <c r="L271" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="272" spans="1:12">
@@ -10641,10 +10650,10 @@
         <v>184</v>
       </c>
       <c r="B272" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C272" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D272">
         <v>0.14</v>
@@ -10662,7 +10671,7 @@
         <v>7</v>
       </c>
       <c r="L272" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="273" spans="1:12">
@@ -10670,10 +10679,10 @@
         <v>185</v>
       </c>
       <c r="B273" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C273" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D273">
         <v>0.15</v>
@@ -10691,7 +10700,7 @@
         <v>6</v>
       </c>
       <c r="L273" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="274" spans="1:12">
@@ -10699,10 +10708,10 @@
         <v>161</v>
       </c>
       <c r="B274" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C274" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D274">
         <v>0.31</v>
@@ -10720,7 +10729,7 @@
         <v>5</v>
       </c>
       <c r="L274" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="275" spans="1:12">
@@ -10728,10 +10737,10 @@
         <v>186</v>
       </c>
       <c r="B275" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C275" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D275">
         <v>0.46</v>
@@ -10749,7 +10758,7 @@
         <v>5</v>
       </c>
       <c r="L275" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="276" spans="1:12">
@@ -10757,10 +10766,10 @@
         <v>160</v>
       </c>
       <c r="B276" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C276" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D276">
         <v>0.63</v>
@@ -10778,7 +10787,7 @@
         <v>15</v>
       </c>
       <c r="L276" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="277" spans="1:12">
@@ -10786,10 +10795,10 @@
         <v>187</v>
       </c>
       <c r="B277" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C277" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D277">
         <v>1.52</v>
@@ -10807,7 +10816,7 @@
         <v>15</v>
       </c>
       <c r="L277" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="278" spans="1:12">
@@ -10815,10 +10824,10 @@
         <v>166</v>
       </c>
       <c r="B278" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C278" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D278">
         <v>2.11</v>
@@ -10836,7 +10845,7 @@
         <v>15</v>
       </c>
       <c r="L278" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="279" spans="1:12">
@@ -10844,10 +10853,10 @@
         <v>171</v>
       </c>
       <c r="B279" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C279" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D279">
         <v>0.18</v>
@@ -10865,7 +10874,7 @@
         <v>12</v>
       </c>
       <c r="L279" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="280" spans="1:12">
@@ -10873,10 +10882,10 @@
         <v>188</v>
       </c>
       <c r="B280" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C280" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D280">
         <v>0.42</v>
@@ -10894,7 +10903,7 @@
         <v>12</v>
       </c>
       <c r="L280" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="281" spans="1:12">
@@ -10902,10 +10911,10 @@
         <v>189</v>
       </c>
       <c r="B281" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C281" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D281">
         <v>1.07</v>
@@ -10923,7 +10932,7 @@
         <v>12</v>
       </c>
       <c r="L281" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="282" spans="1:12">
@@ -10931,10 +10940,10 @@
         <v>183</v>
       </c>
       <c r="B282" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C282" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D282">
         <v>0.43</v>
@@ -10952,7 +10961,7 @@
         <v>9</v>
       </c>
       <c r="L282" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="283" spans="1:12">
@@ -10960,10 +10969,10 @@
         <v>188</v>
       </c>
       <c r="B283" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C283" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D283">
         <v>0.33</v>
@@ -10981,7 +10990,7 @@
         <v>9</v>
       </c>
       <c r="L283" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="284" spans="1:12">
@@ -10989,10 +10998,10 @@
         <v>190</v>
       </c>
       <c r="B284" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C284" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D284">
         <v>0.62</v>
@@ -11010,7 +11019,7 @@
         <v>9</v>
       </c>
       <c r="L284" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="285" spans="1:12">
@@ -11018,10 +11027,10 @@
         <v>176</v>
       </c>
       <c r="B285" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C285" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D285">
         <v>0.11</v>
@@ -11039,7 +11048,7 @@
         <v>11</v>
       </c>
       <c r="L285" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="286" spans="1:12">
@@ -11047,10 +11056,10 @@
         <v>191</v>
       </c>
       <c r="B286" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C286" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D286">
         <v>0.22</v>
@@ -11068,7 +11077,7 @@
         <v>9</v>
       </c>
       <c r="L286" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="287" spans="1:12">
@@ -11076,10 +11085,10 @@
         <v>177</v>
       </c>
       <c r="B287" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C287" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D287">
         <v>0.33</v>
@@ -11097,7 +11106,7 @@
         <v>9</v>
       </c>
       <c r="L287" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="288" spans="1:12">
@@ -11105,10 +11114,10 @@
         <v>192</v>
       </c>
       <c r="B288" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C288" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D288">
         <v>0.11</v>
@@ -11126,7 +11135,7 @@
         <v>9</v>
       </c>
       <c r="L288" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="289" spans="1:12">
@@ -11134,10 +11143,10 @@
         <v>163</v>
       </c>
       <c r="B289" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C289" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D289">
         <v>1.91</v>
@@ -11155,7 +11164,7 @@
         <v>11</v>
       </c>
       <c r="L289" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="290" spans="1:12">
@@ -11163,10 +11172,10 @@
         <v>193</v>
       </c>
       <c r="B290" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C290" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D290">
         <v>2.27</v>
@@ -11184,7 +11193,7 @@
         <v>12</v>
       </c>
       <c r="L290" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="291" spans="1:12">
@@ -11192,10 +11201,10 @@
         <v>173</v>
       </c>
       <c r="B291" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C291" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D291">
         <v>2.64</v>
@@ -11213,7 +11222,7 @@
         <v>16</v>
       </c>
       <c r="L291" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="292" spans="1:12">
@@ -11221,10 +11230,10 @@
         <v>194</v>
       </c>
       <c r="B292" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C292" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D292">
         <v>0.71</v>
@@ -11242,7 +11251,7 @@
         <v>5</v>
       </c>
       <c r="L292" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="293" spans="1:12">
@@ -11250,10 +11259,10 @@
         <v>186</v>
       </c>
       <c r="B293" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C293" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D293">
         <v>0.89</v>
@@ -11271,7 +11280,7 @@
         <v>5</v>
       </c>
       <c r="L293" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="294" spans="1:12">
@@ -11279,10 +11288,10 @@
         <v>195</v>
       </c>
       <c r="B294" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C294" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D294">
         <v>0.15</v>
@@ -11300,7 +11309,7 @@
         <v>6</v>
       </c>
       <c r="L294" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="295" spans="1:12">
@@ -11308,10 +11317,10 @@
         <v>164</v>
       </c>
       <c r="B295" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C295" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D295">
         <v>0.28</v>
@@ -11329,7 +11338,7 @@
         <v>9</v>
       </c>
       <c r="L295" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="296" spans="1:12">
@@ -11337,10 +11346,10 @@
         <v>189</v>
       </c>
       <c r="B296" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C296" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D296">
         <v>5.56</v>
@@ -11358,7 +11367,7 @@
         <v>13</v>
       </c>
       <c r="L296" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="297" spans="1:12">
@@ -11366,10 +11375,10 @@
         <v>189</v>
       </c>
       <c r="B297" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C297" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D297">
         <v>0.19</v>
@@ -11387,7 +11396,7 @@
         <v>29</v>
       </c>
       <c r="L297" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="298" spans="1:12">
@@ -11395,10 +11404,10 @@
         <v>167</v>
       </c>
       <c r="B298" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C298" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D298">
         <v>0.52</v>
@@ -11416,7 +11425,7 @@
         <v>29</v>
       </c>
       <c r="L298" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="299" spans="1:12">
@@ -11424,10 +11433,10 @@
         <v>196</v>
       </c>
       <c r="B299" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C299" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D299">
         <v>0.11</v>
@@ -11445,7 +11454,7 @@
         <v>13</v>
       </c>
       <c r="L299" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="300" spans="1:12">
@@ -11453,10 +11462,10 @@
         <v>184</v>
       </c>
       <c r="B300" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C300" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D300">
         <v>0.09</v>
@@ -11474,7 +11483,7 @@
         <v>12</v>
       </c>
       <c r="L300" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="301" spans="1:12">
@@ -11482,10 +11491,10 @@
         <v>197</v>
       </c>
       <c r="B301" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C301" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D301">
         <v>2</v>
@@ -11503,7 +11512,7 @@
         <v>9</v>
       </c>
       <c r="L301" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="302" spans="1:12">
@@ -11511,10 +11520,10 @@
         <v>198</v>
       </c>
       <c r="B302" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C302" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D302">
         <v>1.29</v>
@@ -11532,7 +11541,7 @@
         <v>9</v>
       </c>
       <c r="L302" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="303" spans="1:12">
@@ -11540,10 +11549,10 @@
         <v>199</v>
       </c>
       <c r="B303" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C303" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D303">
         <v>1.76</v>
@@ -11561,7 +11570,7 @@
         <v>11</v>
       </c>
       <c r="L303" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="304" spans="1:12">
@@ -11569,10 +11578,10 @@
         <v>198</v>
       </c>
       <c r="B304" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C304" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D304">
         <v>1.24</v>
@@ -11590,7 +11599,7 @@
         <v>9</v>
       </c>
       <c r="L304" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="305" spans="1:12">
@@ -11598,10 +11607,10 @@
         <v>200</v>
       </c>
       <c r="B305" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C305" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D305">
         <v>0.11</v>
@@ -11619,7 +11628,7 @@
         <v>7</v>
       </c>
       <c r="L305" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="306" spans="1:12">
@@ -11627,10 +11636,10 @@
         <v>201</v>
       </c>
       <c r="B306" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C306" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D306">
         <v>0.06</v>
@@ -11648,7 +11657,7 @@
         <v>6</v>
       </c>
       <c r="L306" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="307" spans="1:12">
@@ -11656,10 +11665,10 @@
         <v>202</v>
       </c>
       <c r="B307" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C307" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D307">
         <v>0.3</v>
@@ -11677,7 +11686,7 @@
         <v>3</v>
       </c>
       <c r="L307" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="308" spans="1:12">
@@ -11685,10 +11694,10 @@
         <v>203</v>
       </c>
       <c r="B308" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C308" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D308">
         <v>0.53</v>
@@ -11706,7 +11715,7 @@
         <v>18</v>
       </c>
       <c r="L308" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="309" spans="1:12">
@@ -11714,10 +11723,10 @@
         <v>204</v>
       </c>
       <c r="B309" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C309" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D309">
         <v>0.5</v>
@@ -11735,7 +11744,7 @@
         <v>12</v>
       </c>
       <c r="L309" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="310" spans="1:12">
@@ -11743,10 +11752,10 @@
         <v>205</v>
       </c>
       <c r="B310" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C310" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D310">
         <v>1.36</v>
@@ -11764,7 +11773,7 @@
         <v>13</v>
       </c>
       <c r="L310" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="311" spans="1:12">
@@ -11772,10 +11781,10 @@
         <v>204</v>
       </c>
       <c r="B311" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C311" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D311">
         <v>0.21</v>
@@ -11793,7 +11802,7 @@
         <v>6</v>
       </c>
       <c r="L311" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="312" spans="1:12">
@@ -11801,10 +11810,10 @@
         <v>197</v>
       </c>
       <c r="B312" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C312" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D312">
         <v>0.23</v>
@@ -11822,7 +11831,7 @@
         <v>5</v>
       </c>
       <c r="L312" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="313" spans="1:12">
@@ -11830,10 +11839,10 @@
         <v>202</v>
       </c>
       <c r="B313" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C313" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D313">
         <v>1.22</v>
@@ -11851,7 +11860,7 @@
         <v>13</v>
       </c>
       <c r="L313" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="314" spans="1:12">
@@ -11859,10 +11868,10 @@
         <v>202</v>
       </c>
       <c r="B314" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C314" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D314">
         <v>0.27</v>
@@ -11880,7 +11889,7 @@
         <v>9</v>
       </c>
       <c r="L314" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="315" spans="1:12">
@@ -11888,10 +11897,10 @@
         <v>200</v>
       </c>
       <c r="B315" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C315" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D315">
         <v>1.05</v>
@@ -11909,7 +11918,7 @@
         <v>6</v>
       </c>
       <c r="L315" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="316" spans="1:12">
@@ -11917,10 +11926,10 @@
         <v>206</v>
       </c>
       <c r="B316" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C316" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D316">
         <v>0.11</v>
@@ -11938,7 +11947,7 @@
         <v>8</v>
       </c>
       <c r="L316" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="317" spans="1:12">
@@ -11946,10 +11955,10 @@
         <v>207</v>
       </c>
       <c r="B317" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C317" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D317">
         <v>0.11</v>
@@ -11967,7 +11976,7 @@
         <v>9</v>
       </c>
       <c r="L317" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="318" spans="1:12">
@@ -11975,10 +11984,10 @@
         <v>198</v>
       </c>
       <c r="B318" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C318" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D318">
         <v>0.06</v>
@@ -11996,7 +12005,7 @@
         <v>9</v>
       </c>
       <c r="L318" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="319" spans="1:12">
@@ -12004,10 +12013,10 @@
         <v>204</v>
       </c>
       <c r="B319" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C319" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D319">
         <v>1.91</v>
@@ -12025,7 +12034,7 @@
         <v>16</v>
       </c>
       <c r="L319" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="320" spans="1:12">
@@ -12033,10 +12042,10 @@
         <v>197</v>
       </c>
       <c r="B320" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C320" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D320">
         <v>0.4</v>
@@ -12054,7 +12063,7 @@
         <v>5</v>
       </c>
       <c r="L320" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="321" spans="1:12">
@@ -12062,10 +12071,10 @@
         <v>208</v>
       </c>
       <c r="B321" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C321" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D321">
         <v>0.5</v>
@@ -12083,7 +12092,7 @@
         <v>5</v>
       </c>
       <c r="L321" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="322" spans="1:12">
@@ -12091,10 +12100,10 @@
         <v>197</v>
       </c>
       <c r="B322" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C322" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D322">
         <v>1.15</v>
@@ -12112,7 +12121,7 @@
         <v>4</v>
       </c>
       <c r="L322" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="323" spans="1:12">
@@ -12120,10 +12129,10 @@
         <v>209</v>
       </c>
       <c r="B323" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C323" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D323">
         <v>1.38</v>
@@ -12141,7 +12150,7 @@
         <v>5</v>
       </c>
       <c r="L323" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="324" spans="1:12">
@@ -12149,10 +12158,10 @@
         <v>202</v>
       </c>
       <c r="B324" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C324" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D324">
         <v>1.5</v>
@@ -12170,7 +12179,7 @@
         <v>8</v>
       </c>
       <c r="L324" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="325" spans="1:12">
@@ -12178,10 +12187,10 @@
         <v>210</v>
       </c>
       <c r="B325" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C325" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D325">
         <v>0.38</v>
@@ -12199,7 +12208,7 @@
         <v>17</v>
       </c>
       <c r="L325" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="326" spans="1:12">
@@ -12207,10 +12216,10 @@
         <v>211</v>
       </c>
       <c r="B326" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C326" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D326">
         <v>0.14</v>
@@ -12228,7 +12237,7 @@
         <v>11</v>
       </c>
       <c r="L326" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="327" spans="1:12">
@@ -12236,10 +12245,10 @@
         <v>209</v>
       </c>
       <c r="B327" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C327" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D327">
         <v>0.21</v>
@@ -12257,7 +12266,7 @@
         <v>13</v>
       </c>
       <c r="L327" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="328" spans="1:12">
@@ -12265,10 +12274,10 @@
         <v>200</v>
       </c>
       <c r="B328" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C328" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D328">
         <v>0.17</v>
@@ -12286,7 +12295,7 @@
         <v>9</v>
       </c>
       <c r="L328" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="329" spans="1:12">
@@ -12294,10 +12303,10 @@
         <v>199</v>
       </c>
       <c r="B329" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C329" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D329">
         <v>0.23</v>
@@ -12315,7 +12324,7 @@
         <v>4</v>
       </c>
       <c r="L329" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="330" spans="1:12">
@@ -12323,10 +12332,10 @@
         <v>207</v>
       </c>
       <c r="B330" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C330" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D330">
         <v>0.31</v>
@@ -12344,7 +12353,7 @@
         <v>4</v>
       </c>
       <c r="L330" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="331" spans="1:12">
@@ -12352,10 +12361,10 @@
         <v>200</v>
       </c>
       <c r="B331" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C331" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D331">
         <v>0.08</v>
@@ -12373,7 +12382,7 @@
         <v>12</v>
       </c>
       <c r="L331" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="332" spans="1:12">
@@ -12381,10 +12390,10 @@
         <v>201</v>
       </c>
       <c r="B332" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C332" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D332">
         <v>0.12</v>
@@ -12402,7 +12411,7 @@
         <v>13</v>
       </c>
       <c r="L332" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="333" spans="1:12">
@@ -12410,10 +12419,10 @@
         <v>208</v>
       </c>
       <c r="B333" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C333" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D333">
         <v>0.14</v>
@@ -12431,7 +12440,7 @@
         <v>10</v>
       </c>
       <c r="L333" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="334" spans="1:12">
@@ -12439,10 +12448,10 @@
         <v>198</v>
       </c>
       <c r="B334" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C334" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D334">
         <v>0.18</v>
@@ -12460,7 +12469,7 @@
         <v>11</v>
       </c>
       <c r="L334" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="335" spans="1:12">
@@ -12468,10 +12477,10 @@
         <v>201</v>
       </c>
       <c r="B335" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C335" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D335">
         <v>1.47</v>
@@ -12489,7 +12498,7 @@
         <v>10</v>
       </c>
       <c r="L335" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="336" spans="1:12">
@@ -12497,10 +12506,10 @@
         <v>209</v>
       </c>
       <c r="B336" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C336" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D336">
         <v>0.25</v>
@@ -12518,7 +12527,7 @@
         <v>9</v>
       </c>
       <c r="L336" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="337" spans="1:12">
@@ -12526,10 +12535,10 @@
         <v>209</v>
       </c>
       <c r="B337" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C337" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D337">
         <v>1</v>
@@ -12547,7 +12556,7 @@
         <v>4</v>
       </c>
       <c r="L337" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="338" spans="1:12">
@@ -12555,10 +12564,10 @@
         <v>212</v>
       </c>
       <c r="B338" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C338" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D338">
         <v>2</v>
@@ -12576,7 +12585,7 @@
         <v>9</v>
       </c>
       <c r="L338" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="339" spans="1:12">
@@ -12584,10 +12593,10 @@
         <v>213</v>
       </c>
       <c r="B339" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C339" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D339">
         <v>1.53</v>
@@ -12605,7 +12614,7 @@
         <v>9</v>
       </c>
       <c r="L339" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="340" spans="1:12">
@@ -12613,10 +12622,10 @@
         <v>214</v>
       </c>
       <c r="B340" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C340" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D340">
         <v>0.3</v>
@@ -12634,7 +12643,7 @@
         <v>7</v>
       </c>
       <c r="L340" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="341" spans="1:12">
@@ -12642,10 +12651,10 @@
         <v>215</v>
       </c>
       <c r="B341" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C341" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D341">
         <v>0.2</v>
@@ -12663,7 +12672,7 @@
         <v>7</v>
       </c>
       <c r="L341" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="342" spans="1:12">
@@ -12671,10 +12680,10 @@
         <v>216</v>
       </c>
       <c r="B342" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C342" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D342">
         <v>0.38</v>
@@ -12692,7 +12701,7 @@
         <v>16</v>
       </c>
       <c r="L342" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="343" spans="1:12">
@@ -12700,10 +12709,10 @@
         <v>215</v>
       </c>
       <c r="B343" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C343" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="D343">
         <v>0.19</v>
@@ -12721,7 +12730,7 @@
         <v>19</v>
       </c>
       <c r="L343" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="344" spans="1:12">
@@ -12729,10 +12738,10 @@
         <v>217</v>
       </c>
       <c r="B344" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C344" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D344">
         <v>0.36</v>
@@ -12750,7 +12759,7 @@
         <v>16</v>
       </c>
       <c r="L344" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="345" spans="1:12">
@@ -12758,10 +12767,10 @@
         <v>213</v>
       </c>
       <c r="B345" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C345" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D345">
         <v>0.4</v>
@@ -12779,7 +12788,7 @@
         <v>18</v>
       </c>
       <c r="L345" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="346" spans="1:12">
@@ -12787,10 +12796,10 @@
         <v>218</v>
       </c>
       <c r="B346" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C346" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D346">
         <v>1.18</v>
@@ -12808,7 +12817,7 @@
         <v>16</v>
       </c>
       <c r="L346" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="347" spans="1:12">
@@ -12816,10 +12825,10 @@
         <v>219</v>
       </c>
       <c r="B347" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C347" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D347">
         <v>0.65</v>
@@ -12837,7 +12846,7 @@
         <v>13</v>
       </c>
       <c r="L347" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="348" spans="1:12">
@@ -12845,10 +12854,10 @@
         <v>220</v>
       </c>
       <c r="B348" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C348" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D348">
         <v>0.8</v>
@@ -12866,7 +12875,7 @@
         <v>14</v>
       </c>
       <c r="L348" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="349" spans="1:12">
@@ -12874,10 +12883,10 @@
         <v>221</v>
       </c>
       <c r="B349" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C349" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D349">
         <v>0.48</v>
@@ -12895,7 +12904,7 @@
         <v>17</v>
       </c>
       <c r="L349" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="350" spans="1:12">
@@ -12903,10 +12912,10 @@
         <v>222</v>
       </c>
       <c r="B350" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C350" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D350">
         <v>0.32</v>
@@ -12924,7 +12933,7 @@
         <v>16</v>
       </c>
       <c r="L350" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="351" spans="1:12">
@@ -12932,10 +12941,10 @@
         <v>223</v>
       </c>
       <c r="B351" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C351" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D351">
         <v>0.14</v>
@@ -12953,7 +12962,7 @@
         <v>8</v>
       </c>
       <c r="L351" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="352" spans="1:12">
@@ -12961,10 +12970,10 @@
         <v>224</v>
       </c>
       <c r="B352" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C352" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D352">
         <v>0.21</v>
@@ -12982,7 +12991,7 @@
         <v>9</v>
       </c>
       <c r="L352" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="353" spans="1:12">
@@ -12990,10 +12999,10 @@
         <v>225</v>
       </c>
       <c r="B353" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C353" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D353">
         <v>0.14</v>
@@ -13011,7 +13020,7 @@
         <v>7</v>
       </c>
       <c r="L353" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="354" spans="1:12">
@@ -13019,10 +13028,10 @@
         <v>226</v>
       </c>
       <c r="B354" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C354" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D354">
         <v>0.43</v>
@@ -13040,7 +13049,7 @@
         <v>9</v>
       </c>
       <c r="L354" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="355" spans="1:12">
@@ -13048,10 +13057,10 @@
         <v>214</v>
       </c>
       <c r="B355" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C355" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D355">
         <v>0.06</v>
@@ -13069,7 +13078,7 @@
         <v>9</v>
       </c>
       <c r="L355" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="356" spans="1:12">
@@ -13077,10 +13086,10 @@
         <v>224</v>
       </c>
       <c r="B356" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C356" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D356">
         <v>1.14</v>
@@ -13098,7 +13107,7 @@
         <v>11</v>
       </c>
       <c r="L356" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="357" spans="1:12">
@@ -13106,10 +13115,10 @@
         <v>225</v>
       </c>
       <c r="B357" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C357" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D357">
         <v>0.82</v>
@@ -13127,7 +13136,7 @@
         <v>9</v>
       </c>
       <c r="L357" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="358" spans="1:12">
@@ -13135,10 +13144,10 @@
         <v>221</v>
       </c>
       <c r="B358" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C358" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D358">
         <v>0.42</v>
@@ -13156,7 +13165,7 @@
         <v>5</v>
       </c>
       <c r="L358" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="359" spans="1:12">
@@ -13164,10 +13173,10 @@
         <v>227</v>
       </c>
       <c r="B359" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C359" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D359">
         <v>0.77</v>
@@ -13185,7 +13194,7 @@
         <v>4</v>
       </c>
       <c r="L359" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="360" spans="1:12">
@@ -13193,10 +13202,10 @@
         <v>214</v>
       </c>
       <c r="B360" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C360" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D360">
         <v>1.78</v>
@@ -13214,7 +13223,7 @@
         <v>7</v>
       </c>
       <c r="L360" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="361" spans="1:12">
@@ -13222,10 +13231,10 @@
         <v>223</v>
       </c>
       <c r="B361" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C361" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D361">
         <v>0.35</v>
@@ -13243,7 +13252,7 @@
         <v>15</v>
       </c>
       <c r="L361" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="362" spans="1:12">
@@ -13251,10 +13260,10 @@
         <v>228</v>
       </c>
       <c r="B362" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C362" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D362">
         <v>0.14</v>
@@ -13272,7 +13281,7 @@
         <v>9</v>
       </c>
       <c r="L362" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="363" spans="1:12">
@@ -13280,10 +13289,10 @@
         <v>214</v>
       </c>
       <c r="B363" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C363" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D363">
         <v>0.26</v>
@@ -13301,7 +13310,7 @@
         <v>8</v>
       </c>
       <c r="L363" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="364" spans="1:12">
@@ -13309,10 +13318,10 @@
         <v>215</v>
       </c>
       <c r="B364" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C364" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D364">
         <v>0.17</v>
@@ -13330,7 +13339,7 @@
         <v>9</v>
       </c>
       <c r="L364" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="365" spans="1:12">
@@ -13338,10 +13347,10 @@
         <v>229</v>
       </c>
       <c r="B365" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C365" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D365">
         <v>0.38</v>
@@ -13359,7 +13368,7 @@
         <v>3</v>
       </c>
       <c r="L365" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="366" spans="1:12">
@@ -13367,10 +13376,10 @@
         <v>230</v>
       </c>
       <c r="B366" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C366" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D366">
         <v>0.23</v>
@@ -13388,7 +13397,7 @@
         <v>4</v>
       </c>
       <c r="L366" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="367" spans="1:12">
@@ -13396,10 +13405,10 @@
         <v>216</v>
       </c>
       <c r="B367" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C367" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D367">
         <v>0.08</v>
@@ -13417,7 +13426,7 @@
         <v>11</v>
       </c>
       <c r="L367" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="368" spans="1:12">
@@ -13425,10 +13434,10 @@
         <v>217</v>
       </c>
       <c r="B368" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C368" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D368">
         <v>0.12</v>
@@ -13446,7 +13455,7 @@
         <v>13</v>
       </c>
       <c r="L368" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="369" spans="1:12">
@@ -13454,10 +13463,10 @@
         <v>231</v>
       </c>
       <c r="B369" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C369" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D369">
         <v>0.19</v>
@@ -13475,7 +13484,7 @@
         <v>12</v>
       </c>
       <c r="L369" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="370" spans="1:12">
@@ -13483,10 +13492,10 @@
         <v>213</v>
       </c>
       <c r="B370" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C370" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D370">
         <v>0.12</v>
@@ -13504,7 +13513,7 @@
         <v>11</v>
       </c>
       <c r="L370" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="371" spans="1:12">
@@ -13512,10 +13521,10 @@
         <v>226</v>
       </c>
       <c r="B371" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C371" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D371">
         <v>0.04</v>
@@ -13533,7 +13542,7 @@
         <v>13</v>
       </c>
       <c r="L371" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="372" spans="1:12">
@@ -13541,10 +13550,10 @@
         <v>232</v>
       </c>
       <c r="B372" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C372" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D372">
         <v>0.15</v>
@@ -13562,7 +13571,7 @@
         <v>13</v>
       </c>
       <c r="L372" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="373" spans="1:12">
@@ -13570,10 +13579,10 @@
         <v>228</v>
       </c>
       <c r="B373" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C373" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D373">
         <v>0.57</v>
@@ -13591,7 +13600,7 @@
         <v>11</v>
       </c>
       <c r="L373" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="374" spans="1:12">
@@ -13599,10 +13608,10 @@
         <v>219</v>
       </c>
       <c r="B374" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C374" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D374">
         <v>0.89</v>
@@ -13620,7 +13629,7 @@
         <v>12</v>
       </c>
       <c r="L374" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="375" spans="1:12">
@@ -13628,10 +13637,10 @@
         <v>229</v>
       </c>
       <c r="B375" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C375" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D375">
         <v>0.15</v>
@@ -13649,7 +13658,7 @@
         <v>11</v>
       </c>
       <c r="L375" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="376" spans="1:12">
@@ -13657,10 +13666,10 @@
         <v>230</v>
       </c>
       <c r="B376" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C376" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D376">
         <v>0.3</v>
@@ -13678,7 +13687,7 @@
         <v>11</v>
       </c>
       <c r="L376" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="377" spans="1:12">
@@ -13686,10 +13695,10 @@
         <v>233</v>
       </c>
       <c r="B377" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C377" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D377">
         <v>0.4</v>
@@ -13707,7 +13716,7 @@
         <v>11</v>
       </c>
       <c r="L377" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="378" spans="1:12">
@@ -13715,10 +13724,10 @@
         <v>229</v>
       </c>
       <c r="B378" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C378" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D378">
         <v>0.6</v>
@@ -13736,7 +13745,7 @@
         <v>13</v>
       </c>
       <c r="L378" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="379" spans="1:12">
@@ -13744,10 +13753,10 @@
         <v>234</v>
       </c>
       <c r="B379" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C379" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D379">
         <v>0.25</v>
@@ -13765,7 +13774,7 @@
         <v>13</v>
       </c>
       <c r="L379" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="380" spans="1:12">
@@ -13773,10 +13782,10 @@
         <v>235</v>
       </c>
       <c r="B380" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C380" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D380">
         <v>0.36</v>
@@ -13794,7 +13803,7 @@
         <v>13</v>
       </c>
       <c r="L380" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="381" spans="1:12">
@@ -13802,10 +13811,10 @@
         <v>224</v>
       </c>
       <c r="B381" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C381" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D381">
         <v>0.33</v>
@@ -13823,7 +13832,7 @@
         <v>13</v>
       </c>
       <c r="L381" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="382" spans="1:12">
@@ -13831,10 +13840,10 @@
         <v>233</v>
       </c>
       <c r="B382" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C382" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D382">
         <v>0.21</v>
@@ -13852,7 +13861,7 @@
         <v>13</v>
       </c>
       <c r="L382" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="383" spans="1:12">
@@ -13860,10 +13869,10 @@
         <v>236</v>
       </c>
       <c r="B383" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C383" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D383">
         <v>0.5</v>
@@ -13881,7 +13890,7 @@
         <v>11</v>
       </c>
       <c r="L383" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="384" spans="1:12">
@@ -13889,10 +13898,10 @@
         <v>229</v>
       </c>
       <c r="B384" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C384" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D384">
         <v>0.18</v>
@@ -13910,7 +13919,7 @@
         <v>18</v>
       </c>
       <c r="L384" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="385" spans="1:12">
@@ -13918,10 +13927,10 @@
         <v>218</v>
       </c>
       <c r="B385" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C385" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D385">
         <v>0.22</v>
@@ -13939,7 +13948,7 @@
         <v>18</v>
       </c>
       <c r="L385" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="386" spans="1:12">
@@ -13947,10 +13956,10 @@
         <v>237</v>
       </c>
       <c r="B386" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C386" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D386">
         <v>0.15</v>
@@ -13968,7 +13977,7 @@
         <v>16</v>
       </c>
       <c r="L386" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="387" spans="1:12">
@@ -13976,10 +13985,10 @@
         <v>238</v>
       </c>
       <c r="B387" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C387" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D387">
         <v>0.14</v>
@@ -13997,7 +14006,7 @@
         <v>17</v>
       </c>
       <c r="L387" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="388" spans="1:12">
@@ -14005,10 +14014,10 @@
         <v>230</v>
       </c>
       <c r="B388" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C388" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D388">
         <v>0.21</v>
@@ -14026,7 +14035,7 @@
         <v>17</v>
       </c>
       <c r="L388" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="389" spans="1:12">
@@ -14034,10 +14043,10 @@
         <v>239</v>
       </c>
       <c r="B389" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C389" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D389">
         <v>0.24</v>
@@ -14055,7 +14064,7 @@
         <v>16</v>
       </c>
       <c r="L389" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="390" spans="1:12">
@@ -14063,10 +14072,10 @@
         <v>238</v>
       </c>
       <c r="B390" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C390" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D390">
         <v>0.28</v>
@@ -14084,7 +14093,7 @@
         <v>15</v>
       </c>
       <c r="L390" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="391" spans="1:12">
@@ -14092,10 +14101,10 @@
         <v>212</v>
       </c>
       <c r="B391" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C391" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D391">
         <v>0.39</v>
@@ -14113,7 +14122,7 @@
         <v>12</v>
       </c>
       <c r="L391" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="392" spans="1:12">
@@ -14121,10 +14130,10 @@
         <v>224</v>
       </c>
       <c r="B392" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C392" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D392">
         <v>0.5</v>
@@ -14142,7 +14151,7 @@
         <v>11</v>
       </c>
       <c r="L392" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="393" spans="1:12">
@@ -14150,10 +14159,10 @@
         <v>236</v>
       </c>
       <c r="B393" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C393" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D393">
         <v>0.33</v>
@@ -14171,7 +14180,7 @@
         <v>12</v>
       </c>
       <c r="L393" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="394" spans="1:12">
@@ -14179,10 +14188,10 @@
         <v>218</v>
       </c>
       <c r="B394" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C394" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D394">
         <v>0.21</v>
@@ -14200,7 +14209,7 @@
         <v>7</v>
       </c>
       <c r="L394" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="395" spans="1:12">
@@ -14208,10 +14217,10 @@
         <v>235</v>
       </c>
       <c r="B395" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C395" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D395">
         <v>0.36</v>
@@ -14229,7 +14238,7 @@
         <v>7</v>
       </c>
       <c r="L395" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="396" spans="1:12">
@@ -14237,10 +14246,10 @@
         <v>222</v>
       </c>
       <c r="B396" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C396" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D396">
         <v>0.21</v>
@@ -14258,7 +14267,7 @@
         <v>8</v>
       </c>
       <c r="L396" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="397" spans="1:12">
@@ -14266,10 +14275,10 @@
         <v>231</v>
       </c>
       <c r="B397" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C397" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D397">
         <v>0.39</v>
@@ -14287,7 +14296,7 @@
         <v>16</v>
       </c>
       <c r="L397" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="398" spans="1:12">
@@ -14295,10 +14304,10 @@
         <v>213</v>
       </c>
       <c r="B398" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C398" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D398">
         <v>0.46</v>
@@ -14316,7 +14325,7 @@
         <v>16</v>
       </c>
       <c r="L398" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="399" spans="1:12">
@@ -14324,10 +14333,10 @@
         <v>240</v>
       </c>
       <c r="B399" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C399" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="D399">
         <v>0.54</v>
@@ -14345,7 +14354,7 @@
         <v>18</v>
       </c>
       <c r="L399" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="400" spans="1:12">
@@ -14353,10 +14362,10 @@
         <v>241</v>
       </c>
       <c r="B400" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C400" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D400">
         <v>0.1</v>
@@ -14374,7 +14383,7 @@
         <v>16</v>
       </c>
       <c r="L400" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="401" spans="1:12">
@@ -14382,10 +14391,10 @@
         <v>230</v>
       </c>
       <c r="B401" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C401" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D401">
         <v>0.24</v>
@@ -14403,7 +14412,7 @@
         <v>16</v>
       </c>
       <c r="L401" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="402" spans="1:12">
@@ -14411,10 +14420,10 @@
         <v>239</v>
       </c>
       <c r="B402" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C402" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D402">
         <v>0.38</v>
@@ -14432,7 +14441,7 @@
         <v>16</v>
       </c>
       <c r="L402" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="403" spans="1:12">
@@ -14440,10 +14449,10 @@
         <v>235</v>
       </c>
       <c r="B403" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C403" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D403">
         <v>0.18</v>
@@ -14461,7 +14470,7 @@
         <v>18</v>
       </c>
       <c r="L403" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="404" spans="1:12">
@@ -14469,10 +14478,10 @@
         <v>219</v>
       </c>
       <c r="B404" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C404" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D404">
         <v>0.14</v>
@@ -14490,7 +14499,7 @@
         <v>18</v>
       </c>
       <c r="L404" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="405" spans="1:12">
@@ -14498,10 +14507,10 @@
         <v>235</v>
       </c>
       <c r="B405" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C405" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D405">
         <v>0.14</v>
@@ -14519,7 +14528,7 @@
         <v>18</v>
       </c>
       <c r="L405" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="406" spans="1:12">
@@ -14527,28 +14536,115 @@
         <v>219</v>
       </c>
       <c r="B406" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C406" t="s">
-        <v>284</v>
-      </c>
-      <c r="D406" t="s">
-        <v>287</v>
-      </c>
-      <c r="E406" t="s">
-        <v>288</v>
-      </c>
-      <c r="F406" t="s">
-        <v>289</v>
-      </c>
-      <c r="G406" t="s">
+        <v>287</v>
+      </c>
+      <c r="D406">
+        <v>0.11</v>
+      </c>
+      <c r="E406">
+        <v>56.79</v>
+      </c>
+      <c r="F406">
+        <v>4</v>
+      </c>
+      <c r="G406">
+        <v>1.43</v>
+      </c>
+      <c r="K406">
+        <v>18</v>
+      </c>
+      <c r="L406" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="407" spans="1:12">
+      <c r="A407" t="s">
+        <v>242</v>
+      </c>
+      <c r="B407" t="s">
+        <v>250</v>
+      </c>
+      <c r="C407" t="s">
+        <v>286</v>
+      </c>
+      <c r="D407">
+        <v>0.09</v>
+      </c>
+      <c r="E407">
+        <v>58.18</v>
+      </c>
+      <c r="F407">
+        <v>0</v>
+      </c>
+      <c r="G407">
+        <v>0.55</v>
+      </c>
+      <c r="K407">
+        <v>13</v>
+      </c>
+      <c r="L407" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="408" spans="1:12">
+      <c r="A408" t="s">
+        <v>243</v>
+      </c>
+      <c r="B408" t="s">
+        <v>275</v>
+      </c>
+      <c r="C408" t="s">
+        <v>287</v>
+      </c>
+      <c r="D408">
+        <v>0.21</v>
+      </c>
+      <c r="E408">
+        <v>57.5</v>
+      </c>
+      <c r="F408">
+        <v>0</v>
+      </c>
+      <c r="G408">
+        <v>10</v>
+      </c>
+      <c r="K408">
+        <v>9</v>
+      </c>
+      <c r="L408" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="409" spans="1:12">
+      <c r="A409" t="s">
+        <v>244</v>
+      </c>
+      <c r="B409" t="s">
+        <v>282</v>
+      </c>
+      <c r="C409" t="s">
+        <v>287</v>
+      </c>
+      <c r="D409" t="s">
         <v>290</v>
       </c>
-      <c r="K406" t="s">
+      <c r="E409" t="s">
         <v>291</v>
       </c>
-      <c r="L406" t="s">
+      <c r="F409" t="s">
+        <v>292</v>
+      </c>
+      <c r="G409" t="s">
         <v>293</v>
+      </c>
+      <c r="K409" t="s">
+        <v>294</v>
+      </c>
+      <c r="L409" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>

--- a/data/pest_disease_control.xlsx
+++ b/data/pest_disease_control.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="293">
   <si>
     <t>Date</t>
   </si>
@@ -897,94 +897,7 @@
     <t>2026-02-04</t>
   </si>
   <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>2525</t>
-  </si>
-  <si>
-    <t>N14</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>15.71</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>2026/27</t>
-  </si>
-  <si>
     <t>Allice</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>2026-06-27</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-06-22</t>
-  </si>
-  <si>
-    <t>2026-06-23</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>2026-06-16</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>2026-06-21</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L468"/>
+  <dimension ref="A1:L409"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -12243,7 +12156,7 @@
         <v>15.35</v>
       </c>
       <c r="I311" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="J311">
         <v>45</v>
@@ -15683,2077 +15596,6 @@
       </c>
       <c r="L409" t="s">
         <v>202</v>
-      </c>
-    </row>
-    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A410" t="s">
-        <v>292</v>
-      </c>
-      <c r="B410" t="s">
-        <v>293</v>
-      </c>
-      <c r="C410" t="s">
-        <v>294</v>
-      </c>
-      <c r="D410" t="s">
-        <v>295</v>
-      </c>
-      <c r="E410" t="s">
-        <v>296</v>
-      </c>
-      <c r="F410" t="s">
-        <v>297</v>
-      </c>
-      <c r="G410" t="s">
-        <v>298</v>
-      </c>
-      <c r="H410">
-        <v>0</v>
-      </c>
-      <c r="J410">
-        <v>0</v>
-      </c>
-      <c r="K410" t="s">
-        <v>299</v>
-      </c>
-      <c r="L410" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A411" t="s">
-        <v>302</v>
-      </c>
-      <c r="B411" t="s">
-        <v>41</v>
-      </c>
-      <c r="C411" t="s">
-        <v>21</v>
-      </c>
-      <c r="D411">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E411">
-        <v>40.71</v>
-      </c>
-      <c r="F411">
-        <v>0</v>
-      </c>
-      <c r="G411">
-        <v>0</v>
-      </c>
-      <c r="H411">
-        <v>10</v>
-      </c>
-      <c r="I411" t="s">
-        <v>301</v>
-      </c>
-      <c r="J411">
-        <v>4.5</v>
-      </c>
-      <c r="K411">
-        <v>8</v>
-      </c>
-      <c r="L411" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A412" t="s">
-        <v>303</v>
-      </c>
-      <c r="B412" t="s">
-        <v>41</v>
-      </c>
-      <c r="C412" t="s">
-        <v>21</v>
-      </c>
-      <c r="D412">
-        <v>0.21</v>
-      </c>
-      <c r="E412">
-        <v>39.29</v>
-      </c>
-      <c r="F412">
-        <v>0</v>
-      </c>
-      <c r="G412">
-        <v>0</v>
-      </c>
-      <c r="H412">
-        <v>0</v>
-      </c>
-      <c r="J412">
-        <v>0</v>
-      </c>
-      <c r="K412">
-        <v>9</v>
-      </c>
-      <c r="L412" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A413" t="s">
-        <v>304</v>
-      </c>
-      <c r="B413" t="s">
-        <v>41</v>
-      </c>
-      <c r="C413" t="s">
-        <v>21</v>
-      </c>
-      <c r="D413">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E413">
-        <v>61.43</v>
-      </c>
-      <c r="F413">
-        <v>0</v>
-      </c>
-      <c r="G413">
-        <v>0</v>
-      </c>
-      <c r="H413">
-        <v>0</v>
-      </c>
-      <c r="J413">
-        <v>0</v>
-      </c>
-      <c r="K413">
-        <v>7</v>
-      </c>
-      <c r="L413" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A414" t="s">
-        <v>305</v>
-      </c>
-      <c r="B414" t="s">
-        <v>62</v>
-      </c>
-      <c r="C414" t="s">
-        <v>29</v>
-      </c>
-      <c r="D414">
-        <v>0.43</v>
-      </c>
-      <c r="E414">
-        <v>40.479999999999997</v>
-      </c>
-      <c r="F414">
-        <v>0</v>
-      </c>
-      <c r="G414">
-        <v>1.9</v>
-      </c>
-      <c r="H414">
-        <v>0</v>
-      </c>
-      <c r="J414">
-        <v>0</v>
-      </c>
-      <c r="K414">
-        <v>9</v>
-      </c>
-      <c r="L414" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A415" t="s">
-        <v>306</v>
-      </c>
-      <c r="B415" t="s">
-        <v>17</v>
-      </c>
-      <c r="C415" t="s">
-        <v>21</v>
-      </c>
-      <c r="D415">
-        <v>0.06</v>
-      </c>
-      <c r="E415">
-        <v>41.67</v>
-      </c>
-      <c r="F415">
-        <v>0</v>
-      </c>
-      <c r="G415">
-        <v>0</v>
-      </c>
-      <c r="H415">
-        <v>15.35</v>
-      </c>
-      <c r="I415" t="s">
-        <v>301</v>
-      </c>
-      <c r="J415">
-        <v>45</v>
-      </c>
-      <c r="K415">
-        <v>9</v>
-      </c>
-      <c r="L415" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A416" t="s">
-        <v>307</v>
-      </c>
-      <c r="B416" t="s">
-        <v>69</v>
-      </c>
-      <c r="C416" t="s">
-        <v>29</v>
-      </c>
-      <c r="D416">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="E416">
-        <v>22.27</v>
-      </c>
-      <c r="F416">
-        <v>0</v>
-      </c>
-      <c r="G416">
-        <v>0</v>
-      </c>
-      <c r="H416">
-        <v>0</v>
-      </c>
-      <c r="J416">
-        <v>0</v>
-      </c>
-      <c r="K416">
-        <v>11</v>
-      </c>
-      <c r="L416" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A417" t="s">
-        <v>308</v>
-      </c>
-      <c r="B417" t="s">
-        <v>69</v>
-      </c>
-      <c r="C417" t="s">
-        <v>29</v>
-      </c>
-      <c r="D417">
-        <v>0.82</v>
-      </c>
-      <c r="E417">
-        <v>29.55</v>
-      </c>
-      <c r="F417">
-        <v>0</v>
-      </c>
-      <c r="G417">
-        <v>0</v>
-      </c>
-      <c r="H417">
-        <v>0</v>
-      </c>
-      <c r="J417">
-        <v>0</v>
-      </c>
-      <c r="K417">
-        <v>9</v>
-      </c>
-      <c r="L417" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A418" t="s">
-        <v>292</v>
-      </c>
-      <c r="B418" t="s">
-        <v>100</v>
-      </c>
-      <c r="C418" t="s">
-        <v>21</v>
-      </c>
-      <c r="D418">
-        <v>0.42</v>
-      </c>
-      <c r="E418">
-        <v>49.17</v>
-      </c>
-      <c r="F418">
-        <v>0</v>
-      </c>
-      <c r="G418">
-        <v>0</v>
-      </c>
-      <c r="H418">
-        <v>0</v>
-      </c>
-      <c r="J418">
-        <v>0</v>
-      </c>
-      <c r="K418">
-        <v>5</v>
-      </c>
-      <c r="L418" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A419" t="s">
-        <v>302</v>
-      </c>
-      <c r="B419" t="s">
-        <v>80</v>
-      </c>
-      <c r="C419" t="s">
-        <v>29</v>
-      </c>
-      <c r="D419">
-        <v>0.77</v>
-      </c>
-      <c r="E419">
-        <v>4.62</v>
-      </c>
-      <c r="F419">
-        <v>0</v>
-      </c>
-      <c r="G419">
-        <v>0</v>
-      </c>
-      <c r="H419">
-        <v>0</v>
-      </c>
-      <c r="J419">
-        <v>0</v>
-      </c>
-      <c r="K419">
-        <v>4</v>
-      </c>
-      <c r="L419" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A420" t="s">
-        <v>303</v>
-      </c>
-      <c r="B420" t="s">
-        <v>53</v>
-      </c>
-      <c r="C420" t="s">
-        <v>29</v>
-      </c>
-      <c r="D420">
-        <v>1.78</v>
-      </c>
-      <c r="E420">
-        <v>26.11</v>
-      </c>
-      <c r="F420">
-        <v>0</v>
-      </c>
-      <c r="G420">
-        <v>0</v>
-      </c>
-      <c r="H420">
-        <v>0</v>
-      </c>
-      <c r="J420">
-        <v>0</v>
-      </c>
-      <c r="K420">
-        <v>7</v>
-      </c>
-      <c r="L420" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A421" t="s">
-        <v>304</v>
-      </c>
-      <c r="B421" t="s">
-        <v>66</v>
-      </c>
-      <c r="C421" t="s">
-        <v>29</v>
-      </c>
-      <c r="D421">
-        <v>0.35</v>
-      </c>
-      <c r="E421">
-        <v>29.23</v>
-      </c>
-      <c r="F421">
-        <v>0</v>
-      </c>
-      <c r="G421">
-        <v>0</v>
-      </c>
-      <c r="H421">
-        <v>0</v>
-      </c>
-      <c r="J421">
-        <v>0</v>
-      </c>
-      <c r="K421">
-        <v>15</v>
-      </c>
-      <c r="L421" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A422" t="s">
-        <v>316</v>
-      </c>
-      <c r="B422" t="s">
-        <v>82</v>
-      </c>
-      <c r="C422" t="s">
-        <v>21</v>
-      </c>
-      <c r="D422">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E422">
-        <v>64.64</v>
-      </c>
-      <c r="F422">
-        <v>0</v>
-      </c>
-      <c r="G422">
-        <v>0</v>
-      </c>
-      <c r="H422">
-        <v>0</v>
-      </c>
-      <c r="J422">
-        <v>0</v>
-      </c>
-      <c r="K422">
-        <v>9</v>
-      </c>
-      <c r="L422" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A423" t="s">
-        <v>317</v>
-      </c>
-      <c r="B423" t="s">
-        <v>37</v>
-      </c>
-      <c r="C423" t="s">
-        <v>38</v>
-      </c>
-      <c r="D423">
-        <v>0.26</v>
-      </c>
-      <c r="E423">
-        <v>9.57</v>
-      </c>
-      <c r="F423">
-        <v>0</v>
-      </c>
-      <c r="G423">
-        <v>0</v>
-      </c>
-      <c r="H423">
-        <v>0</v>
-      </c>
-      <c r="J423">
-        <v>0</v>
-      </c>
-      <c r="K423">
-        <v>8</v>
-      </c>
-      <c r="L423" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A424" t="s">
-        <v>318</v>
-      </c>
-      <c r="B424" t="s">
-        <v>37</v>
-      </c>
-      <c r="C424" t="s">
-        <v>38</v>
-      </c>
-      <c r="D424">
-        <v>0.17</v>
-      </c>
-      <c r="E424">
-        <v>26.52</v>
-      </c>
-      <c r="F424">
-        <v>0</v>
-      </c>
-      <c r="G424">
-        <v>0</v>
-      </c>
-      <c r="H424">
-        <v>0</v>
-      </c>
-      <c r="J424">
-        <v>0</v>
-      </c>
-      <c r="K424">
-        <v>9</v>
-      </c>
-      <c r="L424" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A425" t="s">
-        <v>319</v>
-      </c>
-      <c r="B425" t="s">
-        <v>20</v>
-      </c>
-      <c r="C425" t="s">
-        <v>38</v>
-      </c>
-      <c r="D425">
-        <v>0.38</v>
-      </c>
-      <c r="E425">
-        <v>16.149999999999999</v>
-      </c>
-      <c r="F425">
-        <v>0</v>
-      </c>
-      <c r="G425">
-        <v>0</v>
-      </c>
-      <c r="H425">
-        <v>0</v>
-      </c>
-      <c r="J425">
-        <v>0</v>
-      </c>
-      <c r="K425">
-        <v>3</v>
-      </c>
-      <c r="L425" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A426" t="s">
-        <v>309</v>
-      </c>
-      <c r="B426" t="s">
-        <v>20</v>
-      </c>
-      <c r="C426" t="s">
-        <v>38</v>
-      </c>
-      <c r="D426">
-        <v>0.23</v>
-      </c>
-      <c r="E426">
-        <v>48.46</v>
-      </c>
-      <c r="F426">
-        <v>0</v>
-      </c>
-      <c r="G426">
-        <v>0</v>
-      </c>
-      <c r="H426">
-        <v>0</v>
-      </c>
-      <c r="J426">
-        <v>0</v>
-      </c>
-      <c r="K426">
-        <v>4</v>
-      </c>
-      <c r="L426" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A427" t="s">
-        <v>310</v>
-      </c>
-      <c r="B427" t="s">
-        <v>92</v>
-      </c>
-      <c r="C427" t="s">
-        <v>21</v>
-      </c>
-      <c r="D427">
-        <v>0.08</v>
-      </c>
-      <c r="E427">
-        <v>90.77</v>
-      </c>
-      <c r="F427">
-        <v>7</v>
-      </c>
-      <c r="G427">
-        <v>0</v>
-      </c>
-      <c r="H427">
-        <v>0</v>
-      </c>
-      <c r="J427">
-        <v>0</v>
-      </c>
-      <c r="K427">
-        <v>11</v>
-      </c>
-      <c r="L427" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A428" t="s">
-        <v>311</v>
-      </c>
-      <c r="B428" t="s">
-        <v>92</v>
-      </c>
-      <c r="C428" t="s">
-        <v>21</v>
-      </c>
-      <c r="D428">
-        <v>0.12</v>
-      </c>
-      <c r="E428">
-        <v>6.92</v>
-      </c>
-      <c r="F428">
-        <v>7</v>
-      </c>
-      <c r="G428">
-        <v>0</v>
-      </c>
-      <c r="H428">
-        <v>0</v>
-      </c>
-      <c r="J428">
-        <v>0</v>
-      </c>
-      <c r="K428">
-        <v>13</v>
-      </c>
-      <c r="L428" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A429" t="s">
-        <v>312</v>
-      </c>
-      <c r="B429" t="s">
-        <v>92</v>
-      </c>
-      <c r="C429" t="s">
-        <v>21</v>
-      </c>
-      <c r="D429">
-        <v>0.19</v>
-      </c>
-      <c r="E429">
-        <v>10</v>
-      </c>
-      <c r="F429">
-        <v>6.89</v>
-      </c>
-      <c r="G429">
-        <v>0</v>
-      </c>
-      <c r="H429">
-        <v>0</v>
-      </c>
-      <c r="J429">
-        <v>0</v>
-      </c>
-      <c r="K429">
-        <v>12</v>
-      </c>
-      <c r="L429" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A430" t="s">
-        <v>313</v>
-      </c>
-      <c r="B430" t="s">
-        <v>92</v>
-      </c>
-      <c r="C430" t="s">
-        <v>21</v>
-      </c>
-      <c r="D430">
-        <v>0.12</v>
-      </c>
-      <c r="E430">
-        <v>32.31</v>
-      </c>
-      <c r="F430">
-        <v>0</v>
-      </c>
-      <c r="G430">
-        <v>2.69</v>
-      </c>
-      <c r="H430">
-        <v>0</v>
-      </c>
-      <c r="J430">
-        <v>0</v>
-      </c>
-      <c r="K430">
-        <v>11</v>
-      </c>
-      <c r="L430" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A431" t="s">
-        <v>314</v>
-      </c>
-      <c r="B431" t="s">
-        <v>92</v>
-      </c>
-      <c r="C431" t="s">
-        <v>21</v>
-      </c>
-      <c r="D431">
-        <v>0.04</v>
-      </c>
-      <c r="E431">
-        <v>38.08</v>
-      </c>
-      <c r="F431">
-        <v>0</v>
-      </c>
-      <c r="G431">
-        <v>1.54</v>
-      </c>
-      <c r="H431">
-        <v>0</v>
-      </c>
-      <c r="J431">
-        <v>0</v>
-      </c>
-      <c r="K431">
-        <v>13</v>
-      </c>
-      <c r="L431" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A432" t="s">
-        <v>315</v>
-      </c>
-      <c r="B432" t="s">
-        <v>92</v>
-      </c>
-      <c r="C432" t="s">
-        <v>21</v>
-      </c>
-      <c r="D432">
-        <v>0.15</v>
-      </c>
-      <c r="E432">
-        <v>56.54</v>
-      </c>
-      <c r="F432">
-        <v>0</v>
-      </c>
-      <c r="G432">
-        <v>3.46</v>
-      </c>
-      <c r="H432">
-        <v>0</v>
-      </c>
-      <c r="J432">
-        <v>0</v>
-      </c>
-      <c r="K432">
-        <v>13</v>
-      </c>
-      <c r="L432" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A433" t="s">
-        <v>306</v>
-      </c>
-      <c r="B433" t="s">
-        <v>44</v>
-      </c>
-      <c r="C433" t="s">
-        <v>14</v>
-      </c>
-      <c r="D433">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="E433">
-        <v>28.93</v>
-      </c>
-      <c r="F433">
-        <v>0</v>
-      </c>
-      <c r="G433">
-        <v>0</v>
-      </c>
-      <c r="H433">
-        <v>0</v>
-      </c>
-      <c r="J433">
-        <v>0</v>
-      </c>
-      <c r="K433">
-        <v>11</v>
-      </c>
-      <c r="L433" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A434" t="s">
-        <v>307</v>
-      </c>
-      <c r="B434" t="s">
-        <v>44</v>
-      </c>
-      <c r="C434" t="s">
-        <v>14</v>
-      </c>
-      <c r="D434">
-        <v>0.89</v>
-      </c>
-      <c r="E434">
-        <v>82.86</v>
-      </c>
-      <c r="F434">
-        <v>0</v>
-      </c>
-      <c r="G434">
-        <v>0</v>
-      </c>
-      <c r="H434">
-        <v>0</v>
-      </c>
-      <c r="J434">
-        <v>0</v>
-      </c>
-      <c r="K434">
-        <v>12</v>
-      </c>
-      <c r="L434" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A435" t="s">
-        <v>308</v>
-      </c>
-      <c r="B435" t="s">
-        <v>108</v>
-      </c>
-      <c r="C435" t="s">
-        <v>29</v>
-      </c>
-      <c r="D435">
-        <v>0.15</v>
-      </c>
-      <c r="E435">
-        <v>51.5</v>
-      </c>
-      <c r="F435">
-        <v>5.5</v>
-      </c>
-      <c r="G435">
-        <v>0</v>
-      </c>
-      <c r="H435">
-        <v>0</v>
-      </c>
-      <c r="J435">
-        <v>0</v>
-      </c>
-      <c r="K435">
-        <v>11</v>
-      </c>
-      <c r="L435" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A436" t="s">
-        <v>292</v>
-      </c>
-      <c r="B436" t="s">
-        <v>108</v>
-      </c>
-      <c r="C436" t="s">
-        <v>29</v>
-      </c>
-      <c r="D436">
-        <v>0.3</v>
-      </c>
-      <c r="E436">
-        <v>72.5</v>
-      </c>
-      <c r="F436">
-        <v>0</v>
-      </c>
-      <c r="G436">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="H436">
-        <v>0</v>
-      </c>
-      <c r="J436">
-        <v>0</v>
-      </c>
-      <c r="K436">
-        <v>11</v>
-      </c>
-      <c r="L436" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A437" t="s">
-        <v>302</v>
-      </c>
-      <c r="B437" t="s">
-        <v>108</v>
-      </c>
-      <c r="C437" t="s">
-        <v>29</v>
-      </c>
-      <c r="D437">
-        <v>0.4</v>
-      </c>
-      <c r="E437">
-        <v>59</v>
-      </c>
-      <c r="F437">
-        <v>0</v>
-      </c>
-      <c r="G437">
-        <v>4</v>
-      </c>
-      <c r="H437">
-        <v>0</v>
-      </c>
-      <c r="J437">
-        <v>0</v>
-      </c>
-      <c r="K437">
-        <v>11</v>
-      </c>
-      <c r="L437" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A438" t="s">
-        <v>303</v>
-      </c>
-      <c r="B438" t="s">
-        <v>112</v>
-      </c>
-      <c r="C438" t="s">
-        <v>29</v>
-      </c>
-      <c r="D438">
-        <v>0.6</v>
-      </c>
-      <c r="E438">
-        <v>46</v>
-      </c>
-      <c r="F438">
-        <v>2.5</v>
-      </c>
-      <c r="G438">
-        <v>0</v>
-      </c>
-      <c r="H438">
-        <v>0</v>
-      </c>
-      <c r="J438">
-        <v>0</v>
-      </c>
-      <c r="K438">
-        <v>13</v>
-      </c>
-      <c r="L438" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A439" t="s">
-        <v>304</v>
-      </c>
-      <c r="B439" t="s">
-        <v>112</v>
-      </c>
-      <c r="C439" t="s">
-        <v>29</v>
-      </c>
-      <c r="D439">
-        <v>0.25</v>
-      </c>
-      <c r="E439">
-        <v>19.170000000000002</v>
-      </c>
-      <c r="F439">
-        <v>0</v>
-      </c>
-      <c r="G439">
-        <v>0</v>
-      </c>
-      <c r="H439">
-        <v>0</v>
-      </c>
-      <c r="J439">
-        <v>0</v>
-      </c>
-      <c r="K439">
-        <v>13</v>
-      </c>
-      <c r="L439" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A440" t="s">
-        <v>321</v>
-      </c>
-      <c r="B440" t="s">
-        <v>112</v>
-      </c>
-      <c r="C440" t="s">
-        <v>29</v>
-      </c>
-      <c r="D440">
-        <v>0.36</v>
-      </c>
-      <c r="E440">
-        <v>63.64</v>
-      </c>
-      <c r="F440">
-        <v>2.5</v>
-      </c>
-      <c r="G440">
-        <v>0</v>
-      </c>
-      <c r="H440">
-        <v>0</v>
-      </c>
-      <c r="J440">
-        <v>0</v>
-      </c>
-      <c r="K440">
-        <v>13</v>
-      </c>
-      <c r="L440" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A441" t="s">
-        <v>316</v>
-      </c>
-      <c r="B441" t="s">
-        <v>112</v>
-      </c>
-      <c r="C441" t="s">
-        <v>29</v>
-      </c>
-      <c r="D441">
-        <v>0.33</v>
-      </c>
-      <c r="E441">
-        <v>37.5</v>
-      </c>
-      <c r="F441">
-        <v>0</v>
-      </c>
-      <c r="G441">
-        <v>0</v>
-      </c>
-      <c r="H441">
-        <v>0</v>
-      </c>
-      <c r="J441">
-        <v>0</v>
-      </c>
-      <c r="K441">
-        <v>13</v>
-      </c>
-      <c r="L441" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A442" t="s">
-        <v>317</v>
-      </c>
-      <c r="B442" t="s">
-        <v>112</v>
-      </c>
-      <c r="C442" t="s">
-        <v>29</v>
-      </c>
-      <c r="D442">
-        <v>0.21</v>
-      </c>
-      <c r="E442">
-        <v>71.430000000000007</v>
-      </c>
-      <c r="F442">
-        <v>0</v>
-      </c>
-      <c r="G442">
-        <v>5</v>
-      </c>
-      <c r="H442">
-        <v>0</v>
-      </c>
-      <c r="J442">
-        <v>0</v>
-      </c>
-      <c r="K442">
-        <v>13</v>
-      </c>
-      <c r="L442" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A443" t="s">
-        <v>318</v>
-      </c>
-      <c r="B443" t="s">
-        <v>112</v>
-      </c>
-      <c r="C443" t="s">
-        <v>29</v>
-      </c>
-      <c r="D443">
-        <v>0.5</v>
-      </c>
-      <c r="E443">
-        <v>57.5</v>
-      </c>
-      <c r="F443">
-        <v>0</v>
-      </c>
-      <c r="G443">
-        <v>0</v>
-      </c>
-      <c r="H443">
-        <v>0</v>
-      </c>
-      <c r="J443">
-        <v>0</v>
-      </c>
-      <c r="K443">
-        <v>11</v>
-      </c>
-      <c r="L443" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A444" t="s">
-        <v>319</v>
-      </c>
-      <c r="B444" t="s">
-        <v>39</v>
-      </c>
-      <c r="C444" t="s">
-        <v>21</v>
-      </c>
-      <c r="D444">
-        <v>0.18</v>
-      </c>
-      <c r="E444">
-        <v>23.45</v>
-      </c>
-      <c r="F444">
-        <v>0</v>
-      </c>
-      <c r="G444">
-        <v>0</v>
-      </c>
-      <c r="H444">
-        <v>0</v>
-      </c>
-      <c r="J444">
-        <v>0</v>
-      </c>
-      <c r="K444">
-        <v>18</v>
-      </c>
-      <c r="L444" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A445" t="s">
-        <v>309</v>
-      </c>
-      <c r="B445" t="s">
-        <v>39</v>
-      </c>
-      <c r="C445" t="s">
-        <v>21</v>
-      </c>
-      <c r="D445">
-        <v>0.22</v>
-      </c>
-      <c r="E445">
-        <v>70.91</v>
-      </c>
-      <c r="F445">
-        <v>0</v>
-      </c>
-      <c r="G445">
-        <v>0</v>
-      </c>
-      <c r="H445">
-        <v>0</v>
-      </c>
-      <c r="J445">
-        <v>0</v>
-      </c>
-      <c r="K445">
-        <v>18</v>
-      </c>
-      <c r="L445" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A446" t="s">
-        <v>310</v>
-      </c>
-      <c r="B446" t="s">
-        <v>39</v>
-      </c>
-      <c r="C446" t="s">
-        <v>21</v>
-      </c>
-      <c r="D446">
-        <v>0.15</v>
-      </c>
-      <c r="E446">
-        <v>32.18</v>
-      </c>
-      <c r="F446">
-        <v>0</v>
-      </c>
-      <c r="G446">
-        <v>0</v>
-      </c>
-      <c r="H446">
-        <v>0</v>
-      </c>
-      <c r="J446">
-        <v>0</v>
-      </c>
-      <c r="K446">
-        <v>16</v>
-      </c>
-      <c r="L446" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A447" t="s">
-        <v>311</v>
-      </c>
-      <c r="B447" t="s">
-        <v>74</v>
-      </c>
-      <c r="C447" t="s">
-        <v>29</v>
-      </c>
-      <c r="D447">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E447">
-        <v>18.28</v>
-      </c>
-      <c r="F447">
-        <v>4.5</v>
-      </c>
-      <c r="G447">
-        <v>0</v>
-      </c>
-      <c r="H447">
-        <v>0</v>
-      </c>
-      <c r="J447">
-        <v>0</v>
-      </c>
-      <c r="K447">
-        <v>17</v>
-      </c>
-      <c r="L447" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A448" t="s">
-        <v>321</v>
-      </c>
-      <c r="B448" t="s">
-        <v>74</v>
-      </c>
-      <c r="C448" t="s">
-        <v>29</v>
-      </c>
-      <c r="D448">
-        <v>0.21</v>
-      </c>
-      <c r="E448">
-        <v>41.38</v>
-      </c>
-      <c r="F448">
-        <v>0</v>
-      </c>
-      <c r="G448">
-        <v>0</v>
-      </c>
-      <c r="H448">
-        <v>0</v>
-      </c>
-      <c r="J448">
-        <v>0</v>
-      </c>
-      <c r="K448">
-        <v>17</v>
-      </c>
-      <c r="L448" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A449" t="s">
-        <v>316</v>
-      </c>
-      <c r="B449" t="s">
-        <v>74</v>
-      </c>
-      <c r="C449" t="s">
-        <v>29</v>
-      </c>
-      <c r="D449">
-        <v>0.24</v>
-      </c>
-      <c r="E449">
-        <v>50.34</v>
-      </c>
-      <c r="F449">
-        <v>0</v>
-      </c>
-      <c r="G449">
-        <v>1.38</v>
-      </c>
-      <c r="H449">
-        <v>0</v>
-      </c>
-      <c r="J449">
-        <v>0</v>
-      </c>
-      <c r="K449">
-        <v>16</v>
-      </c>
-      <c r="L449" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="450" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A450" t="s">
-        <v>317</v>
-      </c>
-      <c r="B450" t="s">
-        <v>111</v>
-      </c>
-      <c r="C450" t="s">
-        <v>18</v>
-      </c>
-      <c r="D450">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E450">
-        <v>16.11</v>
-      </c>
-      <c r="F450">
-        <v>3.5</v>
-      </c>
-      <c r="G450">
-        <v>0</v>
-      </c>
-      <c r="H450">
-        <v>0</v>
-      </c>
-      <c r="J450">
-        <v>0</v>
-      </c>
-      <c r="K450">
-        <v>15</v>
-      </c>
-      <c r="L450" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="451" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A451" t="s">
-        <v>318</v>
-      </c>
-      <c r="B451" t="s">
-        <v>111</v>
-      </c>
-      <c r="C451" t="s">
-        <v>18</v>
-      </c>
-      <c r="D451">
-        <v>0.39</v>
-      </c>
-      <c r="E451">
-        <v>62.78</v>
-      </c>
-      <c r="F451">
-        <v>3.5</v>
-      </c>
-      <c r="G451">
-        <v>0</v>
-      </c>
-      <c r="H451">
-        <v>0</v>
-      </c>
-      <c r="J451">
-        <v>0</v>
-      </c>
-      <c r="K451">
-        <v>12</v>
-      </c>
-      <c r="L451" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A452" t="s">
-        <v>319</v>
-      </c>
-      <c r="B452" t="s">
-        <v>111</v>
-      </c>
-      <c r="C452" t="s">
-        <v>18</v>
-      </c>
-      <c r="D452">
-        <v>0.5</v>
-      </c>
-      <c r="E452">
-        <v>48.89</v>
-      </c>
-      <c r="F452">
-        <v>0</v>
-      </c>
-      <c r="G452">
-        <v>1.1100000000000001</v>
-      </c>
-      <c r="H452">
-        <v>0</v>
-      </c>
-      <c r="J452">
-        <v>0</v>
-      </c>
-      <c r="K452">
-        <v>11</v>
-      </c>
-      <c r="L452" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A453" t="s">
-        <v>309</v>
-      </c>
-      <c r="B453" t="s">
-        <v>111</v>
-      </c>
-      <c r="C453" t="s">
-        <v>18</v>
-      </c>
-      <c r="D453">
-        <v>0.33</v>
-      </c>
-      <c r="E453">
-        <v>67.78</v>
-      </c>
-      <c r="F453">
-        <v>0</v>
-      </c>
-      <c r="G453">
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="H453">
-        <v>0</v>
-      </c>
-      <c r="J453">
-        <v>0</v>
-      </c>
-      <c r="K453">
-        <v>12</v>
-      </c>
-      <c r="L453" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="454" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A454" t="s">
-        <v>310</v>
-      </c>
-      <c r="B454" t="s">
-        <v>76</v>
-      </c>
-      <c r="C454" t="s">
-        <v>29</v>
-      </c>
-      <c r="D454">
-        <v>0.21</v>
-      </c>
-      <c r="E454">
-        <v>53.57</v>
-      </c>
-      <c r="F454">
-        <v>0</v>
-      </c>
-      <c r="G454">
-        <v>0</v>
-      </c>
-      <c r="H454">
-        <v>0</v>
-      </c>
-      <c r="J454">
-        <v>0</v>
-      </c>
-      <c r="K454">
-        <v>7</v>
-      </c>
-      <c r="L454" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A455" t="s">
-        <v>311</v>
-      </c>
-      <c r="B455" t="s">
-        <v>76</v>
-      </c>
-      <c r="C455" t="s">
-        <v>21</v>
-      </c>
-      <c r="D455">
-        <v>0.36</v>
-      </c>
-      <c r="E455">
-        <v>94.29</v>
-      </c>
-      <c r="F455">
-        <v>0</v>
-      </c>
-      <c r="G455">
-        <v>3.57</v>
-      </c>
-      <c r="H455">
-        <v>0</v>
-      </c>
-      <c r="J455">
-        <v>0</v>
-      </c>
-      <c r="K455">
-        <v>7</v>
-      </c>
-      <c r="L455" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A456" t="s">
-        <v>312</v>
-      </c>
-      <c r="B456" t="s">
-        <v>76</v>
-      </c>
-      <c r="C456" t="s">
-        <v>21</v>
-      </c>
-      <c r="D456">
-        <v>0.21</v>
-      </c>
-      <c r="E456">
-        <v>75.709999999999994</v>
-      </c>
-      <c r="F456">
-        <v>0</v>
-      </c>
-      <c r="G456">
-        <v>7.14</v>
-      </c>
-      <c r="H456">
-        <v>0</v>
-      </c>
-      <c r="J456">
-        <v>0</v>
-      </c>
-      <c r="K456">
-        <v>8</v>
-      </c>
-      <c r="L456" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="457" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A457" t="s">
-        <v>313</v>
-      </c>
-      <c r="B457" t="s">
-        <v>54</v>
-      </c>
-      <c r="C457" t="s">
-        <v>14</v>
-      </c>
-      <c r="D457">
-        <v>0.39</v>
-      </c>
-      <c r="E457">
-        <v>47.14</v>
-      </c>
-      <c r="F457">
-        <v>5</v>
-      </c>
-      <c r="G457">
-        <v>1.07</v>
-      </c>
-      <c r="H457">
-        <v>0</v>
-      </c>
-      <c r="J457">
-        <v>0</v>
-      </c>
-      <c r="K457">
-        <v>16</v>
-      </c>
-      <c r="L457" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A458" t="s">
-        <v>314</v>
-      </c>
-      <c r="B458" t="s">
-        <v>54</v>
-      </c>
-      <c r="C458" t="s">
-        <v>14</v>
-      </c>
-      <c r="D458">
-        <v>0.46</v>
-      </c>
-      <c r="E458">
-        <v>49.64</v>
-      </c>
-      <c r="F458">
-        <v>5</v>
-      </c>
-      <c r="G458">
-        <v>0</v>
-      </c>
-      <c r="H458">
-        <v>0</v>
-      </c>
-      <c r="J458">
-        <v>0</v>
-      </c>
-      <c r="K458">
-        <v>16</v>
-      </c>
-      <c r="L458" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A459" t="s">
-        <v>315</v>
-      </c>
-      <c r="B459" t="s">
-        <v>54</v>
-      </c>
-      <c r="C459" t="s">
-        <v>14</v>
-      </c>
-      <c r="D459">
-        <v>0.54</v>
-      </c>
-      <c r="E459">
-        <v>51.43</v>
-      </c>
-      <c r="F459">
-        <v>0</v>
-      </c>
-      <c r="G459">
-        <v>2.5</v>
-      </c>
-      <c r="H459">
-        <v>0</v>
-      </c>
-      <c r="J459">
-        <v>0</v>
-      </c>
-      <c r="K459">
-        <v>18</v>
-      </c>
-      <c r="L459" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A460" t="s">
-        <v>306</v>
-      </c>
-      <c r="B460" t="s">
-        <v>115</v>
-      </c>
-      <c r="C460" t="s">
-        <v>29</v>
-      </c>
-      <c r="D460">
-        <v>0.1</v>
-      </c>
-      <c r="E460">
-        <v>27.14</v>
-      </c>
-      <c r="F460">
-        <v>0</v>
-      </c>
-      <c r="G460">
-        <v>0</v>
-      </c>
-      <c r="H460">
-        <v>0</v>
-      </c>
-      <c r="J460">
-        <v>0</v>
-      </c>
-      <c r="K460">
-        <v>16</v>
-      </c>
-      <c r="L460" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="461" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A461" t="s">
-        <v>307</v>
-      </c>
-      <c r="B461" t="s">
-        <v>115</v>
-      </c>
-      <c r="C461" t="s">
-        <v>29</v>
-      </c>
-      <c r="D461">
-        <v>0.24</v>
-      </c>
-      <c r="E461">
-        <v>59.52</v>
-      </c>
-      <c r="F461">
-        <v>0</v>
-      </c>
-      <c r="G461">
-        <v>0</v>
-      </c>
-      <c r="H461">
-        <v>0</v>
-      </c>
-      <c r="J461">
-        <v>0</v>
-      </c>
-      <c r="K461">
-        <v>16</v>
-      </c>
-      <c r="L461" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A462" t="s">
-        <v>308</v>
-      </c>
-      <c r="B462" t="s">
-        <v>115</v>
-      </c>
-      <c r="C462" t="s">
-        <v>29</v>
-      </c>
-      <c r="D462">
-        <v>0.38</v>
-      </c>
-      <c r="E462">
-        <v>40.479999999999997</v>
-      </c>
-      <c r="F462">
-        <v>0</v>
-      </c>
-      <c r="G462">
-        <v>2.38</v>
-      </c>
-      <c r="H462">
-        <v>0</v>
-      </c>
-      <c r="J462">
-        <v>0</v>
-      </c>
-      <c r="K462">
-        <v>16</v>
-      </c>
-      <c r="L462" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="463" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A463" t="s">
-        <v>292</v>
-      </c>
-      <c r="B463" t="s">
-        <v>94</v>
-      </c>
-      <c r="C463" t="s">
-        <v>29</v>
-      </c>
-      <c r="D463">
-        <v>0.18</v>
-      </c>
-      <c r="E463">
-        <v>25.36</v>
-      </c>
-      <c r="F463">
-        <v>4</v>
-      </c>
-      <c r="G463">
-        <v>0</v>
-      </c>
-      <c r="H463">
-        <v>0</v>
-      </c>
-      <c r="J463">
-        <v>0</v>
-      </c>
-      <c r="K463">
-        <v>18</v>
-      </c>
-      <c r="L463" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A464" t="s">
-        <v>302</v>
-      </c>
-      <c r="B464" t="s">
-        <v>94</v>
-      </c>
-      <c r="C464" t="s">
-        <v>29</v>
-      </c>
-      <c r="D464">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E464">
-        <v>41.43</v>
-      </c>
-      <c r="F464">
-        <v>4</v>
-      </c>
-      <c r="G464">
-        <v>3.93</v>
-      </c>
-      <c r="H464">
-        <v>0</v>
-      </c>
-      <c r="J464">
-        <v>0</v>
-      </c>
-      <c r="K464">
-        <v>18</v>
-      </c>
-      <c r="L464" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="465" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A465" t="s">
-        <v>303</v>
-      </c>
-      <c r="B465" t="s">
-        <v>114</v>
-      </c>
-      <c r="C465" t="s">
-        <v>29</v>
-      </c>
-      <c r="D465">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="E465">
-        <v>14.64</v>
-      </c>
-      <c r="F465">
-        <v>4</v>
-      </c>
-      <c r="G465">
-        <v>0</v>
-      </c>
-      <c r="H465">
-        <v>0</v>
-      </c>
-      <c r="J465">
-        <v>0</v>
-      </c>
-      <c r="K465">
-        <v>18</v>
-      </c>
-      <c r="L465" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="466" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A466" t="s">
-        <v>304</v>
-      </c>
-      <c r="B466" t="s">
-        <v>114</v>
-      </c>
-      <c r="C466" t="s">
-        <v>29</v>
-      </c>
-      <c r="D466">
-        <v>0.11</v>
-      </c>
-      <c r="E466">
-        <v>56.79</v>
-      </c>
-      <c r="F466">
-        <v>4</v>
-      </c>
-      <c r="G466">
-        <v>1.43</v>
-      </c>
-      <c r="H466">
-        <v>0</v>
-      </c>
-      <c r="J466">
-        <v>0</v>
-      </c>
-      <c r="K466">
-        <v>18</v>
-      </c>
-      <c r="L466" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A467" t="s">
-        <v>305</v>
-      </c>
-      <c r="B467" t="s">
-        <v>39</v>
-      </c>
-      <c r="C467" t="s">
-        <v>21</v>
-      </c>
-      <c r="D467">
-        <v>0.09</v>
-      </c>
-      <c r="E467">
-        <v>58.18</v>
-      </c>
-      <c r="F467">
-        <v>0</v>
-      </c>
-      <c r="G467">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="H467">
-        <v>0</v>
-      </c>
-      <c r="J467">
-        <v>0</v>
-      </c>
-      <c r="K467">
-        <v>13</v>
-      </c>
-      <c r="L467" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="468" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A468" t="s">
-        <v>320</v>
-      </c>
-      <c r="B468" t="s">
-        <v>94</v>
-      </c>
-      <c r="C468" t="s">
-        <v>29</v>
-      </c>
-      <c r="D468">
-        <v>0.21</v>
-      </c>
-      <c r="E468">
-        <v>57.5</v>
-      </c>
-      <c r="F468">
-        <v>0</v>
-      </c>
-      <c r="G468">
-        <v>10</v>
-      </c>
-      <c r="H468">
-        <v>0</v>
-      </c>
-      <c r="J468">
-        <v>0</v>
-      </c>
-      <c r="K468">
-        <v>9</v>
-      </c>
-      <c r="L468" t="s">
-        <v>300</v>
       </c>
     </row>
   </sheetData>

--- a/data/pest_disease_control.xlsx
+++ b/data/pest_disease_control.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L433"/>
+  <dimension ref="A1:L442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19382,35 +19382,393 @@
           <t>MIX</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>20.59</t>
-        </is>
-      </c>
-      <c r="F433" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G433" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="D433" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E433" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="F433" t="n">
+        <v>0</v>
+      </c>
+      <c r="G433" t="n">
+        <v>0</v>
       </c>
       <c r="H433" t="inlineStr"/>
       <c r="I433" t="inlineStr"/>
       <c r="J433" t="inlineStr"/>
-      <c r="K433" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="K433" t="n">
+        <v>16</v>
       </c>
       <c r="L433" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>DG05000</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E434" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F434" t="n">
+        <v>0</v>
+      </c>
+      <c r="G434" t="n">
+        <v>0</v>
+      </c>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="n">
+        <v>16</v>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>DG35000</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E435" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="F435" t="n">
+        <v>0</v>
+      </c>
+      <c r="G435" t="n">
+        <v>0</v>
+      </c>
+      <c r="H435" t="inlineStr"/>
+      <c r="I435" t="inlineStr"/>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="n">
+        <v>9</v>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>DG31000</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E436" t="n">
+        <v>20</v>
+      </c>
+      <c r="F436" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G436" t="n">
+        <v>0</v>
+      </c>
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr"/>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="n">
+        <v>16</v>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>DG32000</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>N41</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E437" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="F437" t="n">
+        <v>0</v>
+      </c>
+      <c r="G437" t="n">
+        <v>0</v>
+      </c>
+      <c r="H437" t="inlineStr"/>
+      <c r="I437" t="inlineStr"/>
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="n">
+        <v>15</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>DG12000</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E438" t="n">
+        <v>14.23</v>
+      </c>
+      <c r="F438" t="n">
+        <v>0</v>
+      </c>
+      <c r="G438" t="n">
+        <v>0</v>
+      </c>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr"/>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="n">
+        <v>18</v>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>DG01000</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>MIX</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>1</v>
+      </c>
+      <c r="E439" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="F439" t="n">
+        <v>0</v>
+      </c>
+      <c r="G439" t="n">
+        <v>18</v>
+      </c>
+      <c r="H439" t="inlineStr"/>
+      <c r="I439" t="inlineStr"/>
+      <c r="J439" t="inlineStr"/>
+      <c r="K439" t="inlineStr"/>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>DG37000</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E440" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="F440" t="n">
+        <v>0</v>
+      </c>
+      <c r="G440" t="n">
+        <v>0</v>
+      </c>
+      <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr"/>
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="n">
+        <v>5</v>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>DG39000</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E441" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="F441" t="n">
+        <v>0</v>
+      </c>
+      <c r="G441" t="n">
+        <v>0</v>
+      </c>
+      <c r="H441" t="inlineStr"/>
+      <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="n">
+        <v>9</v>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>DG27000</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>7.78</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr"/>
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
         <is>
           <t>2026/27</t>
         </is>
